--- a/output/tables/mixed_model_results.xlsx
+++ b/output/tables/mixed_model_results.xlsx
@@ -358,7 +358,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -439,25 +439,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3190629929315108</v>
+        <v>0.3190629929315109</v>
       </c>
       <c r="E2">
-        <v>0.3206914106929254</v>
+        <v>0.3206914106929256</v>
       </c>
       <c r="F2">
-        <v>0.001628417761414654</v>
+        <v>0.00162841776141463</v>
       </c>
       <c r="G2">
-        <v>-0.002299408682989934</v>
+        <v>-0.002299408682489893</v>
       </c>
       <c r="H2">
-        <v>0.005556244205819243</v>
+        <v>0.005556244205319152</v>
       </c>
       <c r="I2">
-        <v>0.5103750035229583</v>
+        <v>0.5103750035229504</v>
       </c>
       <c r="J2">
-        <v>0.2786964623956125</v>
+        <v>0.2786964623461505</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0.483487909311432</v>
+        <v>0.4834879092884048</v>
       </c>
     </row>
     <row r="3">
@@ -488,25 +488,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.3190628451357969</v>
+        <v>0.3190628451357968</v>
       </c>
       <c r="E3">
-        <v>0.3176096175964228</v>
+        <v>0.3176096175964226</v>
       </c>
       <c r="F3">
-        <v>-0.001453227539374118</v>
+        <v>-0.001453227539374158</v>
       </c>
       <c r="G3">
-        <v>-0.004185924562831025</v>
+        <v>-0.00418592456331422</v>
       </c>
       <c r="H3">
-        <v>0.001279469484082789</v>
+        <v>0.001279469484565903</v>
       </c>
       <c r="I3">
-        <v>-0.4554674922288764</v>
+        <v>-0.4554674922288893</v>
       </c>
       <c r="J3">
-        <v>0.1891462213993942</v>
+        <v>0.1891462214569604</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0.4911506851247366</v>
+        <v>0.4911506851626125</v>
       </c>
     </row>
     <row r="4">
@@ -537,25 +537,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.3176092318311068</v>
+        <v>0.3176092318311073</v>
       </c>
       <c r="E4">
-        <v>0.3178343161300918</v>
+        <v>0.3178343161300924</v>
       </c>
       <c r="F4">
-        <v>0.0002250842989849678</v>
+        <v>0.0002250842989850668</v>
       </c>
       <c r="G4">
-        <v>-0.003030556125065962</v>
+        <v>-0.00303055612458806</v>
       </c>
       <c r="H4">
-        <v>0.003480724723035898</v>
+        <v>0.003480724722558193</v>
       </c>
       <c r="I4">
-        <v>0.07086831125383017</v>
+        <v>0.0708683112538612</v>
       </c>
       <c r="J4">
-        <v>0.8399743913823063</v>
+        <v>0.8399743913592389</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0.8252510356402808</v>
+        <v>0.825251035653417</v>
       </c>
     </row>
     <row r="5">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.3176091753203836</v>
+        <v>0.3176091753203997</v>
       </c>
       <c r="E5">
-        <v>0.3185644779284539</v>
+        <v>0.3185644779285982</v>
       </c>
       <c r="F5">
-        <v>0.0009553026080703374</v>
+        <v>0.0009553026081983861</v>
       </c>
       <c r="G5">
-        <v>-0.002708898741119811</v>
+        <v>-0.002708898722691901</v>
       </c>
       <c r="H5">
-        <v>0.004619503957260486</v>
+        <v>0.004619503939088674</v>
       </c>
       <c r="I5">
-        <v>0.300779285455683</v>
+        <v>0.3007792854959842</v>
       </c>
       <c r="J5">
-        <v>0.4675607228752174</v>
+        <v>0.4675607208059289</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.4734218050828248</v>
+        <v>0.4734218038422473</v>
       </c>
     </row>
     <row r="6">
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.3176092357716369</v>
+        <v>0.3176092357715212</v>
       </c>
       <c r="E6">
-        <v>0.3180293554077357</v>
+        <v>0.3180293554112534</v>
       </c>
       <c r="F6">
-        <v>0.0004201196360987412</v>
+        <v>0.0004201196397321896</v>
       </c>
       <c r="G6">
-        <v>-0.002675307102020453</v>
+        <v>-0.002675307069720221</v>
       </c>
       <c r="H6">
-        <v>0.003515546374217935</v>
+        <v>0.0035155463491846</v>
       </c>
       <c r="I6">
-        <v>0.1322756358385025</v>
+        <v>0.1322756369825503</v>
       </c>
       <c r="J6">
-        <v>0.6949539694890001</v>
+        <v>0.6949539644488112</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0.4355566206638333</v>
+        <v>0.4355566929311028</v>
       </c>
     </row>
     <row r="7">
@@ -684,25 +684,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>439.9038217031746</v>
+        <v>439.9038217031748</v>
       </c>
       <c r="E7">
-        <v>422.2294087534438</v>
+        <v>422.229408753444</v>
       </c>
       <c r="F7">
-        <v>-17.67441294973088</v>
+        <v>-17.67441294973086</v>
       </c>
       <c r="G7">
-        <v>-38.36366422224572</v>
+        <v>-38.36366422257507</v>
       </c>
       <c r="H7">
-        <v>3.014838322783973</v>
+        <v>3.014838323113359</v>
       </c>
       <c r="I7">
-        <v>-4.017790270905329</v>
+        <v>-4.017790270905324</v>
       </c>
       <c r="J7">
-        <v>0.07262898000717133</v>
+        <v>0.07262898000982476</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0.9889160873094436</v>
+        <v>0.9889160873100195</v>
       </c>
     </row>
     <row r="8">
@@ -733,25 +733,25 @@
         </is>
       </c>
       <c r="D8">
-        <v>439.9024129871331</v>
+        <v>439.9024129871332</v>
       </c>
       <c r="E8">
-        <v>429.8342967628467</v>
+        <v>429.8342967628469</v>
       </c>
       <c r="F8">
-        <v>-10.0681162242864</v>
+        <v>-10.06811622428629</v>
       </c>
       <c r="G8">
-        <v>-40.11797127816327</v>
+        <v>-40.11797127933664</v>
       </c>
       <c r="H8">
-        <v>19.98173882959047</v>
+        <v>19.98173883076407</v>
       </c>
       <c r="I8">
-        <v>-2.288715844025363</v>
+        <v>-2.288715844025337</v>
       </c>
       <c r="J8">
-        <v>0.364497525864669</v>
+        <v>0.3644975258807731</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0.8708491495462888</v>
+        <v>0.8708491495458119</v>
       </c>
     </row>
     <row r="9">
@@ -782,25 +782,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>429.8313277409171</v>
+        <v>429.8313277409174</v>
       </c>
       <c r="E9">
-        <v>423.5415849952277</v>
+        <v>423.541584995228</v>
       </c>
       <c r="F9">
-        <v>-6.289742745689387</v>
+        <v>-6.289742745689423</v>
       </c>
       <c r="G9">
-        <v>-18.62907727691226</v>
+        <v>-18.62907727702702</v>
       </c>
       <c r="H9">
-        <v>6.04959178553348</v>
+        <v>6.04959178564817</v>
       </c>
       <c r="I9">
-        <v>-1.463304868620595</v>
+        <v>-1.463304868620602</v>
       </c>
       <c r="J9">
-        <v>0.2032155511127371</v>
+        <v>0.2032155511158824</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0.9997166154524799</v>
+        <v>0.999716615452511</v>
       </c>
     </row>
     <row r="10">
@@ -831,25 +831,25 @@
         </is>
       </c>
       <c r="D10">
-        <v>429.8315844705174</v>
+        <v>429.8315844705177</v>
       </c>
       <c r="E10">
-        <v>417.9183058987444</v>
+        <v>417.9183058985104</v>
       </c>
       <c r="F10">
-        <v>-11.91327857177308</v>
+        <v>-11.91327857200735</v>
       </c>
       <c r="G10">
-        <v>-28.00835631499929</v>
+        <v>-28.00835632009727</v>
       </c>
       <c r="H10">
-        <v>4.181799171453122</v>
+        <v>4.181799176082567</v>
       </c>
       <c r="I10">
-        <v>-2.771615442464124</v>
+        <v>-2.771615442518624</v>
       </c>
       <c r="J10">
-        <v>0.09979838249743689</v>
+        <v>0.09979838255768392</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0.9954420644573392</v>
+        <v>0.9954420644577676</v>
       </c>
     </row>
     <row r="11">
@@ -880,25 +880,25 @@
         </is>
       </c>
       <c r="D11">
-        <v>429.831509689801</v>
+        <v>429.8315096897875</v>
       </c>
       <c r="E11">
-        <v>415.0544834001441</v>
+        <v>415.0544834054531</v>
       </c>
       <c r="F11">
-        <v>-14.77702628965686</v>
+        <v>-14.77702628433436</v>
       </c>
       <c r="G11">
-        <v>-32.60945203275184</v>
+        <v>-32.60945195737904</v>
       </c>
       <c r="H11">
-        <v>3.05539945343812</v>
+        <v>3.055399388710329</v>
       </c>
       <c r="I11">
-        <v>-3.43786482762073</v>
+        <v>-3.437864826382561</v>
       </c>
       <c r="J11">
-        <v>0.07784478214197299</v>
+        <v>0.07784478151375762</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.9952212449517688</v>
+        <v>0.9952212450447355</v>
       </c>
     </row>
     <row r="12">
@@ -929,25 +929,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>1.981685256768667</v>
+        <v>1.981685256768479</v>
       </c>
       <c r="E12">
-        <v>1.963191854770508</v>
+        <v>1.963191854770372</v>
       </c>
       <c r="F12">
-        <v>-0.01849340199815907</v>
+        <v>-0.01849340199810703</v>
       </c>
       <c r="G12">
-        <v>-0.0516541464588012</v>
+        <v>-0.05165414644730448</v>
       </c>
       <c r="H12">
-        <v>0.01466734246248306</v>
+        <v>0.01466734245109041</v>
       </c>
       <c r="I12">
-        <v>-0.9332159047453573</v>
+        <v>-0.9332159047428198</v>
       </c>
       <c r="J12">
-        <v>0.1740215630764897</v>
+        <v>0.174021562970222</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.4613569056695641</v>
+        <v>0.4613569056096266</v>
       </c>
     </row>
     <row r="13">
@@ -978,25 +978,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>1.981684675825245</v>
+        <v>1.981684675825401</v>
       </c>
       <c r="E13">
-        <v>1.965651069444255</v>
+        <v>1.96565106944436</v>
       </c>
       <c r="F13">
-        <v>-0.01603360638098994</v>
+        <v>-0.01603360638104076</v>
       </c>
       <c r="G13">
-        <v>-0.05039143349570349</v>
+        <v>-0.05039143350350458</v>
       </c>
       <c r="H13">
-        <v>0.01832422073372362</v>
+        <v>0.01832422074142305</v>
       </c>
       <c r="I13">
-        <v>-0.8090896890199226</v>
+        <v>-0.8090896890224238</v>
       </c>
       <c r="J13">
-        <v>0.23418187483169</v>
+        <v>0.234181874912321</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0.9977664570314975</v>
+        <v>0.9977664570309991</v>
       </c>
     </row>
     <row r="14">
@@ -1027,25 +1027,25 @@
         </is>
       </c>
       <c r="D14">
-        <v>1.965659275306106</v>
+        <v>1.965659275306108</v>
       </c>
       <c r="E14">
-        <v>1.961540952445235</v>
+        <v>1.961540952445237</v>
       </c>
       <c r="F14">
-        <v>-0.00411832286087098</v>
+        <v>-0.004118322860870968</v>
       </c>
       <c r="G14">
-        <v>-0.02189110728462484</v>
+        <v>-0.02189110728602746</v>
       </c>
       <c r="H14">
-        <v>0.01365446156288288</v>
+        <v>0.01365446156428552</v>
       </c>
       <c r="I14">
-        <v>-0.2095135669038902</v>
+        <v>-0.2095135669038894</v>
       </c>
       <c r="J14">
-        <v>0.5142972548228758</v>
+        <v>0.5142972548535101</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0.9985126838183408</v>
+        <v>0.9985126838186595</v>
       </c>
     </row>
     <row r="15">
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>1.965659554720978</v>
+        <v>1.965659554720974</v>
       </c>
       <c r="E15">
-        <v>1.955696270988015</v>
+        <v>1.95569627098797</v>
       </c>
       <c r="F15">
-        <v>-0.009963283732962441</v>
+        <v>-0.009963283733004312</v>
       </c>
       <c r="G15">
-        <v>-0.02722022575657781</v>
+        <v>-0.02722022575549572</v>
       </c>
       <c r="H15">
-        <v>0.00729365829065293</v>
+        <v>0.007293658289487094</v>
       </c>
       <c r="I15">
-        <v>-0.5068672094836236</v>
+        <v>-0.5068672094857546</v>
       </c>
       <c r="J15">
-        <v>0.1634630943122229</v>
+        <v>0.1634630942915104</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0.9479401743007232</v>
+        <v>0.9479401742957627</v>
       </c>
     </row>
     <row r="16">
@@ -1125,25 +1125,25 @@
         </is>
       </c>
       <c r="D16">
-        <v>1.965659414533605</v>
+        <v>1.965659414533604</v>
       </c>
       <c r="E16">
-        <v>1.95270588394614</v>
+        <v>1.952705883946115</v>
       </c>
       <c r="F16">
-        <v>-0.01295353058746412</v>
+        <v>-0.01295353058748931</v>
       </c>
       <c r="G16">
-        <v>-0.02987359521662381</v>
+        <v>-0.02987359521608061</v>
       </c>
       <c r="H16">
-        <v>0.003966534041695566</v>
+        <v>0.003966534041102003</v>
       </c>
       <c r="I16">
-        <v>-0.6589916081946284</v>
+        <v>-0.65899160819591</v>
       </c>
       <c r="J16">
-        <v>0.0927985567921672</v>
+        <v>0.09279855678501803</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0.9121962359982263</v>
+        <v>0.9121962359954086</v>
       </c>
     </row>
     <row r="17">
@@ -1174,25 +1174,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>2.167068746891311</v>
+        <v>2.16706874689131</v>
       </c>
       <c r="E17">
-        <v>2.377924955682625</v>
+        <v>2.377924955682624</v>
       </c>
       <c r="F17">
-        <v>0.2108562087913144</v>
+        <v>0.2108562087913147</v>
       </c>
       <c r="G17">
-        <v>-0.006022623638805735</v>
+        <v>-0.006022623638297586</v>
       </c>
       <c r="H17">
-        <v>0.4277350412214346</v>
+        <v>0.427735041220927</v>
       </c>
       <c r="I17">
-        <v>9.730019368042225</v>
+        <v>9.730019368042239</v>
       </c>
       <c r="J17">
-        <v>0.05354293974251745</v>
+        <v>0.05354293974221414</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0.1934635983285402</v>
+        <v>0.1934635983299994</v>
       </c>
     </row>
     <row r="18">
@@ -1223,25 +1223,25 @@
         </is>
       </c>
       <c r="D18">
-        <v>2.167036359080488</v>
+        <v>2.167036359080486</v>
       </c>
       <c r="E18">
-        <v>2.323636537722989</v>
+        <v>2.323636537722987</v>
       </c>
       <c r="F18">
-        <v>0.1566001786425011</v>
+        <v>0.1566001786425012</v>
       </c>
       <c r="G18">
-        <v>-0.0025217474087737</v>
+        <v>-0.00252174740915731</v>
       </c>
       <c r="H18">
-        <v>0.3157221046937759</v>
+        <v>0.3157221046941596</v>
       </c>
       <c r="I18">
-        <v>7.226467520321132</v>
+        <v>7.226467520321143</v>
       </c>
       <c r="J18">
-        <v>0.05198437459121874</v>
+        <v>0.05198437459152316</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0.4481444809596478</v>
+        <v>0.4481444809641534</v>
       </c>
     </row>
     <row r="19">
@@ -1272,25 +1272,25 @@
         </is>
       </c>
       <c r="D19">
-        <v>2.323636537722991</v>
+        <v>2.323636537722984</v>
       </c>
       <c r="E19">
-        <v>2.348369878112611</v>
+        <v>2.348369878112605</v>
       </c>
       <c r="F19">
-        <v>0.02473334038962124</v>
+        <v>0.02473334038962182</v>
       </c>
       <c r="G19">
-        <v>-0.1356712701756237</v>
+        <v>-0.1356712701752076</v>
       </c>
       <c r="H19">
-        <v>0.1851379509548662</v>
+        <v>0.1851379509544513</v>
       </c>
       <c r="I19">
-        <v>1.064423802435912</v>
+        <v>1.064423802435941</v>
       </c>
       <c r="J19">
-        <v>0.6572819459231013</v>
+        <v>0.6572819459222934</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0.8301008524331054</v>
+        <v>0.8301008524302518</v>
       </c>
     </row>
     <row r="20">
@@ -1321,25 +1321,25 @@
         </is>
       </c>
       <c r="D20">
-        <v>2.323636537722987</v>
+        <v>2.323636537722988</v>
       </c>
       <c r="E20">
-        <v>2.442352776688062</v>
+        <v>2.442352776688102</v>
       </c>
       <c r="F20">
-        <v>0.1187162389650756</v>
+        <v>0.118716238965114</v>
       </c>
       <c r="G20">
-        <v>-0.0357568597948538</v>
+        <v>-0.03575685979426968</v>
       </c>
       <c r="H20">
-        <v>0.273189337725005</v>
+        <v>0.2731893377244977</v>
       </c>
       <c r="I20">
-        <v>5.109070934192221</v>
+        <v>5.109070934193872</v>
       </c>
       <c r="J20">
-        <v>0.09202428553305975</v>
+        <v>0.09202428553228659</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0.264832301347909</v>
+        <v>0.2648323013414869</v>
       </c>
     </row>
     <row r="21">
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="D21">
-        <v>2.323636537722986</v>
+        <v>2.323636537722989</v>
       </c>
       <c r="E21">
-        <v>2.474549123645008</v>
+        <v>2.474549123644997</v>
       </c>
       <c r="F21">
-        <v>0.1509125859220221</v>
+        <v>0.150912585922009</v>
       </c>
       <c r="G21">
-        <v>-0.006672177662184753</v>
+        <v>-0.006672177662350676</v>
       </c>
       <c r="H21">
-        <v>0.308497349506229</v>
+        <v>0.3084973495063686</v>
       </c>
       <c r="I21">
-        <v>6.494672616480147</v>
+        <v>6.494672616479572</v>
       </c>
       <c r="J21">
-        <v>0.05552863374471806</v>
+        <v>0.05552863374485917</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0.2541464968336551</v>
+        <v>0.254146496835586</v>
       </c>
     </row>
     <row r="22">
@@ -1419,25 +1419,25 @@
         </is>
       </c>
       <c r="D22">
-        <v>5.715657023779306</v>
+        <v>5.715657023779298</v>
       </c>
       <c r="E22">
-        <v>4.475082483533155</v>
+        <v>4.475082483533146</v>
       </c>
       <c r="F22">
-        <v>-1.240574540246151</v>
+        <v>-1.240574540246152</v>
       </c>
       <c r="G22">
-        <v>-2.574207131152335</v>
+        <v>-2.574207131143766</v>
       </c>
       <c r="H22">
-        <v>0.09305805066003248</v>
+        <v>0.09305805065146089</v>
       </c>
       <c r="I22">
-        <v>-21.70484574362824</v>
+        <v>-21.70484574362829</v>
       </c>
       <c r="J22">
-        <v>0.05952571919122629</v>
+        <v>0.05952571919031668</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0.5685524937785471</v>
+        <v>0.5685524937685535</v>
       </c>
     </row>
     <row r="23">
@@ -1468,25 +1468,25 @@
         </is>
       </c>
       <c r="D23">
-        <v>5.716450412948344</v>
+        <v>5.716450412948245</v>
       </c>
       <c r="E23">
-        <v>6.281438179491058</v>
+        <v>6.281438179490992</v>
       </c>
       <c r="F23">
-        <v>0.5649877665427132</v>
+        <v>0.5649877665427475</v>
       </c>
       <c r="G23">
-        <v>-1.705914417416853</v>
+        <v>-1.705914417349804</v>
       </c>
       <c r="H23">
-        <v>2.835889950502279</v>
+        <v>2.835889950435299</v>
       </c>
       <c r="I23">
-        <v>9.883541808793762</v>
+        <v>9.883541808794533</v>
       </c>
       <c r="J23">
-        <v>0.4863208836095088</v>
+        <v>0.4863208835977372</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0.9463393348705065</v>
+        <v>0.9463393348786391</v>
       </c>
     </row>
     <row r="24">
@@ -1517,25 +1517,25 @@
         </is>
       </c>
       <c r="D24">
-        <v>6.281363940121921</v>
+        <v>6.281363940122243</v>
       </c>
       <c r="E24">
-        <v>6.18247979200877</v>
+        <v>6.182479792008519</v>
       </c>
       <c r="F24">
-        <v>-0.0988841481131527</v>
+        <v>-0.09888414811372354</v>
       </c>
       <c r="G24">
-        <v>-2.508565184343755</v>
+        <v>-2.508565185856439</v>
       </c>
       <c r="H24">
-        <v>2.310796888117449</v>
+        <v>2.310796889628992</v>
       </c>
       <c r="I24">
-        <v>-1.574246438445236</v>
+        <v>-1.574246438454243</v>
       </c>
       <c r="J24">
-        <v>0.9043605697779602</v>
+        <v>0.9043605698369798</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0.8311648905466491</v>
+        <v>0.8311648906587366</v>
       </c>
     </row>
     <row r="25">
@@ -1566,25 +1566,25 @@
         </is>
       </c>
       <c r="D25">
-        <v>6.281298995275262</v>
+        <v>6.281298995275222</v>
       </c>
       <c r="E25">
-        <v>6.918865152854916</v>
+        <v>6.918865152854911</v>
       </c>
       <c r="F25">
-        <v>0.6375661575796534</v>
+        <v>0.6375661575796896</v>
       </c>
       <c r="G25">
-        <v>-2.719222156386482</v>
+        <v>-2.719222156449216</v>
       </c>
       <c r="H25">
-        <v>3.994354471545789</v>
+        <v>3.994354471608596</v>
       </c>
       <c r="I25">
-        <v>10.15022781210105</v>
+        <v>10.15022781210169</v>
       </c>
       <c r="J25">
-        <v>0.5881959312427495</v>
+        <v>0.5881959312493291</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.5118438171616353</v>
+        <v>0.5118438171490337</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         </is>
       </c>
       <c r="D26">
-        <v>6.281496051175661</v>
+        <v>6.281496054994521</v>
       </c>
       <c r="E26">
-        <v>6.384748473479042</v>
+        <v>6.384748469060736</v>
       </c>
       <c r="F26">
-        <v>0.1032524223033814</v>
+        <v>0.1032524140662161</v>
       </c>
       <c r="G26">
-        <v>-2.331481381839451</v>
+        <v>-2.331481319615513</v>
       </c>
       <c r="H26">
-        <v>2.537986226446214</v>
+        <v>2.537986147747945</v>
       </c>
       <c r="I26">
-        <v>1.643755268843263</v>
+        <v>1.643755136710122</v>
       </c>
       <c r="J26">
-        <v>0.9011885044968754</v>
+        <v>0.90118850947977</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0.3970272733520497</v>
+        <v>0.3970272446204093</v>
       </c>
     </row>
     <row r="27">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.3181513304353052</v>
+        <v>0.3181513304352998</v>
       </c>
       <c r="E27">
-        <v>0.3184091075185372</v>
+        <v>0.3184091075185365</v>
       </c>
       <c r="F27">
-        <v>0.0002577770832319153</v>
+        <v>0.0002577770832367278</v>
       </c>
       <c r="G27">
-        <v>-0.002681013398921037</v>
+        <v>-0.002681013398857472</v>
       </c>
       <c r="H27">
-        <v>0.003196567565384867</v>
+        <v>0.003196567565330927</v>
       </c>
       <c r="I27">
-        <v>0.08102341828312211</v>
+        <v>0.08102341828463613</v>
       </c>
       <c r="J27">
-        <v>0.7982681553576989</v>
+        <v>0.7982681553501167</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0.986655601296103</v>
+        <v>0.9866556012932424</v>
       </c>
     </row>
     <row r="28">
@@ -1713,25 +1713,25 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.3181408563298643</v>
+        <v>0.3181408563298728</v>
       </c>
       <c r="E28">
-        <v>0.3171571133163673</v>
+        <v>0.3171571133163644</v>
       </c>
       <c r="F28">
-        <v>-0.0009837430134970195</v>
+        <v>-0.0009837430135084845</v>
       </c>
       <c r="G28">
-        <v>-0.003848530882615325</v>
+        <v>-0.00384853087937032</v>
       </c>
       <c r="H28">
-        <v>0.001881044855621286</v>
+        <v>0.001881044852353351</v>
       </c>
       <c r="I28">
-        <v>-0.309216183311277</v>
+        <v>-0.3092161833148724</v>
       </c>
       <c r="J28">
-        <v>0.3543718200413557</v>
+        <v>0.3543718195693368</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0.1106425823974312</v>
+        <v>0.1106425824672489</v>
       </c>
     </row>
     <row r="29">
@@ -1762,25 +1762,25 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.3171563766424993</v>
+        <v>0.317156376642493</v>
       </c>
       <c r="E29">
-        <v>0.3175283304406998</v>
+        <v>0.3175283304419296</v>
       </c>
       <c r="F29">
-        <v>0.0003719537982004884</v>
+        <v>0.0003719537994366687</v>
       </c>
       <c r="G29">
-        <v>-0.002513151898269434</v>
+        <v>-0.002513151900273034</v>
       </c>
       <c r="H29">
-        <v>0.003257059494670411</v>
+        <v>0.003257059499146371</v>
       </c>
       <c r="I29">
-        <v>0.1172777297237688</v>
+        <v>0.1172777301135411</v>
       </c>
       <c r="J29">
-        <v>0.709136997857327</v>
+        <v>0.7091369972620301</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0.01385623935917413</v>
+        <v>0.01385623970414773</v>
       </c>
     </row>
     <row r="30">
@@ -1811,25 +1811,25 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.3171564320783765</v>
+        <v>0.317156432078655</v>
       </c>
       <c r="E30">
-        <v>0.3179407069618047</v>
+        <v>0.3179407069398695</v>
       </c>
       <c r="F30">
-        <v>0.000784274883428174</v>
+        <v>0.0007842748612146082</v>
       </c>
       <c r="G30">
-        <v>-0.002019907402320281</v>
+        <v>-0.002019907070692724</v>
       </c>
       <c r="H30">
-        <v>0.003588457169176629</v>
+        <v>0.00358845679312194</v>
       </c>
       <c r="I30">
-        <v>0.2472832974846816</v>
+        <v>0.2472832904804868</v>
       </c>
       <c r="J30">
-        <v>0.4389989982730254</v>
+        <v>0.4389989582019507</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.2730796857938258</v>
+        <v>0.2730796761965297</v>
       </c>
     </row>
     <row r="31">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.3171564401370898</v>
+        <v>0.3171564401370906</v>
       </c>
       <c r="E31">
-        <v>0.3168147616817668</v>
+        <v>0.3168147616816879</v>
       </c>
       <c r="F31">
-        <v>-0.0003416784553230011</v>
+        <v>-0.0003416784554026475</v>
       </c>
       <c r="G31">
-        <v>-0.003245858254783553</v>
+        <v>-0.003245858253491779</v>
       </c>
       <c r="H31">
-        <v>0.002562501344137551</v>
+        <v>0.002562501342686484</v>
       </c>
       <c r="I31">
-        <v>-0.1077318358016983</v>
+        <v>-0.1077318358268107</v>
       </c>
       <c r="J31">
-        <v>0.7329934793640946</v>
+        <v>0.7329934791869043</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0.7744304314373962</v>
+        <v>0.7744304315875609</v>
       </c>
     </row>
     <row r="32">
@@ -1909,25 +1909,25 @@
         </is>
       </c>
       <c r="D32">
-        <v>439.0329017272365</v>
+        <v>439.0329017272575</v>
       </c>
       <c r="E32">
-        <v>428.5560578434253</v>
+        <v>428.5560578434248</v>
       </c>
       <c r="F32">
-        <v>-10.47684388381112</v>
+        <v>-10.47684388383265</v>
       </c>
       <c r="G32">
-        <v>-39.51048655275635</v>
+        <v>-39.51048655409504</v>
       </c>
       <c r="H32">
-        <v>18.55679878513412</v>
+        <v>18.55679878642975</v>
       </c>
       <c r="I32">
-        <v>-2.386345953251631</v>
+        <v>-2.38634595325642</v>
       </c>
       <c r="J32">
-        <v>0.3340716888524247</v>
+        <v>0.3340716888700744</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0.9972508176712978</v>
+        <v>0.9972508176715205</v>
       </c>
     </row>
     <row r="33">
@@ -1958,25 +1958,25 @@
         </is>
       </c>
       <c r="D33">
-        <v>439.1151617433837</v>
+        <v>439.115161743403</v>
       </c>
       <c r="E33">
-        <v>419.9439712850182</v>
+        <v>419.9439712850209</v>
       </c>
       <c r="F33">
-        <v>-19.17119045836542</v>
+        <v>-19.17119045838206</v>
       </c>
       <c r="G33">
-        <v>-56.59647365462964</v>
+        <v>-56.59647366188492</v>
       </c>
       <c r="H33">
-        <v>18.25409273789881</v>
+        <v>18.25409274512079</v>
       </c>
       <c r="I33">
-        <v>-4.365868484761851</v>
+        <v>-4.365868484765451</v>
       </c>
       <c r="J33">
-        <v>0.2015493918467621</v>
+        <v>0.2015493919116456</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0.4793425432040139</v>
+        <v>0.4793425431134143</v>
       </c>
     </row>
     <row r="34">
@@ -2007,25 +2007,25 @@
         </is>
       </c>
       <c r="D34">
-        <v>419.9434235819385</v>
+        <v>419.94342358187</v>
       </c>
       <c r="E34">
-        <v>414.589977860073</v>
+        <v>414.5899778585058</v>
       </c>
       <c r="F34">
-        <v>-5.353445721865612</v>
+        <v>-5.353445723364242</v>
       </c>
       <c r="G34">
-        <v>-18.44377565189861</v>
+        <v>-18.44377569496977</v>
       </c>
       <c r="H34">
-        <v>7.736884208167388</v>
+        <v>7.736884248241282</v>
       </c>
       <c r="I34">
-        <v>-1.274801656900113</v>
+        <v>-1.274801657257186</v>
       </c>
       <c r="J34">
-        <v>0.2840169652659473</v>
+        <v>0.2840169663976808</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0.9974110775388939</v>
+        <v>0.9974110775454158</v>
       </c>
     </row>
     <row r="35">
@@ -2056,25 +2056,25 @@
         </is>
       </c>
       <c r="D35">
-        <v>419.944080847873</v>
+        <v>419.9440808479996</v>
       </c>
       <c r="E35">
-        <v>411.7723441333368</v>
+        <v>411.7723441361204</v>
       </c>
       <c r="F35">
-        <v>-8.17173671453611</v>
+        <v>-8.171736711879216</v>
       </c>
       <c r="G35">
-        <v>-21.32096748880579</v>
+        <v>-21.3209674496637</v>
       </c>
       <c r="H35">
-        <v>4.977494059733573</v>
+        <v>4.977494025905274</v>
       </c>
       <c r="I35">
-        <v>-1.945910678878307</v>
+        <v>-1.945910678245042</v>
       </c>
       <c r="J35">
-        <v>0.1423663507076569</v>
+        <v>0.1423663500366886</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0.9899349947255803</v>
+        <v>0.9899349947564495</v>
       </c>
     </row>
     <row r="36">
@@ -2105,25 +2105,25 @@
         </is>
       </c>
       <c r="D36">
-        <v>419.9430405774252</v>
+        <v>419.9430405774364</v>
       </c>
       <c r="E36">
-        <v>409.0229283268124</v>
+        <v>409.0229283264894</v>
       </c>
       <c r="F36">
-        <v>-10.92011225061277</v>
+        <v>-10.92011225094705</v>
       </c>
       <c r="G36">
-        <v>-24.02106226875536</v>
+        <v>-24.02106226202772</v>
       </c>
       <c r="H36">
-        <v>2.180837767529816</v>
+        <v>2.180837760133613</v>
       </c>
       <c r="I36">
-        <v>-2.600379383736787</v>
+        <v>-2.600379383816319</v>
       </c>
       <c r="J36">
-        <v>0.07681735305147486</v>
+        <v>0.07681735295222714</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0.787033512181703</v>
+        <v>0.7870335122044502</v>
       </c>
     </row>
     <row r="37">
@@ -2154,25 +2154,25 @@
         </is>
       </c>
       <c r="D37">
-        <v>1.97704373701642</v>
+        <v>1.977043737016501</v>
       </c>
       <c r="E37">
-        <v>1.965222678620958</v>
+        <v>1.965222678620959</v>
       </c>
       <c r="F37">
-        <v>-0.01182105839546244</v>
+        <v>-0.01182105839554173</v>
       </c>
       <c r="G37">
-        <v>-0.04346164696482454</v>
+        <v>-0.04346164696580174</v>
       </c>
       <c r="H37">
-        <v>0.01981953017389967</v>
+        <v>0.01981953017471827</v>
       </c>
       <c r="I37">
-        <v>-0.597915876828387</v>
+        <v>-0.5979158768323733</v>
       </c>
       <c r="J37">
-        <v>0.3199840945187651</v>
+        <v>0.3199840945275008</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0.5775376647740844</v>
+        <v>0.5775376647891546</v>
       </c>
     </row>
     <row r="38">
@@ -2203,25 +2203,25 @@
         </is>
       </c>
       <c r="D38">
-        <v>1.977019663303818</v>
+        <v>1.977019663765039</v>
       </c>
       <c r="E38">
-        <v>1.959981697313949</v>
+        <v>1.959981697463381</v>
       </c>
       <c r="F38">
-        <v>-0.01703796598986976</v>
+        <v>-0.01703796630165793</v>
       </c>
       <c r="G38">
-        <v>-0.04958376712637238</v>
+        <v>-0.04958378083047689</v>
       </c>
       <c r="H38">
-        <v>0.01550783514663285</v>
+        <v>0.01550784822716102</v>
       </c>
       <c r="I38">
-        <v>-0.8618005326966471</v>
+        <v>-0.8618005482662123</v>
       </c>
       <c r="J38">
-        <v>0.1942967722598404</v>
+        <v>0.1942969021797325</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0.9964476612020922</v>
+        <v>0.9964476621430448</v>
       </c>
     </row>
     <row r="39">
@@ -2252,25 +2252,25 @@
         </is>
       </c>
       <c r="D39">
-        <v>1.959991158442248</v>
+        <v>1.95999115844225</v>
       </c>
       <c r="E39">
-        <v>1.955058475168589</v>
+        <v>1.955058475168531</v>
       </c>
       <c r="F39">
-        <v>-0.004932683273658923</v>
+        <v>-0.00493268327371874</v>
       </c>
       <c r="G39">
-        <v>-0.02180391178362335</v>
+        <v>-0.02180391178091621</v>
       </c>
       <c r="H39">
-        <v>0.01193854523630551</v>
+        <v>0.01193854523347873</v>
       </c>
       <c r="I39">
-        <v>-0.251668649239178</v>
+        <v>-0.2516686492422297</v>
       </c>
       <c r="J39">
-        <v>0.4207676176854898</v>
+        <v>0.4207676176129129</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0.9990343225680034</v>
+        <v>0.9990343225677822</v>
       </c>
     </row>
     <row r="40">
@@ -2301,25 +2301,25 @@
         </is>
       </c>
       <c r="D40">
-        <v>1.959991377556695</v>
+        <v>1.959991377556689</v>
       </c>
       <c r="E40">
-        <v>1.951057483394317</v>
+        <v>1.951057483394225</v>
       </c>
       <c r="F40">
-        <v>-0.008933894162378768</v>
+        <v>-0.00893389416246371</v>
       </c>
       <c r="G40">
-        <v>-0.02559226459075884</v>
+        <v>-0.02559226458537813</v>
       </c>
       <c r="H40">
-        <v>0.007724476266001302</v>
+        <v>0.007724476260450714</v>
       </c>
       <c r="I40">
-        <v>-0.4558129318668568</v>
+        <v>-0.4558129318711922</v>
       </c>
       <c r="J40">
-        <v>0.1864087881303214</v>
+        <v>0.1864087880212859</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0.9381004222932535</v>
+        <v>0.9381004222975569</v>
       </c>
     </row>
     <row r="41">
@@ -2350,25 +2350,25 @@
         </is>
       </c>
       <c r="D41">
-        <v>1.95999141268432</v>
+        <v>1.959991412684328</v>
       </c>
       <c r="E41">
-        <v>1.947385616410563</v>
+        <v>1.94738561641093</v>
       </c>
       <c r="F41">
-        <v>-0.01260579627375704</v>
+        <v>-0.01260579627339727</v>
       </c>
       <c r="G41">
-        <v>-0.02927415557757732</v>
+        <v>-0.02927415558964218</v>
       </c>
       <c r="H41">
-        <v>0.004062563030063237</v>
+        <v>0.004062563042847633</v>
       </c>
       <c r="I41">
-        <v>-0.6431556889574678</v>
+        <v>-0.6431556889391095</v>
       </c>
       <c r="J41">
-        <v>0.09529110274516273</v>
+        <v>0.0952911029045802</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0.9120278248678994</v>
+        <v>0.9120278248754501</v>
       </c>
     </row>
     <row r="42">
@@ -2399,25 +2399,25 @@
         </is>
       </c>
       <c r="D42">
-        <v>2.328550850518401</v>
+        <v>2.328550850518403</v>
       </c>
       <c r="E42">
-        <v>2.375560612447559</v>
+        <v>2.375560612447569</v>
       </c>
       <c r="F42">
-        <v>0.04700976192915828</v>
+        <v>0.04700976192916646</v>
       </c>
       <c r="G42">
-        <v>-0.1428628747304765</v>
+        <v>-0.1428628747361482</v>
       </c>
       <c r="H42">
-        <v>0.2368823985887931</v>
+        <v>0.2368823985944811</v>
       </c>
       <c r="I42">
-        <v>2.018841972838711</v>
+        <v>2.018841972839061</v>
       </c>
       <c r="J42">
-        <v>0.488258676838041</v>
+        <v>0.4882586768498665</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>0.5961392227807991</v>
+        <v>0.5961392227840887</v>
       </c>
     </row>
     <row r="43">
@@ -2448,25 +2448,25 @@
         </is>
       </c>
       <c r="D43">
-        <v>2.327663122467713</v>
+        <v>2.327663122467758</v>
       </c>
       <c r="E43">
-        <v>2.538140299683224</v>
+        <v>2.538140299683232</v>
       </c>
       <c r="F43">
-        <v>0.2104771772155119</v>
+        <v>0.2104771772154732</v>
       </c>
       <c r="G43">
-        <v>0.06585776629886597</v>
+        <v>0.0658577662992737</v>
       </c>
       <c r="H43">
-        <v>0.3550965881321578</v>
+        <v>0.3550965881316727</v>
       </c>
       <c r="I43">
-        <v>9.042424360462043</v>
+        <v>9.042424360460204</v>
       </c>
       <c r="J43">
-        <v>0.01895754807943828</v>
+        <v>0.01895754807928951</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="M43">
-        <v>0.4128154230454026</v>
+        <v>0.4128154230396275</v>
       </c>
     </row>
     <row r="44">
@@ -2497,25 +2497,25 @@
         </is>
       </c>
       <c r="D44">
-        <v>2.538140299683228</v>
+        <v>2.538140299683223</v>
       </c>
       <c r="E44">
-        <v>2.586284951871236</v>
+        <v>2.586284951871228</v>
       </c>
       <c r="F44">
-        <v>0.04814465218800856</v>
+        <v>0.04814465218800511</v>
       </c>
       <c r="G44">
-        <v>-0.08955335129383485</v>
+        <v>-0.08955335129383994</v>
       </c>
       <c r="H44">
-        <v>0.185842655669852</v>
+        <v>0.1858426556698501</v>
       </c>
       <c r="I44">
-        <v>1.896847553857336</v>
+        <v>1.896847553857203</v>
       </c>
       <c r="J44">
-        <v>0.3469707721733717</v>
+        <v>0.3469707721734031</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>0.7680312217992304</v>
+        <v>0.7680312217998135</v>
       </c>
     </row>
     <row r="45">
@@ -2546,25 +2546,25 @@
         </is>
       </c>
       <c r="D45">
-        <v>2.538140299683226</v>
+        <v>2.538140299683234</v>
       </c>
       <c r="E45">
-        <v>2.640380226043094</v>
+        <v>2.640380226043109</v>
       </c>
       <c r="F45">
-        <v>0.1022399263598679</v>
+        <v>0.1022399263598751</v>
       </c>
       <c r="G45">
-        <v>-0.03496204301453591</v>
+        <v>-0.03496204301447114</v>
       </c>
       <c r="H45">
-        <v>0.2394418957342717</v>
+        <v>0.2394418957342214</v>
       </c>
       <c r="I45">
-        <v>4.0281432185852</v>
+        <v>4.02814321858547</v>
       </c>
       <c r="J45">
-        <v>0.09837134235166967</v>
+        <v>0.09837134235156719</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>0.5294091879953482</v>
+        <v>0.5294091879943162</v>
       </c>
     </row>
     <row r="46">
@@ -2595,25 +2595,25 @@
         </is>
       </c>
       <c r="D46">
-        <v>2.538140299683227</v>
+        <v>2.538140299683226</v>
       </c>
       <c r="E46">
-        <v>2.697934368694882</v>
+        <v>2.697934368694944</v>
       </c>
       <c r="F46">
-        <v>0.1597940690116546</v>
+        <v>0.1597940690117191</v>
       </c>
       <c r="G46">
-        <v>0.01608110119596926</v>
+        <v>0.0160811011967274</v>
       </c>
       <c r="H46">
-        <v>0.30350703682734</v>
+        <v>0.3035070368267108</v>
       </c>
       <c r="I46">
-        <v>6.295714584083383</v>
+        <v>6.295714584085927</v>
       </c>
       <c r="J46">
-        <v>0.03840340273559473</v>
+        <v>0.03840340273508602</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="M46">
-        <v>0.3531781092826729</v>
+        <v>0.3531781092717563</v>
       </c>
     </row>
     <row r="47">
@@ -2644,25 +2644,25 @@
         </is>
       </c>
       <c r="D47">
-        <v>6.848290622806104</v>
+        <v>6.848290622803901</v>
       </c>
       <c r="E47">
-        <v>5.441696710889639</v>
+        <v>5.441696710889643</v>
       </c>
       <c r="F47">
-        <v>-1.406593911916465</v>
+        <v>-1.406593911914258</v>
       </c>
       <c r="G47">
-        <v>-4.394451033880415</v>
+        <v>-4.394451034233184</v>
       </c>
       <c r="H47">
-        <v>1.581263210047484</v>
+        <v>1.581263210404667</v>
       </c>
       <c r="I47">
-        <v>-20.53934316444225</v>
+        <v>-20.53934316441663</v>
       </c>
       <c r="J47">
-        <v>0.2310162060949046</v>
+        <v>0.2310162061382826</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>0.7522300431538997</v>
+        <v>0.7522300431411013</v>
       </c>
     </row>
     <row r="48">
@@ -2693,25 +2693,25 @@
         </is>
       </c>
       <c r="D48">
-        <v>6.85296048599002</v>
+        <v>6.852960485995165</v>
       </c>
       <c r="E48">
-        <v>6.591158548346779</v>
+        <v>6.591158548346657</v>
       </c>
       <c r="F48">
-        <v>-0.2618019376432418</v>
+        <v>-0.2618019376485092</v>
       </c>
       <c r="G48">
-        <v>-3.110009627119845</v>
+        <v>-3.110009627259566</v>
       </c>
       <c r="H48">
-        <v>2.586405751833361</v>
+        <v>2.586405751962548</v>
       </c>
       <c r="I48">
-        <v>-3.820275020970303</v>
+        <v>-3.820275021044297</v>
       </c>
       <c r="J48">
-        <v>0.788950567247475</v>
+        <v>0.7889505672529816</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>0.9313837563336225</v>
+        <v>0.9313837563421024</v>
       </c>
     </row>
     <row r="49">
@@ -2742,25 +2742,25 @@
         </is>
       </c>
       <c r="D49">
-        <v>6.591660462000718</v>
+        <v>6.591660461972968</v>
       </c>
       <c r="E49">
-        <v>6.053370927575157</v>
+        <v>6.053370927566542</v>
       </c>
       <c r="F49">
-        <v>-0.5382895344255604</v>
+        <v>-0.5382895344064257</v>
       </c>
       <c r="G49">
-        <v>-2.462320888681475</v>
+        <v>-2.462320888977404</v>
       </c>
       <c r="H49">
-        <v>1.385741819830355</v>
+        <v>1.385741820164553</v>
       </c>
       <c r="I49">
-        <v>-8.166220598416219</v>
+        <v>-8.166220598160313</v>
       </c>
       <c r="J49">
-        <v>0.4388653682256807</v>
+        <v>0.4388653683072901</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>0.9997089461463154</v>
+        <v>0.9997089461462456</v>
       </c>
     </row>
     <row r="50">
@@ -2791,25 +2791,25 @@
         </is>
       </c>
       <c r="D50">
-        <v>6.591163326493771</v>
+        <v>6.591163326493835</v>
       </c>
       <c r="E50">
-        <v>6.437592986622431</v>
+        <v>6.437592986621416</v>
       </c>
       <c r="F50">
-        <v>-0.1535703398713409</v>
+        <v>-0.1535703398724186</v>
       </c>
       <c r="G50">
-        <v>-2.214573327777816</v>
+        <v>-2.214573327734982</v>
       </c>
       <c r="H50">
-        <v>1.907432648035134</v>
+        <v>1.907432647990145</v>
       </c>
       <c r="I50">
-        <v>-2.329942868416736</v>
+        <v>-2.329942868433063</v>
       </c>
       <c r="J50">
-        <v>0.8278253196050767</v>
+        <v>0.8278253196003207</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="M50">
-        <v>0.6219832346611236</v>
+        <v>0.6219832346644401</v>
       </c>
     </row>
     <row r="51">
@@ -2840,25 +2840,25 @@
         </is>
       </c>
       <c r="D51">
-        <v>6.59158001012565</v>
+        <v>6.59158001013266</v>
       </c>
       <c r="E51">
-        <v>6.242144985201877</v>
+        <v>6.242144985203292</v>
       </c>
       <c r="F51">
-        <v>-0.3494350249237726</v>
+        <v>-0.3494350249293684</v>
       </c>
       <c r="G51">
-        <v>-2.307944880871749</v>
+        <v>-2.307944880570919</v>
       </c>
       <c r="H51">
-        <v>1.609074831024204</v>
+        <v>1.609074830712182</v>
       </c>
       <c r="I51">
-        <v>-5.301233154827648</v>
+        <v>-5.301233154906902</v>
       </c>
       <c r="J51">
-        <v>0.6098816503173572</v>
+        <v>0.6098816502586638</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>0.5475309935857016</v>
+        <v>0.547530993451675</v>
       </c>
     </row>
     <row r="52">
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="D52">
-        <v>0.3153365870082135</v>
+        <v>0.315336587008214</v>
       </c>
       <c r="E52">
-        <v>0.3159451172153055</v>
+        <v>0.3159451172153056</v>
       </c>
       <c r="F52">
-        <v>0.0006085302070919936</v>
+        <v>0.000608530207091618</v>
       </c>
       <c r="G52">
-        <v>-0.002259796896710062</v>
+        <v>-0.002259796896350418</v>
       </c>
       <c r="H52">
-        <v>0.003476857310894049</v>
+        <v>0.003476857310533655</v>
       </c>
       <c r="I52">
-        <v>0.1929779899203841</v>
+        <v>0.1929779899202647</v>
       </c>
       <c r="J52">
-        <v>0.5479469244852728</v>
+        <v>0.5479469244385434</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>0.5518506953633422</v>
+        <v>0.5518506953782982</v>
       </c>
     </row>
     <row r="53">
@@ -2938,25 +2938,25 @@
         </is>
       </c>
       <c r="D53">
-        <v>0.3153355993269266</v>
+        <v>0.3153355993272437</v>
       </c>
       <c r="E53">
-        <v>0.3157231349448583</v>
+        <v>0.3157231349461231</v>
       </c>
       <c r="F53">
-        <v>0.0003875356179316792</v>
+        <v>0.0003875356188793529</v>
       </c>
       <c r="G53">
-        <v>-0.002617449196342826</v>
+        <v>-0.00261744930149703</v>
       </c>
       <c r="H53">
-        <v>0.003392520432206184</v>
+        <v>0.003392520539255736</v>
       </c>
       <c r="I53">
-        <v>0.1228962472866563</v>
+        <v>0.1228962475870612</v>
       </c>
       <c r="J53">
-        <v>0.7090485268710752</v>
+        <v>0.7090485357599001</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>0.3458447435348703</v>
+        <v>0.3458447272586079</v>
       </c>
     </row>
     <row r="54">
@@ -2987,25 +2987,25 @@
         </is>
       </c>
       <c r="D54">
-        <v>0.3157230535705683</v>
+        <v>0.3157230535705502</v>
       </c>
       <c r="E54">
-        <v>0.3154075004466768</v>
+        <v>0.3154075004466786</v>
       </c>
       <c r="F54">
-        <v>-0.0003155531238915595</v>
+        <v>-0.0003155531238716422</v>
       </c>
       <c r="G54">
-        <v>-0.00418345156918755</v>
+        <v>-0.004183451567311045</v>
       </c>
       <c r="H54">
-        <v>0.003552345321404431</v>
+        <v>0.003552345319567761</v>
       </c>
       <c r="I54">
-        <v>-0.09994617761449882</v>
+        <v>-0.09994617760819607</v>
       </c>
       <c r="J54">
-        <v>0.8119454255999564</v>
+        <v>0.8119454255237746</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="M54">
-        <v>0.04229615594091818</v>
+        <v>0.04229615597581859</v>
       </c>
     </row>
     <row r="55">
@@ -3036,25 +3036,25 @@
         </is>
       </c>
       <c r="D55">
-        <v>0.3157046821594313</v>
+        <v>0.3157046821594244</v>
       </c>
       <c r="E55">
-        <v>0.3162806761833875</v>
+        <v>0.3162806761833847</v>
       </c>
       <c r="F55">
-        <v>0.0005759940239561061</v>
+        <v>0.0005759940239603648</v>
       </c>
       <c r="G55">
-        <v>-0.001884972603359676</v>
+        <v>-0.001884972603326749</v>
       </c>
       <c r="H55">
-        <v>0.003036960651271888</v>
+        <v>0.003036960651247478</v>
       </c>
       <c r="I55">
-        <v>0.1824470958163453</v>
+        <v>0.1824470958176983</v>
       </c>
       <c r="J55">
-        <v>0.510401006251353</v>
+        <v>0.5104010062440915</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>0.9165832287037617</v>
+        <v>0.916583228695367</v>
       </c>
     </row>
     <row r="56">
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="D56">
-        <v>0.3157231357166116</v>
+        <v>0.3157231357166184</v>
       </c>
       <c r="E56">
-        <v>0.3151123796484233</v>
+        <v>0.3151123796484406</v>
       </c>
       <c r="F56">
-        <v>-0.0006107560681883037</v>
+        <v>-0.0006107560681777322</v>
       </c>
       <c r="G56">
-        <v>-0.004483032621541129</v>
+        <v>-0.004483032621473771</v>
       </c>
       <c r="H56">
-        <v>0.003261520485164522</v>
+        <v>0.003261520485118307</v>
       </c>
       <c r="I56">
-        <v>-0.1934467256579224</v>
+        <v>-0.1934467256545699</v>
       </c>
       <c r="J56">
-        <v>0.6502258100567</v>
+        <v>0.6502258100576246</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>0.5368706021608186</v>
+        <v>0.5368706021295284</v>
       </c>
     </row>
     <row r="57">
@@ -3134,25 +3134,25 @@
         </is>
       </c>
       <c r="D57">
-        <v>430.0425100089752</v>
+        <v>430.0425100089135</v>
       </c>
       <c r="E57">
-        <v>436.428524200925</v>
+        <v>436.4285242009247</v>
       </c>
       <c r="F57">
-        <v>6.38601419194977</v>
+        <v>6.386014192011181</v>
       </c>
       <c r="G57">
-        <v>-24.09820590410912</v>
+        <v>-24.09820589456557</v>
       </c>
       <c r="H57">
-        <v>36.87023428800866</v>
+        <v>36.87023427858793</v>
       </c>
       <c r="I57">
-        <v>1.484972774393045</v>
+        <v>1.484972774407539</v>
       </c>
       <c r="J57">
-        <v>0.5526682063523424</v>
+        <v>0.5526682062331189</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>0.9724332632352244</v>
+        <v>0.9724332632279405</v>
       </c>
     </row>
     <row r="58">
@@ -3183,25 +3183,25 @@
         </is>
       </c>
       <c r="D58">
-        <v>430.2111944878761</v>
+        <v>430.2111944878837</v>
       </c>
       <c r="E58">
-        <v>409.7197413723746</v>
+        <v>409.719741372384</v>
       </c>
       <c r="F58">
-        <v>-20.49145311550153</v>
+        <v>-20.49145311549982</v>
       </c>
       <c r="G58">
-        <v>-32.13771866327225</v>
+        <v>-32.13771866337567</v>
       </c>
       <c r="H58">
-        <v>-8.845187567730809</v>
+        <v>-8.845187567623974</v>
       </c>
       <c r="I58">
-        <v>-4.763114809203089</v>
+        <v>-4.763114809202607</v>
       </c>
       <c r="J58">
-        <v>0.01125339679424764</v>
+        <v>0.01125339679453341</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="M58">
-        <v>0.6943840068632192</v>
+        <v>0.6943840068664153</v>
       </c>
     </row>
     <row r="59">
@@ -3232,25 +3232,25 @@
         </is>
       </c>
       <c r="D59">
-        <v>409.6221705240998</v>
+        <v>409.622170524124</v>
       </c>
       <c r="E59">
-        <v>400.7567577842041</v>
+        <v>400.7567577842185</v>
       </c>
       <c r="F59">
-        <v>-8.865412739895726</v>
+        <v>-8.86541273990559</v>
       </c>
       <c r="G59">
-        <v>-22.96319691368175</v>
+        <v>-22.96319691387236</v>
       </c>
       <c r="H59">
-        <v>5.2323714338903</v>
+        <v>5.232371434061177</v>
       </c>
       <c r="I59">
-        <v>-2.164290260107915</v>
+        <v>-2.164290260110195</v>
       </c>
       <c r="J59">
-        <v>0.1391524428721533</v>
+        <v>0.1391524428753107</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>0.981373034243701</v>
+        <v>0.9813730342446082</v>
       </c>
     </row>
     <row r="60">
@@ -3281,25 +3281,25 @@
         </is>
       </c>
       <c r="D60">
-        <v>409.6276692313696</v>
+        <v>409.627669231335</v>
       </c>
       <c r="E60">
-        <v>397.4039510399183</v>
+        <v>397.4039510398969</v>
       </c>
       <c r="F60">
-        <v>-12.22371819145127</v>
+        <v>-12.2237181914381</v>
       </c>
       <c r="G60">
-        <v>-25.78168135422173</v>
+        <v>-25.78168135415108</v>
       </c>
       <c r="H60">
-        <v>1.334244971319192</v>
+        <v>1.33424497127487</v>
       </c>
       <c r="I60">
-        <v>-2.984104617343844</v>
+        <v>-2.984104617340882</v>
       </c>
       <c r="J60">
-        <v>0.06408908599892915</v>
+        <v>0.06408908599845142</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>0.8915837031122363</v>
+        <v>0.8915837031056246</v>
       </c>
     </row>
     <row r="61">
@@ -3330,25 +3330,25 @@
         </is>
       </c>
       <c r="D61">
-        <v>409.6140990578638</v>
+        <v>409.6140990578524</v>
       </c>
       <c r="E61">
-        <v>390.5933372272714</v>
+        <v>390.593337227264</v>
       </c>
       <c r="F61">
-        <v>-19.02076183059244</v>
+        <v>-19.02076183058843</v>
       </c>
       <c r="G61">
-        <v>-32.06255878504451</v>
+        <v>-32.06255878500485</v>
       </c>
       <c r="H61">
-        <v>-5.978964876140372</v>
+        <v>-5.978964876172014</v>
       </c>
       <c r="I61">
-        <v>-4.643580842149062</v>
+        <v>-4.643580842148212</v>
       </c>
       <c r="J61">
-        <v>0.0188502051065631</v>
+        <v>0.01885020510643454</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="M61">
-        <v>0.2323660201964053</v>
+        <v>0.2323660201923865</v>
       </c>
     </row>
     <row r="62">
@@ -3379,25 +3379,25 @@
         </is>
       </c>
       <c r="D62">
-        <v>1.948222356401741</v>
+        <v>1.948222356401677</v>
       </c>
       <c r="E62">
-        <v>1.952893290192556</v>
+        <v>1.952893290192558</v>
       </c>
       <c r="F62">
-        <v>0.004670933790814945</v>
+        <v>0.004670933790880949</v>
       </c>
       <c r="G62">
-        <v>-0.006759380155719816</v>
+        <v>-0.006759380155280606</v>
       </c>
       <c r="H62">
-        <v>0.01610124773734971</v>
+        <v>0.0161012477370425</v>
       </c>
       <c r="I62">
-        <v>0.2397536285048028</v>
+        <v>0.2397536285081986</v>
       </c>
       <c r="J62">
-        <v>0.2843205093377064</v>
+        <v>0.2843205093194051</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="M62">
-        <v>0.9983910750317936</v>
+        <v>0.9983910750305389</v>
       </c>
     </row>
     <row r="63">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="D63">
-        <v>1.948268149331444</v>
+        <v>1.948268149331924</v>
       </c>
       <c r="E63">
-        <v>1.943024357262547</v>
+        <v>1.943024357263128</v>
       </c>
       <c r="F63">
-        <v>-0.005243792068897846</v>
+        <v>-0.00524379206879628</v>
       </c>
       <c r="G63">
-        <v>-0.0178253114224194</v>
+        <v>-0.01782531154857997</v>
       </c>
       <c r="H63">
-        <v>0.007337727284623705</v>
+        <v>0.007337727410987411</v>
       </c>
       <c r="I63">
-        <v>-0.2691514548804421</v>
+        <v>-0.2691514548751626</v>
       </c>
       <c r="J63">
-        <v>0.2766432049024888</v>
+        <v>0.2766432087978002</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="M63">
-        <v>0.9936804683851606</v>
+        <v>0.9936804682547112</v>
       </c>
     </row>
     <row r="64">
@@ -3477,25 +3477,25 @@
         </is>
       </c>
       <c r="D64">
-        <v>1.943039652383848</v>
+        <v>1.943039652383867</v>
       </c>
       <c r="E64">
-        <v>1.941265305603689</v>
+        <v>1.941265305603797</v>
       </c>
       <c r="F64">
-        <v>-0.001774346780159246</v>
+        <v>-0.00177434678006975</v>
       </c>
       <c r="G64">
-        <v>-0.01558402601079689</v>
+        <v>-0.01558402602800314</v>
       </c>
       <c r="H64">
-        <v>0.01203533245047839</v>
+        <v>0.01203533246786364</v>
       </c>
       <c r="I64">
-        <v>-0.09131809420267679</v>
+        <v>-0.09131809419806994</v>
       </c>
       <c r="J64">
-        <v>0.7100525161946403</v>
+        <v>0.7100525165459641</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>0.9999468365282022</v>
+        <v>0.99994683652827</v>
       </c>
     </row>
     <row r="65">
@@ -3526,25 +3526,25 @@
         </is>
       </c>
       <c r="D65">
-        <v>1.943056409485904</v>
+        <v>1.943056409485883</v>
       </c>
       <c r="E65">
-        <v>1.939257543721848</v>
+        <v>1.939257543721702</v>
       </c>
       <c r="F65">
-        <v>-0.003798865764056357</v>
+        <v>-0.003798865764180969</v>
       </c>
       <c r="G65">
-        <v>-0.01615204767195703</v>
+        <v>-0.0161520476632651</v>
       </c>
       <c r="H65">
-        <v>0.008554316143844314</v>
+        <v>0.008554316134903159</v>
       </c>
       <c r="I65">
-        <v>-0.1955098032929196</v>
+        <v>-0.1955098032993349</v>
       </c>
       <c r="J65">
-        <v>0.3999165719756286</v>
+        <v>0.3999165716671191</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <v>0.9991148718578572</v>
+        <v>0.999114871858075</v>
       </c>
     </row>
     <row r="66">
@@ -3575,25 +3575,25 @@
         </is>
       </c>
       <c r="D66">
-        <v>1.943043816760048</v>
+        <v>1.943043816759888</v>
       </c>
       <c r="E66">
-        <v>1.936367353769539</v>
+        <v>1.936367353770543</v>
       </c>
       <c r="F66">
-        <v>-0.006676462990508372</v>
+        <v>-0.006676462989344632</v>
       </c>
       <c r="G66">
-        <v>-0.01991462522906009</v>
+        <v>-0.01991462524686022</v>
       </c>
       <c r="H66">
-        <v>0.006561699248043343</v>
+        <v>0.006561699268170957</v>
       </c>
       <c r="I66">
-        <v>-0.3436084628107421</v>
+        <v>-0.3436084627508776</v>
       </c>
       <c r="J66">
-        <v>0.2068339959552066</v>
+        <v>0.2068339965039547</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>0.9861669451483582</v>
+        <v>0.9861669451029793</v>
       </c>
     </row>
     <row r="67">
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="D67">
-        <v>2.771264664201397</v>
+        <v>2.771264664201385</v>
       </c>
       <c r="E67">
-        <v>2.629540280219728</v>
+        <v>2.629540280219723</v>
       </c>
       <c r="F67">
-        <v>-0.1417243839816695</v>
+        <v>-0.1417243839816619</v>
       </c>
       <c r="G67">
-        <v>-0.2689250409919897</v>
+        <v>-0.2689250409920134</v>
       </c>
       <c r="H67">
-        <v>-0.0145237269713494</v>
+        <v>-0.01452372697131044</v>
       </c>
       <c r="I67">
-        <v>-5.114068887480677</v>
+        <v>-5.114068887480426</v>
       </c>
       <c r="J67">
-        <v>0.03820459707087376</v>
+        <v>0.03820459707090262</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="M67">
-        <v>0.9915086422509133</v>
+        <v>0.9915086422509709</v>
       </c>
     </row>
     <row r="68">
@@ -3673,25 +3673,25 @@
         </is>
       </c>
       <c r="D68">
-        <v>2.771225627884647</v>
+        <v>2.771225627884546</v>
       </c>
       <c r="E68">
-        <v>2.841602092123697</v>
+        <v>2.841602092123555</v>
       </c>
       <c r="F68">
-        <v>0.07037646423904924</v>
+        <v>0.07037646423900969</v>
       </c>
       <c r="G68">
-        <v>-0.06469419082771628</v>
+        <v>-0.06469419082836662</v>
       </c>
       <c r="H68">
-        <v>0.2054471193058148</v>
+        <v>0.205447119306386</v>
       </c>
       <c r="I68">
-        <v>2.539542920320405</v>
+        <v>2.53954292031907</v>
       </c>
       <c r="J68">
-        <v>0.1958647064789756</v>
+        <v>0.1958647064806621</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>0.9736762231780339</v>
+        <v>0.9736762231794301</v>
       </c>
     </row>
     <row r="69">
@@ -3722,25 +3722,25 @@
         </is>
       </c>
       <c r="D69">
-        <v>2.839335005286982</v>
+        <v>2.839335005286892</v>
       </c>
       <c r="E69">
-        <v>2.867045763636906</v>
+        <v>2.86704576363682</v>
       </c>
       <c r="F69">
-        <v>0.02771075834992368</v>
+        <v>0.0277107583499275</v>
       </c>
       <c r="G69">
-        <v>-0.1400966209670282</v>
+        <v>-0.1400966209661139</v>
       </c>
       <c r="H69">
-        <v>0.1955181376668756</v>
+        <v>0.1955181376659689</v>
       </c>
       <c r="I69">
-        <v>0.9759594517140415</v>
+        <v>0.9759594517142067</v>
       </c>
       <c r="J69">
-        <v>0.6355829920326592</v>
+        <v>0.6355829920308547</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>0.9919686581441736</v>
+        <v>0.991968658144788</v>
       </c>
     </row>
     <row r="70">
@@ -3771,25 +3771,25 @@
         </is>
       </c>
       <c r="D70">
-        <v>2.840525949985915</v>
+        <v>2.840525949986456</v>
       </c>
       <c r="E70">
-        <v>2.843171654728137</v>
+        <v>2.843171654728482</v>
       </c>
       <c r="F70">
-        <v>0.002645704742222092</v>
+        <v>0.002645704742025528</v>
       </c>
       <c r="G70">
-        <v>-0.1542310661456565</v>
+        <v>-0.1542310661446231</v>
       </c>
       <c r="H70">
-        <v>0.1595224756301006</v>
+        <v>0.1595224756286741</v>
       </c>
       <c r="I70">
-        <v>0.09314136849322609</v>
+        <v>0.09314136848628836</v>
       </c>
       <c r="J70">
-        <v>0.9605710281647692</v>
+        <v>0.9605710281673863</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="M70">
-        <v>0.9581093717078429</v>
+        <v>0.95810937170445</v>
       </c>
     </row>
     <row r="71">
@@ -3820,25 +3820,25 @@
         </is>
       </c>
       <c r="D71">
-        <v>2.841758573885818</v>
+        <v>2.841758573884985</v>
       </c>
       <c r="E71">
-        <v>2.926898197668097</v>
+        <v>2.926898197667955</v>
       </c>
       <c r="F71">
-        <v>0.08513962378227811</v>
+        <v>0.08513962378297039</v>
       </c>
       <c r="G71">
-        <v>-0.06758891865166418</v>
+        <v>-0.06758891865277016</v>
       </c>
       <c r="H71">
-        <v>0.2378681662162204</v>
+        <v>0.2378681662187109</v>
       </c>
       <c r="I71">
-        <v>2.996018893535289</v>
+        <v>2.996018893560529</v>
       </c>
       <c r="J71">
-        <v>0.1741509923544055</v>
+        <v>0.1741509923555374</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="M71">
-        <v>0.7951163346153158</v>
+        <v>0.7951163346389026</v>
       </c>
     </row>
     <row r="72">
@@ -3869,25 +3869,25 @@
         </is>
       </c>
       <c r="D72">
-        <v>5.582817420022018</v>
+        <v>5.582817420021843</v>
       </c>
       <c r="E72">
-        <v>5.692826753212736</v>
+        <v>5.692826753212589</v>
       </c>
       <c r="F72">
-        <v>0.1100093331907174</v>
+        <v>0.1100093331907465</v>
       </c>
       <c r="G72">
-        <v>-0.9780751178146107</v>
+        <v>-0.9780751177704347</v>
       </c>
       <c r="H72">
-        <v>1.198093784196046</v>
+        <v>1.198093784151928</v>
       </c>
       <c r="I72">
-        <v>1.970498494114886</v>
+        <v>1.970498494115469</v>
       </c>
       <c r="J72">
-        <v>0.7687526528055507</v>
+        <v>0.7687526527965265</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>0.99969527353034</v>
+        <v>0.9996952735303613</v>
       </c>
     </row>
     <row r="73">
@@ -3918,25 +3918,25 @@
         </is>
       </c>
       <c r="D73">
-        <v>5.583867041106891</v>
+        <v>5.583867041105841</v>
       </c>
       <c r="E73">
-        <v>5.525482094822082</v>
+        <v>5.525482094818368</v>
       </c>
       <c r="F73">
-        <v>-0.05838494628480872</v>
+        <v>-0.05838494628747413</v>
       </c>
       <c r="G73">
-        <v>-1.071976348294252</v>
+        <v>-1.071976348304141</v>
       </c>
       <c r="H73">
-        <v>0.9552064557246343</v>
+        <v>0.9552064557291924</v>
       </c>
       <c r="I73">
-        <v>-1.045600582087554</v>
+        <v>-1.045600582135485</v>
       </c>
       <c r="J73">
-        <v>0.866240143403847</v>
+        <v>0.8662401433987721</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>0.9984314835720902</v>
+        <v>0.9984314835722887</v>
       </c>
     </row>
     <row r="74">
@@ -3967,25 +3967,25 @@
         </is>
       </c>
       <c r="D74">
-        <v>5.523315766741651</v>
+        <v>5.523315766740235</v>
       </c>
       <c r="E74">
-        <v>5.714420479699132</v>
+        <v>5.714420479698197</v>
       </c>
       <c r="F74">
-        <v>0.1911047129574807</v>
+        <v>0.1911047129579628</v>
       </c>
       <c r="G74">
-        <v>-1.270378004672956</v>
+        <v>-1.2703780046271</v>
       </c>
       <c r="H74">
-        <v>1.652587430587918</v>
+        <v>1.652587430543026</v>
       </c>
       <c r="I74">
-        <v>3.459963562253809</v>
+        <v>3.459963562263425</v>
       </c>
       <c r="J74">
-        <v>0.7052861346182906</v>
+        <v>0.7052861346091143</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>0.6633184133242938</v>
+        <v>0.663318413328859</v>
       </c>
     </row>
     <row r="75">
@@ -4016,25 +4016,25 @@
         </is>
       </c>
       <c r="D75">
-        <v>5.522953577646966</v>
+        <v>5.522953577512842</v>
       </c>
       <c r="E75">
-        <v>5.840061574013717</v>
+        <v>5.840061574115506</v>
       </c>
       <c r="F75">
-        <v>0.3171079963667504</v>
+        <v>0.3171079966026632</v>
       </c>
       <c r="G75">
-        <v>-0.9300653448399058</v>
+        <v>-0.9300653389647285</v>
       </c>
       <c r="H75">
-        <v>1.564281337573406</v>
+        <v>1.564281332170055</v>
       </c>
       <c r="I75">
-        <v>5.741637910015768</v>
+        <v>5.7416379144267</v>
       </c>
       <c r="J75">
-        <v>0.477636974852492</v>
+        <v>0.4776369727421054</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>0.8622167179367171</v>
+        <v>0.8622167181625052</v>
       </c>
     </row>
     <row r="76">
@@ -4065,25 +4065,25 @@
         </is>
       </c>
       <c r="D76">
-        <v>5.525669808318205</v>
+        <v>5.525669808315548</v>
       </c>
       <c r="E76">
-        <v>5.644751024458977</v>
+        <v>5.644751024459976</v>
       </c>
       <c r="F76">
-        <v>0.1190812161407718</v>
+        <v>0.1190812161444288</v>
       </c>
       <c r="G76">
-        <v>-1.153161458447812</v>
+        <v>-1.153161458305643</v>
       </c>
       <c r="H76">
-        <v>1.391323890729356</v>
+        <v>1.3913238905945</v>
       </c>
       <c r="I76">
-        <v>2.155054867040914</v>
+        <v>2.155054867108133</v>
       </c>
       <c r="J76">
-        <v>0.7852361682214175</v>
+        <v>0.7852361681925821</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="M76">
-        <v>0.7873021624975396</v>
+        <v>0.7873021625055505</v>
       </c>
     </row>
   </sheetData>
@@ -4110,7 +4110,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -4254,37 +4254,37 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.3190629929315108</v>
+        <v>0.3190629929315109</v>
       </c>
       <c r="H2">
-        <v>0.3206914106929254</v>
+        <v>0.3206914106929256</v>
       </c>
       <c r="I2">
-        <v>0.001628417761414654</v>
+        <v>0.00162841776141463</v>
       </c>
       <c r="J2">
-        <v>0.001234216092784771</v>
+        <v>0.001234216092627639</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>-0.002299408682989934</v>
+        <v>-0.002299408682489893</v>
       </c>
       <c r="M2">
-        <v>0.005556244205819243</v>
+        <v>0.005556244205319152</v>
       </c>
       <c r="N2">
-        <v>0.5103750035229583</v>
+        <v>0.5103750035229504</v>
       </c>
       <c r="O2">
-        <v>0.2786964623956125</v>
+        <v>0.2786964623461505</v>
       </c>
       <c r="P2">
-        <v>0.04216774239141552</v>
+        <v>0.04216774238543708</v>
       </c>
       <c r="Q2">
-        <v>0.483487909311432</v>
+        <v>0.4834879092884048</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -4295,16 +4295,16 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0.003422727659134562</v>
+        <v>0.003422727660973646</v>
       </c>
       <c r="U2">
-        <v>0.001309372421490973</v>
+        <v>0.001309372421206919</v>
       </c>
       <c r="V2">
-        <v>0.004470105008661937</v>
+        <v>0.004470105008608635</v>
       </c>
       <c r="W2">
-        <v>0.00154261536326599</v>
+        <v>0.001542598725996101</v>
       </c>
     </row>
     <row r="3">
@@ -4337,37 +4337,37 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>0.3190628451357969</v>
+        <v>0.3190628451357968</v>
       </c>
       <c r="H3">
-        <v>0.3176096175964228</v>
+        <v>0.3176096175964226</v>
       </c>
       <c r="I3">
-        <v>-0.001453227539374118</v>
+        <v>-0.001453227539374158</v>
       </c>
       <c r="J3">
-        <v>0.0008586781240958888</v>
+        <v>0.0008586781242477076</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>-0.004185924562831025</v>
+        <v>-0.00418592456331422</v>
       </c>
       <c r="M3">
-        <v>0.001279469484082789</v>
+        <v>0.001279469484565903</v>
       </c>
       <c r="N3">
-        <v>-0.4554674922288764</v>
+        <v>-0.4554674922288893</v>
       </c>
       <c r="O3">
-        <v>0.1891462213993942</v>
+        <v>0.1891462214569604</v>
       </c>
       <c r="P3">
-        <v>0.2743740238249447</v>
+        <v>0.2743740238672312</v>
       </c>
       <c r="Q3">
-        <v>0.4911506851247366</v>
+        <v>0.4911506851626125</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -4378,16 +4378,16 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0.001814376685429088</v>
+        <v>0.001814376683462574</v>
       </c>
       <c r="U3">
-        <v>3.040157107948689E-07</v>
+        <v>3.044557092772668E-07</v>
       </c>
       <c r="V3">
-        <v>0.004374840810095642</v>
+        <v>0.004374840810243658</v>
       </c>
       <c r="W3">
-        <v>0.4866654510972472</v>
+        <v>0.4866654511999496</v>
       </c>
     </row>
     <row r="4">
@@ -4420,37 +4420,37 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0.3176092318311068</v>
+        <v>0.3176092318311073</v>
       </c>
       <c r="H4">
-        <v>0.3178343161300918</v>
+        <v>0.3178343161300924</v>
       </c>
       <c r="I4">
-        <v>0.0002250842989849678</v>
+        <v>0.0002250842989850668</v>
       </c>
       <c r="J4">
-        <v>0.001022999325596068</v>
+        <v>0.00102299932544593</v>
       </c>
       <c r="K4">
         <v>3</v>
       </c>
       <c r="L4">
-        <v>-0.003030556125065962</v>
+        <v>-0.00303055612458806</v>
       </c>
       <c r="M4">
-        <v>0.003480724723035898</v>
+        <v>0.003480724722558193</v>
       </c>
       <c r="N4">
-        <v>0.07086831125383017</v>
+        <v>0.0708683112538612</v>
       </c>
       <c r="O4">
-        <v>0.8399743913823063</v>
+        <v>0.8399743913592389</v>
       </c>
       <c r="P4">
-        <v>0.1703001167345637</v>
+        <v>0.1703001167107493</v>
       </c>
       <c r="Q4">
-        <v>0.8252510356402808</v>
+        <v>0.825251035653417</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -4461,16 +4461,16 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>0.0009427803440979522</v>
+        <v>0.0009427803450924147</v>
       </c>
       <c r="U4">
-        <v>2.135406524573204E-07</v>
+        <v>2.135423372936149E-07</v>
       </c>
       <c r="V4">
-        <v>0.004472154437490381</v>
+        <v>0.004472154437293908</v>
       </c>
       <c r="W4">
-        <v>0.6722599636335737</v>
+        <v>0.6722599635497423</v>
       </c>
     </row>
     <row r="5">
@@ -4503,37 +4503,37 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.3176091753203836</v>
+        <v>0.3176091753203997</v>
       </c>
       <c r="H5">
-        <v>0.3185644779284539</v>
+        <v>0.3185644779285982</v>
       </c>
       <c r="I5">
-        <v>0.0009553026080703374</v>
+        <v>0.0009553026081983861</v>
       </c>
       <c r="J5">
-        <v>0.001151378844352095</v>
+        <v>0.001151378838601845</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>-0.002708898741119811</v>
+        <v>-0.002708898722691901</v>
       </c>
       <c r="M5">
-        <v>0.004619503957260486</v>
+        <v>0.004619503939088674</v>
       </c>
       <c r="N5">
-        <v>0.300779285455683</v>
+        <v>0.3007792854959842</v>
       </c>
       <c r="O5">
-        <v>0.4675607228752174</v>
+        <v>0.4675607208059289</v>
       </c>
       <c r="P5">
-        <v>0.199738181110695</v>
+        <v>0.199738178848319</v>
       </c>
       <c r="Q5">
-        <v>0.4734218050828248</v>
+        <v>0.4734218038422473</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -4544,16 +4544,16 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0.001071377489469727</v>
+        <v>0.001071377587647318</v>
       </c>
       <c r="U5">
-        <v>2.112574426014252E-07</v>
+        <v>2.117985653013393E-07</v>
       </c>
       <c r="V5">
-        <v>0.004762396861113817</v>
+        <v>0.004762396849982416</v>
       </c>
       <c r="W5">
-        <v>0.7114450128856332</v>
+        <v>0.7114450110293856</v>
       </c>
     </row>
     <row r="6">
@@ -4586,37 +4586,37 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0.3176092357716369</v>
+        <v>0.3176092357715212</v>
       </c>
       <c r="H6">
-        <v>0.3180293554077357</v>
+        <v>0.3180293554112534</v>
       </c>
       <c r="I6">
-        <v>0.0004201196360987412</v>
+        <v>0.0004201196397321896</v>
       </c>
       <c r="J6">
-        <v>0.0009726563910850475</v>
+        <v>0.000972656382077265</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
-        <v>-0.002675307102020453</v>
+        <v>-0.002675307069720221</v>
       </c>
       <c r="M6">
-        <v>0.003515546374217935</v>
+        <v>0.0035155463491846</v>
       </c>
       <c r="N6">
-        <v>0.1322756358385025</v>
+        <v>0.1322756369825503</v>
       </c>
       <c r="O6">
-        <v>0.6949539694890001</v>
+        <v>0.6949539644488112</v>
       </c>
       <c r="P6">
-        <v>0.03766431162456851</v>
+        <v>0.03766431836403239</v>
       </c>
       <c r="Q6">
-        <v>0.4355566206638333</v>
+        <v>0.4355566929311028</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -4627,16 +4627,16 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0.0004635381884356442</v>
+        <v>0.0004635366584902323</v>
       </c>
       <c r="U6">
-        <v>4.124506129842607E-07</v>
+        <v>4.163919606032297E-07</v>
       </c>
       <c r="V6">
-        <v>0.004410094442907383</v>
+        <v>0.004410094511171526</v>
       </c>
       <c r="W6">
-        <v>0.6370247194732073</v>
+        <v>0.6370246948414546</v>
       </c>
     </row>
     <row r="7">
@@ -4669,37 +4669,37 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>439.9038217031746</v>
+        <v>439.9038217031748</v>
       </c>
       <c r="H7">
-        <v>422.2294087534438</v>
+        <v>422.229408753444</v>
       </c>
       <c r="I7">
-        <v>-17.67441294973088</v>
+        <v>-17.67441294973086</v>
       </c>
       <c r="J7">
-        <v>6.501052739889181</v>
+        <v>6.501052739992676</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>-38.36366422224572</v>
+        <v>-38.36366422257507</v>
       </c>
       <c r="M7">
-        <v>3.014838322783973</v>
+        <v>3.014838323113359</v>
       </c>
       <c r="N7">
-        <v>-4.017790270905329</v>
+        <v>-4.017790270905324</v>
       </c>
       <c r="O7">
-        <v>0.07262898000717133</v>
+        <v>0.07262898000982476</v>
       </c>
       <c r="P7">
-        <v>8.036492106677784E-06</v>
+        <v>8.036492108010052E-06</v>
       </c>
       <c r="Q7">
-        <v>0.9889160873094436</v>
+        <v>0.9889160873100195</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>21.27219037516358</v>
+        <v>21.27219037150927</v>
       </c>
       <c r="U7">
-        <v>0.002196418604770477</v>
+        <v>0.002196826223954745</v>
       </c>
       <c r="V7">
-        <v>28.69535233359801</v>
+        <v>28.69535233375088</v>
       </c>
       <c r="W7">
         <v>0.6643814892471324</v>
@@ -4752,37 +4752,37 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>439.9024129871331</v>
+        <v>439.9024129871332</v>
       </c>
       <c r="H8">
-        <v>429.8342967628467</v>
+        <v>429.8342967628469</v>
       </c>
       <c r="I8">
-        <v>-10.0681162242864</v>
+        <v>-10.06811622428629</v>
       </c>
       <c r="J8">
-        <v>9.442376138125603</v>
+        <v>9.442376138494339</v>
       </c>
       <c r="K8">
         <v>3</v>
       </c>
       <c r="L8">
-        <v>-40.11797127816327</v>
+        <v>-40.11797127933664</v>
       </c>
       <c r="M8">
-        <v>19.98173882959047</v>
+        <v>19.98173883076407</v>
       </c>
       <c r="N8">
-        <v>-2.288715844025363</v>
+        <v>-2.288715844025337</v>
       </c>
       <c r="O8">
-        <v>0.364497525864669</v>
+        <v>0.3644975258807731</v>
       </c>
       <c r="P8">
-        <v>9.870648038923235E-07</v>
+        <v>9.870648043364127E-07</v>
       </c>
       <c r="Q8">
-        <v>0.8708491495462888</v>
+        <v>0.8708491495458119</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4793,16 +4793,16 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>17.84068338226912</v>
+        <v>17.84068337721665</v>
       </c>
       <c r="U8">
-        <v>0.003898196634964848</v>
+        <v>0.003898200315043696</v>
       </c>
       <c r="V8">
-        <v>31.45176072104691</v>
+        <v>31.45176072163853</v>
       </c>
       <c r="W8">
-        <v>0.8242362576284475</v>
+        <v>0.824236257636354</v>
       </c>
     </row>
     <row r="9">
@@ -4835,37 +4835,37 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>429.8313277409171</v>
+        <v>429.8313277409174</v>
       </c>
       <c r="H9">
-        <v>423.5415849952277</v>
+        <v>423.541584995228</v>
       </c>
       <c r="I9">
-        <v>-6.289742745689387</v>
+        <v>-6.289742745689423</v>
       </c>
       <c r="J9">
-        <v>3.877311146062791</v>
+        <v>3.877311146098841</v>
       </c>
       <c r="K9">
         <v>3</v>
       </c>
       <c r="L9">
-        <v>-18.62907727691226</v>
+        <v>-18.62907727702702</v>
       </c>
       <c r="M9">
-        <v>6.04959178553348</v>
+        <v>6.04959178564817</v>
       </c>
       <c r="N9">
-        <v>-1.463304868620595</v>
+        <v>-1.463304868620602</v>
       </c>
       <c r="O9">
-        <v>0.2032155511127371</v>
+        <v>0.2032155511158824</v>
       </c>
       <c r="P9">
         <v>2.844391389089651E-13</v>
       </c>
       <c r="Q9">
-        <v>0.9997166154524799</v>
+        <v>0.999716615452511</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -4876,16 +4876,16 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>8.731587626132567</v>
+        <v>8.73158762328424</v>
       </c>
       <c r="U9">
-        <v>0.001059617915883422</v>
+        <v>0.001059616580743435</v>
       </c>
       <c r="V9">
-        <v>21.23690737510728</v>
+        <v>21.23690737530573</v>
       </c>
       <c r="W9">
-        <v>0.0001360144895295659</v>
+        <v>0.0001360065020195579</v>
       </c>
     </row>
     <row r="10">
@@ -4918,37 +4918,37 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>429.8315844705174</v>
+        <v>429.8315844705177</v>
       </c>
       <c r="H10">
-        <v>417.9183058987444</v>
+        <v>417.9183058985104</v>
       </c>
       <c r="I10">
-        <v>-11.91327857177308</v>
+        <v>-11.91327857200735</v>
       </c>
       <c r="J10">
-        <v>5.057454611725607</v>
+        <v>5.057454613253901</v>
       </c>
       <c r="K10">
         <v>3</v>
       </c>
       <c r="L10">
-        <v>-28.00835631499929</v>
+        <v>-28.00835632009727</v>
       </c>
       <c r="M10">
-        <v>4.181799171453122</v>
+        <v>4.181799176082567</v>
       </c>
       <c r="N10">
-        <v>-2.771615442464124</v>
+        <v>-2.771615442518624</v>
       </c>
       <c r="O10">
-        <v>0.09979838249743689</v>
+        <v>0.09979838255768392</v>
       </c>
       <c r="P10">
         <v>2.646438623798986E-12</v>
       </c>
       <c r="Q10">
-        <v>0.9954420644573392</v>
+        <v>0.9954420644577676</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>8.83395132953264</v>
+        <v>8.833951335290674</v>
       </c>
       <c r="U10">
-        <v>0.002581849534625439</v>
+        <v>0.002581773914008793</v>
       </c>
       <c r="V10">
-        <v>22.64631558095153</v>
+        <v>22.64631558202587</v>
       </c>
       <c r="W10">
-        <v>0.6487351293063918</v>
+        <v>0.6487351295428624</v>
       </c>
     </row>
     <row r="11">
@@ -5001,37 +5001,37 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>429.831509689801</v>
+        <v>429.8315096897875</v>
       </c>
       <c r="H11">
-        <v>415.0544834001441</v>
+        <v>415.0544834054531</v>
       </c>
       <c r="I11">
-        <v>-14.77702628965686</v>
+        <v>-14.77702628433436</v>
       </c>
       <c r="J11">
-        <v>5.603370499445162</v>
+        <v>5.603370477433701</v>
       </c>
       <c r="K11">
         <v>3</v>
       </c>
       <c r="L11">
-        <v>-32.60945203275184</v>
+        <v>-32.60945195737904</v>
       </c>
       <c r="M11">
-        <v>3.05539945343812</v>
+        <v>3.055399388710329</v>
       </c>
       <c r="N11">
-        <v>-3.43786482762073</v>
+        <v>-3.437864826382561</v>
       </c>
       <c r="O11">
-        <v>0.07784478214197299</v>
+        <v>0.07784478151375762</v>
       </c>
       <c r="P11">
         <v>3.610667320685934E-12</v>
       </c>
       <c r="Q11">
-        <v>0.9952212449517688</v>
+        <v>0.9952212450447355</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -5042,16 +5042,16 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>5.889483571091525</v>
+        <v>5.889483408377254</v>
       </c>
       <c r="U11">
-        <v>4.652425908048239</v>
+        <v>4.652426021855286</v>
       </c>
       <c r="V11">
-        <v>22.47827464573599</v>
+        <v>22.47827459127926</v>
       </c>
       <c r="W11">
-        <v>0.52752927257779</v>
+        <v>0.5275292459860681</v>
       </c>
     </row>
     <row r="12">
@@ -5084,37 +5084,37 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>1.981685256768667</v>
+        <v>1.981685256768479</v>
       </c>
       <c r="H12">
-        <v>1.963191854770508</v>
+        <v>1.963191854770372</v>
       </c>
       <c r="I12">
-        <v>-0.01849340199815907</v>
+        <v>-0.01849340199810703</v>
       </c>
       <c r="J12">
-        <v>0.0104198912659065</v>
+        <v>0.01041989126231031</v>
       </c>
       <c r="K12">
         <v>3</v>
       </c>
       <c r="L12">
-        <v>-0.0516541464588012</v>
+        <v>-0.05165414644730448</v>
       </c>
       <c r="M12">
-        <v>0.01466734246248306</v>
+        <v>0.01466734245109041</v>
       </c>
       <c r="N12">
-        <v>-0.9332159047453573</v>
+        <v>-0.9332159047428198</v>
       </c>
       <c r="O12">
-        <v>0.1740215630764897</v>
+        <v>0.174021562970222</v>
       </c>
       <c r="P12">
-        <v>0.2117555391119873</v>
+        <v>0.2117555388874715</v>
       </c>
       <c r="Q12">
-        <v>0.4613569056695641</v>
+        <v>0.4613569056096266</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -5125,16 +5125,16 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0.01238757523937283</v>
+        <v>0.0123875752442685</v>
       </c>
       <c r="U12">
-        <v>3.005247290810374E-06</v>
+        <v>3.004756511691673E-06</v>
       </c>
       <c r="V12">
-        <v>0.05699224802316458</v>
+        <v>0.05699224802231811</v>
       </c>
       <c r="W12">
-        <v>0.1458365797199489</v>
+        <v>0.145836569111762</v>
       </c>
     </row>
     <row r="13">
@@ -5167,37 +5167,37 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1.981684675825245</v>
+        <v>1.981684675825401</v>
       </c>
       <c r="H13">
-        <v>1.965651069444255</v>
+        <v>1.96565106944436</v>
       </c>
       <c r="I13">
-        <v>-0.01603360638098994</v>
+        <v>-0.01603360638104076</v>
       </c>
       <c r="J13">
-        <v>0.0107960429867019</v>
+        <v>0.01079604298913722</v>
       </c>
       <c r="K13">
         <v>3</v>
       </c>
       <c r="L13">
-        <v>-0.05039143349570349</v>
+        <v>-0.05039143350350458</v>
       </c>
       <c r="M13">
-        <v>0.01832422073372362</v>
+        <v>0.01832422074142305</v>
       </c>
       <c r="N13">
-        <v>-0.8090896890199226</v>
+        <v>-0.8090896890224238</v>
       </c>
       <c r="O13">
-        <v>0.23418187483169</v>
+        <v>0.234181874912321</v>
       </c>
       <c r="P13">
-        <v>0.01118395161900354</v>
+        <v>0.01118395163182817</v>
       </c>
       <c r="Q13">
-        <v>0.9977664570314975</v>
+        <v>0.9977664570309991</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -5208,16 +5208,16 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0.01369726947006115</v>
+        <v>0.01369726946739424</v>
       </c>
       <c r="U13">
-        <v>5.687994119428557E-06</v>
+        <v>5.688290709761192E-06</v>
       </c>
       <c r="V13">
-        <v>0.05910306897375561</v>
+        <v>0.05910306897425976</v>
       </c>
       <c r="W13">
-        <v>0.1048045832867494</v>
+        <v>0.1048045974279482</v>
       </c>
     </row>
     <row r="14">
@@ -5250,37 +5250,37 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>1.965659275306106</v>
+        <v>1.965659275306108</v>
       </c>
       <c r="H14">
-        <v>1.961540952445235</v>
+        <v>1.961540952445237</v>
       </c>
       <c r="I14">
-        <v>-0.00411832286087098</v>
+        <v>-0.004118322860870968</v>
       </c>
       <c r="J14">
-        <v>0.005584629784404001</v>
+        <v>0.005584629784844738</v>
       </c>
       <c r="K14">
         <v>3</v>
       </c>
       <c r="L14">
-        <v>-0.02189110728462484</v>
+        <v>-0.02189110728602746</v>
       </c>
       <c r="M14">
-        <v>0.01365446156288288</v>
+        <v>0.01365446156428552</v>
       </c>
       <c r="N14">
-        <v>-0.2095135669038902</v>
+        <v>-0.2095135669038894</v>
       </c>
       <c r="O14">
-        <v>0.5142972548228758</v>
+        <v>0.5142972548535101</v>
       </c>
       <c r="P14">
-        <v>4.203193682883466E-06</v>
+        <v>4.203193683771644E-06</v>
       </c>
       <c r="Q14">
-        <v>0.9985126838183408</v>
+        <v>0.9985126838186595</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -5291,16 +5291,16 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>0.01378509965858572</v>
+        <v>0.01378509965474239</v>
       </c>
       <c r="U14">
-        <v>7.432130407202171E-07</v>
+        <v>7.432206917985261E-07</v>
       </c>
       <c r="V14">
-        <v>0.02877296467780717</v>
+        <v>0.02877296467823919</v>
       </c>
       <c r="W14">
-        <v>0.4632309024730724</v>
+        <v>0.4632309026152645</v>
       </c>
     </row>
     <row r="15">
@@ -5333,37 +5333,37 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>1.965659554720978</v>
+        <v>1.965659554720974</v>
       </c>
       <c r="H15">
-        <v>1.955696270988015</v>
+        <v>1.95569627098797</v>
       </c>
       <c r="I15">
-        <v>-0.009963283732962441</v>
+        <v>-0.009963283733004312</v>
       </c>
       <c r="J15">
-        <v>0.005422539885422185</v>
+        <v>0.005422539885069008</v>
       </c>
       <c r="K15">
         <v>3</v>
       </c>
       <c r="L15">
-        <v>-0.02722022575657781</v>
+        <v>-0.02722022575549572</v>
       </c>
       <c r="M15">
-        <v>0.00729365829065293</v>
+        <v>0.007293658289487094</v>
       </c>
       <c r="N15">
-        <v>-0.5068672094836236</v>
+        <v>-0.5068672094857546</v>
       </c>
       <c r="O15">
-        <v>0.1634630943122229</v>
+        <v>0.1634630942915104</v>
       </c>
       <c r="P15">
-        <v>5.803985780206133E-06</v>
+        <v>5.803985777763643E-06</v>
       </c>
       <c r="Q15">
-        <v>0.9479401743007232</v>
+        <v>0.9479401742957627</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -5374,16 +5374,16 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>0.01373435692409535</v>
+        <v>0.01373435692962461</v>
       </c>
       <c r="U15">
-        <v>6.792528870651155E-07</v>
+        <v>6.799860030275971E-07</v>
       </c>
       <c r="V15">
-        <v>0.02767522938429513</v>
+        <v>0.02767522938378442</v>
       </c>
       <c r="W15">
-        <v>0.4730807773194391</v>
+        <v>0.4730807772014515</v>
       </c>
     </row>
     <row r="16">
@@ -5416,37 +5416,37 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>1.965659414533605</v>
+        <v>1.965659414533604</v>
       </c>
       <c r="H16">
-        <v>1.95270588394614</v>
+        <v>1.952705883946115</v>
       </c>
       <c r="I16">
-        <v>-0.01295353058746412</v>
+        <v>-0.01295353058748931</v>
       </c>
       <c r="J16">
-        <v>0.005316685029710596</v>
+        <v>0.005316685029531998</v>
       </c>
       <c r="K16">
         <v>3</v>
       </c>
       <c r="L16">
-        <v>-0.02987359521662381</v>
+        <v>-0.02987359521608061</v>
       </c>
       <c r="M16">
-        <v>0.003966534041695566</v>
+        <v>0.003966534041102003</v>
       </c>
       <c r="N16">
-        <v>-0.6589916081946284</v>
+        <v>-0.65899160819591</v>
       </c>
       <c r="O16">
-        <v>0.0927985567921672</v>
+        <v>0.09279855678501803</v>
       </c>
       <c r="P16">
-        <v>1.369626127134538E-05</v>
+        <v>1.369626127156742E-05</v>
       </c>
       <c r="Q16">
-        <v>0.9121962359982263</v>
+        <v>0.9121962359954086</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -5457,16 +5457,16 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>0.01352914145014216</v>
+        <v>0.01352914144995473</v>
       </c>
       <c r="U16">
-        <v>8.053928197436389E-07</v>
+        <v>8.05376751109937E-07</v>
       </c>
       <c r="V16">
-        <v>0.02720732351510541</v>
+        <v>0.0272073235150266</v>
       </c>
       <c r="W16">
-        <v>0.467243284974466</v>
+        <v>0.4672432849072362</v>
       </c>
     </row>
     <row r="17">
@@ -5499,37 +5499,37 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>2.167068746891311</v>
+        <v>2.16706874689131</v>
       </c>
       <c r="H17">
-        <v>2.377924955682625</v>
+        <v>2.377924955682624</v>
       </c>
       <c r="I17">
-        <v>0.2108562087913144</v>
+        <v>0.2108562087913147</v>
       </c>
       <c r="J17">
-        <v>0.06814846555935401</v>
+        <v>0.06814846555919442</v>
       </c>
       <c r="K17">
         <v>3</v>
       </c>
       <c r="L17">
-        <v>-0.006022623638805735</v>
+        <v>-0.006022623638297586</v>
       </c>
       <c r="M17">
-        <v>0.4277350412214346</v>
+        <v>0.427735041220927</v>
       </c>
       <c r="N17">
-        <v>9.730019368042225</v>
+        <v>9.730019368042239</v>
       </c>
       <c r="O17">
-        <v>0.05354293974251745</v>
+        <v>0.05354293974221414</v>
       </c>
       <c r="P17">
         <v>5.809730474481967E-11</v>
       </c>
       <c r="Q17">
-        <v>0.1934635983285402</v>
+        <v>0.1934635983299994</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -5540,16 +5540,16 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>0.2389574825280075</v>
+        <v>0.2389574825170981</v>
       </c>
       <c r="U17">
-        <v>1.457473006550927E-05</v>
+        <v>1.457457155045578E-05</v>
       </c>
       <c r="V17">
-        <v>0.3399273294324012</v>
+        <v>0.3399273294327436</v>
       </c>
       <c r="W17">
-        <v>0.524544065430447</v>
+        <v>0.5245440654254153</v>
       </c>
     </row>
     <row r="18">
@@ -5582,37 +5582,37 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>2.167036359080488</v>
+        <v>2.167036359080486</v>
       </c>
       <c r="H18">
-        <v>2.323636537722989</v>
+        <v>2.323636537722987</v>
       </c>
       <c r="I18">
-        <v>0.1566001786425011</v>
+        <v>0.1566001786425012</v>
       </c>
       <c r="J18">
-        <v>0.04999987770008565</v>
+        <v>0.0499998777002062</v>
       </c>
       <c r="K18">
         <v>3</v>
       </c>
       <c r="L18">
-        <v>-0.0025217474087737</v>
+        <v>-0.00252174740915731</v>
       </c>
       <c r="M18">
-        <v>0.3157221046937759</v>
+        <v>0.3157221046941596</v>
       </c>
       <c r="N18">
-        <v>7.226467520321132</v>
+        <v>7.226467520321143</v>
       </c>
       <c r="O18">
-        <v>0.05198437459121874</v>
+        <v>0.05198437459152316</v>
       </c>
       <c r="P18">
         <v>3.321787289678468E-13</v>
       </c>
       <c r="Q18">
-        <v>0.4481444809596478</v>
+        <v>0.4481444809641534</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -5623,16 +5623,16 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>0.1896254632807048</v>
+        <v>0.1896254632669268</v>
       </c>
       <c r="U18">
-        <v>6.983698670177986E-06</v>
+        <v>6.983750823041532E-06</v>
       </c>
       <c r="V18">
-        <v>0.2738606075526838</v>
+        <v>0.2738606075533238</v>
       </c>
       <c r="W18">
-        <v>1.013620887409919E-07</v>
+        <v>1.013680136728262E-07</v>
       </c>
     </row>
     <row r="19">
@@ -5665,37 +5665,37 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>2.323636537722991</v>
+        <v>2.323636537722984</v>
       </c>
       <c r="H19">
-        <v>2.348369878112611</v>
+        <v>2.348369878112605</v>
       </c>
       <c r="I19">
-        <v>0.02473334038962124</v>
+        <v>0.02473334038962182</v>
       </c>
       <c r="J19">
-        <v>0.05040292755259707</v>
+        <v>0.05040292755246652</v>
       </c>
       <c r="K19">
         <v>3</v>
       </c>
       <c r="L19">
-        <v>-0.1356712701756237</v>
+        <v>-0.1356712701752076</v>
       </c>
       <c r="M19">
-        <v>0.1851379509548662</v>
+        <v>0.1851379509544513</v>
       </c>
       <c r="N19">
-        <v>1.064423802435912</v>
+        <v>1.064423802435941</v>
       </c>
       <c r="O19">
-        <v>0.6572819459231013</v>
+        <v>0.6572819459222934</v>
       </c>
       <c r="P19">
         <v>1.998401444325282E-15</v>
       </c>
       <c r="Q19">
-        <v>0.8301008524331054</v>
+        <v>0.8301008524302518</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -5706,16 +5706,16 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0.173423921978251</v>
+        <v>0.1734239219924387</v>
       </c>
       <c r="U19">
-        <v>8.326509257367822E-06</v>
+        <v>8.326511634792292E-06</v>
       </c>
       <c r="V19">
-        <v>0.2760682019650385</v>
+        <v>0.2760682019643222</v>
       </c>
       <c r="W19">
-        <v>4.808086373956985E-09</v>
+        <v>4.808843242668202E-09</v>
       </c>
     </row>
     <row r="20">
@@ -5748,37 +5748,37 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>2.323636537722987</v>
+        <v>2.323636537722988</v>
       </c>
       <c r="H20">
-        <v>2.442352776688062</v>
+        <v>2.442352776688102</v>
       </c>
       <c r="I20">
-        <v>0.1187162389650756</v>
+        <v>0.118716238965114</v>
       </c>
       <c r="J20">
-        <v>0.04853910606550155</v>
+        <v>0.04853910606533006</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20">
-        <v>-0.0357568597948538</v>
+        <v>-0.03575685979426968</v>
       </c>
       <c r="M20">
-        <v>0.273189337725005</v>
+        <v>0.2731893377244977</v>
       </c>
       <c r="N20">
-        <v>5.109070934192221</v>
+        <v>5.109070934193872</v>
       </c>
       <c r="O20">
-        <v>0.09202428553305975</v>
+        <v>0.09202428553228659</v>
       </c>
       <c r="P20">
         <v>1.332267629550188E-15</v>
       </c>
       <c r="Q20">
-        <v>0.264832301347909</v>
+        <v>0.2648323013414869</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -5789,16 +5789,16 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>0.1692602372197817</v>
+        <v>0.1692602372384586</v>
       </c>
       <c r="U20">
-        <v>6.972755000141599E-06</v>
+        <v>6.972762850649347E-06</v>
       </c>
       <c r="V20">
-        <v>0.2643486340909924</v>
+        <v>0.2643486340900547</v>
       </c>
       <c r="W20">
-        <v>1.339162380154497E-12</v>
+        <v>1.339370581077944E-12</v>
       </c>
     </row>
     <row r="21">
@@ -5831,37 +5831,37 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>2.323636537722986</v>
+        <v>2.323636537722989</v>
       </c>
       <c r="H21">
-        <v>2.474549123645008</v>
+        <v>2.474549123644997</v>
       </c>
       <c r="I21">
-        <v>0.1509125859220221</v>
+        <v>0.150912585922009</v>
       </c>
       <c r="J21">
-        <v>0.04951686484782925</v>
+        <v>0.04951686484787725</v>
       </c>
       <c r="K21">
         <v>3</v>
       </c>
       <c r="L21">
-        <v>-0.006672177662184753</v>
+        <v>-0.006672177662350676</v>
       </c>
       <c r="M21">
-        <v>0.308497349506229</v>
+        <v>0.3084973495063686</v>
       </c>
       <c r="N21">
-        <v>6.494672616480147</v>
+        <v>6.494672616479572</v>
       </c>
       <c r="O21">
-        <v>0.05552863374471806</v>
+        <v>0.05552863374485917</v>
       </c>
       <c r="P21">
         <v>1.110223024625157E-14</v>
       </c>
       <c r="Q21">
-        <v>0.2541464968336551</v>
+        <v>0.254146496835586</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -5872,16 +5872,16 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>0.1636676990743938</v>
+        <v>0.1636676990688068</v>
       </c>
       <c r="U21">
-        <v>6.803338879776516E-06</v>
+        <v>6.803253732255091E-06</v>
       </c>
       <c r="V21">
-        <v>0.2696740120299915</v>
+        <v>0.2696740120302848</v>
       </c>
       <c r="W21">
-        <v>4.884018230961587E-09</v>
+        <v>4.883386411699965E-09</v>
       </c>
     </row>
     <row r="22">
@@ -5914,37 +5914,37 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>5.715657023779306</v>
+        <v>5.715657023779298</v>
       </c>
       <c r="H22">
-        <v>4.475082483533155</v>
+        <v>4.475082483533146</v>
       </c>
       <c r="I22">
-        <v>-1.240574540246151</v>
+        <v>-1.240574540246152</v>
       </c>
       <c r="J22">
-        <v>0.4190589449041132</v>
+        <v>0.4190589449014201</v>
       </c>
       <c r="K22">
         <v>3</v>
       </c>
       <c r="L22">
-        <v>-2.574207131152335</v>
+        <v>-2.574207131143766</v>
       </c>
       <c r="M22">
-        <v>0.09305805066003248</v>
+        <v>0.09305805065146089</v>
       </c>
       <c r="N22">
-        <v>-21.70484574362824</v>
+        <v>-21.70484574362829</v>
       </c>
       <c r="O22">
-        <v>0.05952571919122629</v>
+        <v>0.05952571919031668</v>
       </c>
       <c r="P22">
-        <v>6.985755919775016E-05</v>
+        <v>6.985755918820225E-05</v>
       </c>
       <c r="Q22">
-        <v>0.5685524937785471</v>
+        <v>0.5685524937685535</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -5955,16 +5955,16 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>0.5086165068961878</v>
+        <v>0.5086165070319885</v>
       </c>
       <c r="U22">
-        <v>0.0001458774364943609</v>
+        <v>0.0001458748969931011</v>
       </c>
       <c r="V22">
-        <v>2.295280300948245</v>
+        <v>2.295280300935914</v>
       </c>
       <c r="W22">
-        <v>7.265050061747529E-08</v>
+        <v>7.268969538949591E-08</v>
       </c>
     </row>
     <row r="23">
@@ -5997,37 +5997,37 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>5.716450412948344</v>
+        <v>5.716450412948245</v>
       </c>
       <c r="H23">
-        <v>6.281438179491058</v>
+        <v>6.281438179490992</v>
       </c>
       <c r="I23">
-        <v>0.5649877665427132</v>
+        <v>0.5649877665427475</v>
       </c>
       <c r="J23">
-        <v>0.7135712486929519</v>
+        <v>0.7135712486718941</v>
       </c>
       <c r="K23">
         <v>3</v>
       </c>
       <c r="L23">
-        <v>-1.705914417416853</v>
+        <v>-1.705914417349804</v>
       </c>
       <c r="M23">
-        <v>2.835889950502279</v>
+        <v>2.835889950435299</v>
       </c>
       <c r="N23">
-        <v>9.883541808793762</v>
+        <v>9.883541808794533</v>
       </c>
       <c r="O23">
-        <v>0.4863208836095088</v>
+        <v>0.4863208835977372</v>
       </c>
       <c r="P23">
-        <v>0.002785151783264661</v>
+        <v>0.002785151782864093</v>
       </c>
       <c r="Q23">
-        <v>0.9463393348705065</v>
+        <v>0.9463393348786391</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -6038,16 +6038,16 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>0.0001678026054428877</v>
+        <v>0.0001678020502344692</v>
       </c>
       <c r="U23">
-        <v>0.0002169320966909897</v>
+        <v>0.0002169289287681086</v>
       </c>
       <c r="V23">
-        <v>3.502826415322216</v>
+        <v>3.502826415310855</v>
       </c>
       <c r="W23">
-        <v>0.5488864132614647</v>
+        <v>0.5488864132246087</v>
       </c>
     </row>
     <row r="24">
@@ -6080,37 +6080,37 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>6.281363940121921</v>
+        <v>6.281363940122243</v>
       </c>
       <c r="H24">
-        <v>6.18247979200877</v>
+        <v>6.182479792008519</v>
       </c>
       <c r="I24">
-        <v>-0.0988841481131527</v>
+        <v>-0.09888414811372354</v>
       </c>
       <c r="J24">
-        <v>0.757178850819852</v>
+        <v>0.757178851294994</v>
       </c>
       <c r="K24">
         <v>3</v>
       </c>
       <c r="L24">
-        <v>-2.508565184343755</v>
+        <v>-2.508565185856439</v>
       </c>
       <c r="M24">
-        <v>2.310796888117449</v>
+        <v>2.310796889628992</v>
       </c>
       <c r="N24">
-        <v>-1.574246438445236</v>
+        <v>-1.574246438454243</v>
       </c>
       <c r="O24">
-        <v>0.9043605697779602</v>
+        <v>0.9043605698369798</v>
       </c>
       <c r="P24">
-        <v>0.0729223860699284</v>
+        <v>0.07292238618551405</v>
       </c>
       <c r="Q24">
-        <v>0.8311648905466491</v>
+        <v>0.8311648906587366</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -6121,16 +6121,16 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>0.9058948088322798</v>
+        <v>0.9058948050375422</v>
       </c>
       <c r="U24">
-        <v>0.0002319006786673716</v>
+        <v>0.0002319083323328616</v>
       </c>
       <c r="V24">
-        <v>4.000145886924588</v>
+        <v>4.000145887397047</v>
       </c>
       <c r="W24">
-        <v>0.3961713649885404</v>
+        <v>0.3961713666530482</v>
       </c>
     </row>
     <row r="25">
@@ -6163,37 +6163,37 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>6.281298995275262</v>
+        <v>6.281298995275222</v>
       </c>
       <c r="H25">
-        <v>6.918865152854916</v>
+        <v>6.918865152854911</v>
       </c>
       <c r="I25">
-        <v>0.6375661575796534</v>
+        <v>0.6375661575796896</v>
       </c>
       <c r="J25">
-        <v>1.054782388124813</v>
+        <v>1.054782388144537</v>
       </c>
       <c r="K25">
         <v>3</v>
       </c>
       <c r="L25">
-        <v>-2.719222156386482</v>
+        <v>-2.719222156449216</v>
       </c>
       <c r="M25">
-        <v>3.994354471545789</v>
+        <v>3.994354471608596</v>
       </c>
       <c r="N25">
-        <v>10.15022781210105</v>
+        <v>10.15022781210169</v>
       </c>
       <c r="O25">
-        <v>0.5881959312427495</v>
+        <v>0.5881959312493291</v>
       </c>
       <c r="P25">
-        <v>0.2053806799524933</v>
+        <v>0.2053806799595039</v>
       </c>
       <c r="Q25">
-        <v>0.5118438171616353</v>
+        <v>0.5118438171490337</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -6204,16 +6204,16 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>0.000218382873236984</v>
+        <v>0.000218380394267238</v>
       </c>
       <c r="U25">
-        <v>0.0001280547371095927</v>
+        <v>0.0001280531088997812</v>
       </c>
       <c r="V25">
-        <v>5.628494834643921</v>
+        <v>5.628494834646911</v>
       </c>
       <c r="W25">
-        <v>0.3356135814566467</v>
+        <v>0.3356135815467887</v>
       </c>
     </row>
     <row r="26">
@@ -6246,37 +6246,37 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>6.281496051175661</v>
+        <v>6.281496054994521</v>
       </c>
       <c r="H26">
-        <v>6.384748473479042</v>
+        <v>6.384748469060736</v>
       </c>
       <c r="I26">
-        <v>0.1032524223033814</v>
+        <v>0.1032524140662161</v>
       </c>
       <c r="J26">
-        <v>0.7650510238304811</v>
+        <v>0.7650510016899337</v>
       </c>
       <c r="K26">
         <v>3</v>
       </c>
       <c r="L26">
-        <v>-2.331481381839451</v>
+        <v>-2.331481319615513</v>
       </c>
       <c r="M26">
-        <v>2.537986226446214</v>
+        <v>2.537986147747945</v>
       </c>
       <c r="N26">
-        <v>1.643755268843263</v>
+        <v>1.643755136710122</v>
       </c>
       <c r="O26">
-        <v>0.9011885044968754</v>
+        <v>0.90118850947977</v>
       </c>
       <c r="P26">
-        <v>0.03660610003024045</v>
+        <v>0.03660609310719154</v>
       </c>
       <c r="Q26">
-        <v>0.3970272733520497</v>
+        <v>0.3970272446204093</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -6287,16 +6287,16 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>1.562156998599149E-15</v>
+        <v>8.306195834474859E-17</v>
       </c>
       <c r="U26">
-        <v>2.86516116825702E-15</v>
+        <v>1.568397145701247E-16</v>
       </c>
       <c r="V26">
-        <v>4.16726934734741</v>
+        <v>4.167269341827359</v>
       </c>
       <c r="W26">
-        <v>0.004609721183365982</v>
+        <v>0.002718898046545157</v>
       </c>
     </row>
     <row r="27">
@@ -6329,37 +6329,37 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>0.3181513304353052</v>
+        <v>0.3181513304352998</v>
       </c>
       <c r="H27">
-        <v>0.3184091075185372</v>
+        <v>0.3184091075185365</v>
       </c>
       <c r="I27">
-        <v>0.0002577770832319153</v>
+        <v>0.0002577770832367278</v>
       </c>
       <c r="J27">
-        <v>0.0009234375697945879</v>
+        <v>0.0009234375697761263</v>
       </c>
       <c r="K27">
         <v>3</v>
       </c>
       <c r="L27">
-        <v>-0.002681013398921037</v>
+        <v>-0.002681013398857472</v>
       </c>
       <c r="M27">
-        <v>0.003196567565384867</v>
+        <v>0.003196567565330927</v>
       </c>
       <c r="N27">
-        <v>0.08102341828312211</v>
+        <v>0.08102341828463613</v>
       </c>
       <c r="O27">
-        <v>0.7982681553576989</v>
+        <v>0.7982681553501167</v>
       </c>
       <c r="P27">
-        <v>0.1094290418008494</v>
+        <v>0.109429041781189</v>
       </c>
       <c r="Q27">
-        <v>0.986655601296103</v>
+        <v>0.9866556012932424</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -6370,16 +6370,16 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>0.001580600481501544</v>
+        <v>0.001580600482743718</v>
       </c>
       <c r="U27">
-        <v>1.844344891734876E-07</v>
+        <v>1.844365809805105E-07</v>
       </c>
       <c r="V27">
-        <v>0.005029302278582551</v>
+        <v>0.005029302278480572</v>
       </c>
       <c r="W27">
-        <v>9.35068695999918E-19</v>
+        <v>9.378194156565162E-19</v>
       </c>
     </row>
     <row r="28">
@@ -6412,37 +6412,37 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>0.3181408563298643</v>
+        <v>0.3181408563298728</v>
       </c>
       <c r="H28">
-        <v>0.3171571133163673</v>
+        <v>0.3171571133163644</v>
       </c>
       <c r="I28">
-        <v>-0.0009837430134970195</v>
+        <v>-0.0009837430135084845</v>
       </c>
       <c r="J28">
-        <v>0.0009001841961518706</v>
+        <v>0.0009001841951286106</v>
       </c>
       <c r="K28">
         <v>3</v>
       </c>
       <c r="L28">
-        <v>-0.003848530882615325</v>
+        <v>-0.00384853087937032</v>
       </c>
       <c r="M28">
-        <v>0.001881044855621286</v>
+        <v>0.001881044852353351</v>
       </c>
       <c r="N28">
-        <v>-0.309216183311277</v>
+        <v>-0.3092161833148724</v>
       </c>
       <c r="O28">
-        <v>0.3543718200413557</v>
+        <v>0.3543718195693368</v>
       </c>
       <c r="P28">
-        <v>0.4971386725042369</v>
+        <v>0.4971386725833122</v>
       </c>
       <c r="Q28">
-        <v>0.1106425823974312</v>
+        <v>0.1106425824672489</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -6453,16 +6453,16 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>0.001278537277335406</v>
+        <v>0.001278537278212777</v>
       </c>
       <c r="U28">
-        <v>0.0005359749024851043</v>
+        <v>0.0005359748981150795</v>
       </c>
       <c r="V28">
-        <v>0.004399181256258509</v>
+        <v>0.00439918125654726</v>
       </c>
       <c r="W28">
-        <v>0.2756842847306371</v>
+        <v>0.2756842871582819</v>
       </c>
     </row>
     <row r="29">
@@ -6495,37 +6495,37 @@
         <v>1</v>
       </c>
       <c r="G29">
-        <v>0.3171563766424993</v>
+        <v>0.317156376642493</v>
       </c>
       <c r="H29">
-        <v>0.3175283304406998</v>
+        <v>0.3175283304419296</v>
       </c>
       <c r="I29">
-        <v>0.0003719537982004884</v>
+        <v>0.0003719537994366687</v>
       </c>
       <c r="J29">
-        <v>0.000906568538699264</v>
+        <v>0.0009065685397172795</v>
       </c>
       <c r="K29">
         <v>3</v>
       </c>
       <c r="L29">
-        <v>-0.002513151898269434</v>
+        <v>-0.002513151900273034</v>
       </c>
       <c r="M29">
-        <v>0.003257059494670411</v>
+        <v>0.003257059499146371</v>
       </c>
       <c r="N29">
-        <v>0.1172777297237688</v>
+        <v>0.1172777301135411</v>
       </c>
       <c r="O29">
-        <v>0.709136997857327</v>
+        <v>0.7091369972620301</v>
       </c>
       <c r="P29">
-        <v>0.2613793998216061</v>
+        <v>0.2613794034399521</v>
       </c>
       <c r="Q29">
-        <v>0.01385623935917413</v>
+        <v>0.01385623970414773</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -6536,16 +6536,16 @@
         <v>0</v>
       </c>
       <c r="T29">
-        <v>0.0004517040926702948</v>
+        <v>0.0004517039795848431</v>
       </c>
       <c r="U29">
-        <v>2.446673771798971E-07</v>
+        <v>2.45098018648587E-07</v>
       </c>
       <c r="V29">
-        <v>0.004010536089376378</v>
+        <v>0.004010536095739664</v>
       </c>
       <c r="W29">
-        <v>0.6595978331720734</v>
+        <v>0.6595978327165216</v>
       </c>
     </row>
     <row r="30">
@@ -6578,37 +6578,37 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>0.3171564320783765</v>
+        <v>0.317156432078655</v>
       </c>
       <c r="H30">
-        <v>0.3179407069618047</v>
+        <v>0.3179407069398695</v>
       </c>
       <c r="I30">
-        <v>0.000784274883428174</v>
+        <v>0.0007842748612146082</v>
       </c>
       <c r="J30">
-        <v>0.0008811404865159127</v>
+        <v>0.0008811403753306518</v>
       </c>
       <c r="K30">
         <v>3</v>
       </c>
       <c r="L30">
-        <v>-0.002019907402320281</v>
+        <v>-0.002019907070692724</v>
       </c>
       <c r="M30">
-        <v>0.003588457169176629</v>
+        <v>0.00358845679312194</v>
       </c>
       <c r="N30">
-        <v>0.2472832974846816</v>
+        <v>0.2472832904804868</v>
       </c>
       <c r="O30">
-        <v>0.4389989982730254</v>
+        <v>0.4389989582019507</v>
       </c>
       <c r="P30">
-        <v>0.005513859568007762</v>
+        <v>0.005513855972722803</v>
       </c>
       <c r="Q30">
-        <v>0.2730796857938258</v>
+        <v>0.2730796761965297</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -6619,16 +6619,16 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>0.0002244287170304542</v>
+        <v>0.0002244311172107746</v>
       </c>
       <c r="U30">
-        <v>2.855057817832476E-07</v>
+        <v>2.850785702896955E-07</v>
       </c>
       <c r="V30">
-        <v>0.004038739793741095</v>
+        <v>0.00403873963453661</v>
       </c>
       <c r="W30">
-        <v>0.6263326301199706</v>
+        <v>0.6263325422466779</v>
       </c>
     </row>
     <row r="31">
@@ -6661,37 +6661,37 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>0.3171564401370898</v>
+        <v>0.3171564401370906</v>
       </c>
       <c r="H31">
-        <v>0.3168147616817668</v>
+        <v>0.3168147616816879</v>
       </c>
       <c r="I31">
-        <v>-0.0003416784553230011</v>
+        <v>-0.0003416784554026475</v>
       </c>
       <c r="J31">
-        <v>0.0009125620735969184</v>
+        <v>0.0009125620731659855</v>
       </c>
       <c r="K31">
         <v>3</v>
       </c>
       <c r="L31">
-        <v>-0.003245858254783553</v>
+        <v>-0.003245858253491779</v>
       </c>
       <c r="M31">
-        <v>0.002562501344137551</v>
+        <v>0.002562501342686484</v>
       </c>
       <c r="N31">
-        <v>-0.1077318358016983</v>
+        <v>-0.1077318358268107</v>
       </c>
       <c r="O31">
-        <v>0.7329934793640946</v>
+        <v>0.7329934791869043</v>
       </c>
       <c r="P31">
-        <v>0.01119289631378639</v>
+        <v>0.01119289628672138</v>
       </c>
       <c r="Q31">
-        <v>0.7744304314373962</v>
+        <v>0.7744304315875609</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>0.0003813839472422011</v>
+        <v>0.0003813839506608239</v>
       </c>
       <c r="U31">
-        <v>3.037334581689714E-07</v>
+        <v>3.037262782511067E-07</v>
       </c>
       <c r="V31">
-        <v>0.004152731680142648</v>
+        <v>0.004152731679652062</v>
       </c>
       <c r="W31">
-        <v>0.6247842950821191</v>
+        <v>0.6247842947165358</v>
       </c>
     </row>
     <row r="32">
@@ -6744,37 +6744,37 @@
         <v>1</v>
       </c>
       <c r="G32">
-        <v>439.0329017272365</v>
+        <v>439.0329017272575</v>
       </c>
       <c r="H32">
-        <v>428.5560578434253</v>
+        <v>428.5560578434248</v>
       </c>
       <c r="I32">
-        <v>-10.47684388381112</v>
+        <v>-10.47684388383265</v>
       </c>
       <c r="J32">
-        <v>9.123058139501573</v>
+        <v>9.123058139915456</v>
       </c>
       <c r="K32">
         <v>3</v>
       </c>
       <c r="L32">
-        <v>-39.51048655275635</v>
+        <v>-39.51048655409504</v>
       </c>
       <c r="M32">
-        <v>18.55679878513412</v>
+        <v>18.55679878642975</v>
       </c>
       <c r="N32">
-        <v>-2.386345953251631</v>
+        <v>-2.38634595325642</v>
       </c>
       <c r="O32">
-        <v>0.3340716888524247</v>
+        <v>0.3340716888700744</v>
       </c>
       <c r="P32">
-        <v>4.730516415984987E-05</v>
+        <v>4.730516418360864E-05</v>
       </c>
       <c r="Q32">
-        <v>0.9972508176712978</v>
+        <v>0.9972508176715205</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -6785,16 +6785,16 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>24.4305974707205</v>
+        <v>24.43059746433977</v>
       </c>
       <c r="U32">
-        <v>0.002285324063442582</v>
+        <v>0.002285345364736415</v>
       </c>
       <c r="V32">
-        <v>35.00623374807756</v>
+        <v>35.00623374873532</v>
       </c>
       <c r="W32">
-        <v>0.7577387413843951</v>
+        <v>0.7577387413989322</v>
       </c>
     </row>
     <row r="33">
@@ -6827,37 +6827,37 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>439.1151617433837</v>
+        <v>439.115161743403</v>
       </c>
       <c r="H33">
-        <v>419.9439712850182</v>
+        <v>419.9439712850209</v>
       </c>
       <c r="I33">
-        <v>-19.17119045836542</v>
+        <v>-19.17119045838206</v>
       </c>
       <c r="J33">
-        <v>11.75991033505523</v>
+        <v>11.75991033732979</v>
       </c>
       <c r="K33">
         <v>3</v>
       </c>
       <c r="L33">
-        <v>-56.59647365462964</v>
+        <v>-56.59647366188492</v>
       </c>
       <c r="M33">
-        <v>18.25409273789881</v>
+        <v>18.25409274512079</v>
       </c>
       <c r="N33">
-        <v>-4.365868484761851</v>
+        <v>-4.365868484765451</v>
       </c>
       <c r="O33">
-        <v>0.2015493918467621</v>
+        <v>0.2015493919116456</v>
       </c>
       <c r="P33">
-        <v>6.311311262496844E-08</v>
+        <v>6.311311273599074E-08</v>
       </c>
       <c r="Q33">
-        <v>0.4793425432040139</v>
+        <v>0.4793425431134143</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -6868,16 +6868,16 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>17.91034988176458</v>
+        <v>17.91034988214612</v>
       </c>
       <c r="U33">
-        <v>0.006812203913394613</v>
+        <v>0.006811502086809066</v>
       </c>
       <c r="V33">
-        <v>35.50589093423358</v>
+        <v>35.50589093718587</v>
       </c>
       <c r="W33">
-        <v>0.8588515702403611</v>
+        <v>0.8588515702815531</v>
       </c>
     </row>
     <row r="34">
@@ -6910,37 +6910,37 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>419.9434235819385</v>
+        <v>419.94342358187</v>
       </c>
       <c r="H34">
-        <v>414.589977860073</v>
+        <v>414.5899778585058</v>
       </c>
       <c r="I34">
-        <v>-5.353445721865612</v>
+        <v>-5.353445723364242</v>
       </c>
       <c r="J34">
-        <v>4.113291686429892</v>
+        <v>4.113291699492963</v>
       </c>
       <c r="K34">
         <v>3</v>
       </c>
       <c r="L34">
-        <v>-18.44377565189861</v>
+        <v>-18.44377569496977</v>
       </c>
       <c r="M34">
-        <v>7.736884208167388</v>
+        <v>7.736884248241282</v>
       </c>
       <c r="N34">
-        <v>-1.274801656900113</v>
+        <v>-1.274801657257186</v>
       </c>
       <c r="O34">
-        <v>0.2840169652659473</v>
+        <v>0.2840169663976808</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0.9974110775388939</v>
+        <v>0.9974110775454158</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -6951,16 +6951,16 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>7.778182078181437</v>
+        <v>7.778182024092115</v>
       </c>
       <c r="U34">
-        <v>0.001020096230107847</v>
+        <v>0.001020110285450408</v>
       </c>
       <c r="V34">
-        <v>21.61573389191533</v>
+        <v>21.61573390045852</v>
       </c>
       <c r="W34">
-        <v>0.3963314385784725</v>
+        <v>0.3963314477939908</v>
       </c>
     </row>
     <row r="35">
@@ -6993,37 +6993,37 @@
         <v>1</v>
       </c>
       <c r="G35">
-        <v>419.944080847873</v>
+        <v>419.9440808479996</v>
       </c>
       <c r="H35">
-        <v>411.7723441333368</v>
+        <v>411.7723441361204</v>
       </c>
       <c r="I35">
-        <v>-8.17173671453611</v>
+        <v>-8.171736711879216</v>
       </c>
       <c r="J35">
-        <v>4.131799726656333</v>
+        <v>4.131799715191822</v>
       </c>
       <c r="K35">
         <v>3</v>
       </c>
       <c r="L35">
-        <v>-21.32096748880579</v>
+        <v>-21.3209674496637</v>
       </c>
       <c r="M35">
-        <v>4.977494059733573</v>
+        <v>4.977494025905274</v>
       </c>
       <c r="N35">
-        <v>-1.945910678878307</v>
+        <v>-1.945910678245042</v>
       </c>
       <c r="O35">
-        <v>0.1423663507076569</v>
+        <v>0.1423663500366886</v>
       </c>
       <c r="P35">
         <v>2.220446049250313E-16</v>
       </c>
       <c r="Q35">
-        <v>0.9899349947255803</v>
+        <v>0.9899349947564495</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -7034,16 +7034,16 @@
         <v>0</v>
       </c>
       <c r="T35">
-        <v>8.781238452479705</v>
+        <v>8.781238439825964</v>
       </c>
       <c r="U35">
-        <v>0.001724516643820262</v>
+        <v>0.001724496182469414</v>
       </c>
       <c r="V35">
-        <v>22.24333491580935</v>
+        <v>22.24333491400158</v>
       </c>
       <c r="W35">
-        <v>0.2819682133472115</v>
+        <v>0.2819681933237931</v>
       </c>
     </row>
     <row r="36">
@@ -7076,37 +7076,37 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>419.9430405774252</v>
+        <v>419.9430405774364</v>
       </c>
       <c r="H36">
-        <v>409.0229283268124</v>
+        <v>409.0229283264894</v>
       </c>
       <c r="I36">
-        <v>-10.92011225061277</v>
+        <v>-10.92011225094705</v>
       </c>
       <c r="J36">
-        <v>4.116628769632822</v>
+        <v>4.116628767413799</v>
       </c>
       <c r="K36">
         <v>3</v>
       </c>
       <c r="L36">
-        <v>-24.02106226875536</v>
+        <v>-24.02106226202772</v>
       </c>
       <c r="M36">
-        <v>2.180837767529816</v>
+        <v>2.180837760133613</v>
       </c>
       <c r="N36">
-        <v>-2.600379383736787</v>
+        <v>-2.600379383816319</v>
       </c>
       <c r="O36">
-        <v>0.07681735305147486</v>
+        <v>0.07681735295222714</v>
       </c>
       <c r="P36">
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0.787033512181703</v>
+        <v>0.7870335122044502</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -7117,16 +7117,16 @@
         <v>0</v>
       </c>
       <c r="T36">
-        <v>8.3783992929202</v>
+        <v>8.37839930800795</v>
       </c>
       <c r="U36">
-        <v>0.004287983677371903</v>
+        <v>0.004288166877257681</v>
       </c>
       <c r="V36">
-        <v>21.22038576719632</v>
+        <v>21.22038576521224</v>
       </c>
       <c r="W36">
-        <v>0.4227210331648442</v>
+        <v>0.4227210318186112</v>
       </c>
     </row>
     <row r="37">
@@ -7159,37 +7159,37 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>1.97704373701642</v>
+        <v>1.977043737016501</v>
       </c>
       <c r="H37">
-        <v>1.965222678620958</v>
+        <v>1.965222678620959</v>
       </c>
       <c r="I37">
-        <v>-0.01182105839546244</v>
+        <v>-0.01182105839554173</v>
       </c>
       <c r="J37">
-        <v>0.009942222282534762</v>
+        <v>0.009942222282816902</v>
       </c>
       <c r="K37">
         <v>3</v>
       </c>
       <c r="L37">
-        <v>-0.04346164696482454</v>
+        <v>-0.04346164696580174</v>
       </c>
       <c r="M37">
-        <v>0.01981953017389967</v>
+        <v>0.01981953017471827</v>
       </c>
       <c r="N37">
-        <v>-0.597915876828387</v>
+        <v>-0.5979158768323733</v>
       </c>
       <c r="O37">
-        <v>0.3199840945187651</v>
+        <v>0.3199840945275008</v>
       </c>
       <c r="P37">
-        <v>0.1252499278715331</v>
+        <v>0.1252499278888124</v>
       </c>
       <c r="Q37">
-        <v>0.5775376647740844</v>
+        <v>0.5775376647891546</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -7200,16 +7200,16 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>0.01499536694907356</v>
+        <v>0.0149953669447823</v>
       </c>
       <c r="U37">
-        <v>1.115778032789977E-06</v>
+        <v>1.115838238703062E-06</v>
       </c>
       <c r="V37">
-        <v>0.05394245505373956</v>
+        <v>0.05394245505414247</v>
       </c>
       <c r="W37">
-        <v>0.2001463099164262</v>
+        <v>0.2001463102524095</v>
       </c>
     </row>
     <row r="38">
@@ -7242,37 +7242,37 @@
         <v>1</v>
       </c>
       <c r="G38">
-        <v>1.977019663303818</v>
+        <v>1.977019663765039</v>
       </c>
       <c r="H38">
-        <v>1.959981697313949</v>
+        <v>1.959981697463381</v>
       </c>
       <c r="I38">
-        <v>-0.01703796598986976</v>
+        <v>-0.01703796630165793</v>
       </c>
       <c r="J38">
-        <v>0.01022666150956512</v>
+        <v>0.01022666571774809</v>
       </c>
       <c r="K38">
         <v>3</v>
       </c>
       <c r="L38">
-        <v>-0.04958376712637238</v>
+        <v>-0.04958378083047689</v>
       </c>
       <c r="M38">
-        <v>0.01550783514663285</v>
+        <v>0.01550784822716102</v>
       </c>
       <c r="N38">
-        <v>-0.8618005326966471</v>
+        <v>-0.8618005482662123</v>
       </c>
       <c r="O38">
-        <v>0.1942967722598404</v>
+        <v>0.1942969021797325</v>
       </c>
       <c r="P38">
-        <v>0.009728275374082385</v>
+        <v>0.009728293408042821</v>
       </c>
       <c r="Q38">
-        <v>0.9964476612020922</v>
+        <v>0.9964476621430448</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>0.01484901614146134</v>
+        <v>0.01484901343583858</v>
       </c>
       <c r="U38">
-        <v>4.038098087022613E-07</v>
+        <v>5.739714527853905E-07</v>
       </c>
       <c r="V38">
-        <v>0.05559480272848758</v>
+        <v>0.05559480354971349</v>
       </c>
       <c r="W38">
-        <v>0.1596760955735511</v>
+        <v>0.1596868132628043</v>
       </c>
     </row>
     <row r="39">
@@ -7325,37 +7325,37 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>1.959991158442248</v>
+        <v>1.95999115844225</v>
       </c>
       <c r="H39">
-        <v>1.955058475168589</v>
+        <v>1.955058475168531</v>
       </c>
       <c r="I39">
-        <v>-0.004932683273658923</v>
+        <v>-0.00493268327371874</v>
       </c>
       <c r="J39">
-        <v>0.005301339564458229</v>
+        <v>0.005301339563588784</v>
       </c>
       <c r="K39">
         <v>3</v>
       </c>
       <c r="L39">
-        <v>-0.02180391178362335</v>
+        <v>-0.02180391178091621</v>
       </c>
       <c r="M39">
-        <v>0.01193854523630551</v>
+        <v>0.01193854523347873</v>
       </c>
       <c r="N39">
-        <v>-0.251668649239178</v>
+        <v>-0.2516686492422297</v>
       </c>
       <c r="O39">
-        <v>0.4207676176854898</v>
+        <v>0.4207676176129129</v>
       </c>
       <c r="P39">
-        <v>9.873009634286944E-07</v>
+        <v>9.873009627625606E-07</v>
       </c>
       <c r="Q39">
-        <v>0.9990343225680034</v>
+        <v>0.9990343225677822</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -7366,16 +7366,16 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>0.01402988139425565</v>
+        <v>0.01402988140497981</v>
       </c>
       <c r="U39">
-        <v>6.999626050821042E-07</v>
+        <v>6.862976090898095E-07</v>
       </c>
       <c r="V39">
-        <v>0.02655662820734062</v>
+        <v>0.02655662820687501</v>
       </c>
       <c r="W39">
-        <v>0.509324287532895</v>
+        <v>0.5093242875719801</v>
       </c>
     </row>
     <row r="40">
@@ -7408,37 +7408,37 @@
         <v>1</v>
       </c>
       <c r="G40">
-        <v>1.959991377556695</v>
+        <v>1.959991377556689</v>
       </c>
       <c r="H40">
-        <v>1.951057483394317</v>
+        <v>1.951057483394225</v>
       </c>
       <c r="I40">
-        <v>-0.008933894162378768</v>
+        <v>-0.00893389416246371</v>
       </c>
       <c r="J40">
-        <v>0.005234454514039324</v>
+        <v>0.005234454512321888</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40">
-        <v>-0.02559226459075884</v>
+        <v>-0.02559226458537813</v>
       </c>
       <c r="M40">
-        <v>0.007724476266001302</v>
+        <v>0.007724476260450714</v>
       </c>
       <c r="N40">
-        <v>-0.4558129318668568</v>
+        <v>-0.4558129318711922</v>
       </c>
       <c r="O40">
-        <v>0.1864087881303214</v>
+        <v>0.1864087880212859</v>
       </c>
       <c r="P40">
-        <v>2.000975177551823E-06</v>
+        <v>2.000975178217956E-06</v>
       </c>
       <c r="Q40">
-        <v>0.9381004222932535</v>
+        <v>0.9381004222975569</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -7449,16 +7449,16 @@
         <v>0</v>
       </c>
       <c r="T40">
-        <v>0.0139429769790312</v>
+        <v>0.01394297698047975</v>
       </c>
       <c r="U40">
-        <v>6.885722576524788E-07</v>
+        <v>6.778940653616748E-07</v>
       </c>
       <c r="V40">
-        <v>0.02608502309693555</v>
+        <v>0.02608502309629446</v>
       </c>
       <c r="W40">
-        <v>0.5183520222259168</v>
+        <v>0.5183520219375268</v>
       </c>
     </row>
     <row r="41">
@@ -7491,37 +7491,37 @@
         <v>1</v>
       </c>
       <c r="G41">
-        <v>1.95999141268432</v>
+        <v>1.959991412684328</v>
       </c>
       <c r="H41">
-        <v>1.947385616410563</v>
+        <v>1.94738561641093</v>
       </c>
       <c r="I41">
-        <v>-0.01260579627375704</v>
+        <v>-0.01260579627339727</v>
       </c>
       <c r="J41">
-        <v>0.005237593255272325</v>
+        <v>0.005237593259176438</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41">
-        <v>-0.02927415557757732</v>
+        <v>-0.02927415558964218</v>
       </c>
       <c r="M41">
-        <v>0.004062563030063237</v>
+        <v>0.004062563042847633</v>
       </c>
       <c r="N41">
-        <v>-0.6431556889574678</v>
+        <v>-0.6431556889391095</v>
       </c>
       <c r="O41">
-        <v>0.09529110274516273</v>
+        <v>0.0952911029045802</v>
       </c>
       <c r="P41">
-        <v>4.497545799120317E-06</v>
+        <v>4.497545797899072E-06</v>
       </c>
       <c r="Q41">
-        <v>0.9120278248678994</v>
+        <v>0.9120278248754501</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -7532,16 +7532,16 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>0.01391438321393967</v>
+        <v>0.01391438320699816</v>
       </c>
       <c r="U41">
-        <v>7.236135882003624E-07</v>
+        <v>7.61447726230038E-07</v>
       </c>
       <c r="V41">
-        <v>0.0258268792964012</v>
+        <v>0.02582687929729691</v>
       </c>
       <c r="W41">
-        <v>0.5191647398916057</v>
+        <v>0.5191647402302482</v>
       </c>
     </row>
     <row r="42">
@@ -7574,37 +7574,37 @@
         <v>1</v>
       </c>
       <c r="G42">
-        <v>2.328550850518401</v>
+        <v>2.328550850518403</v>
       </c>
       <c r="H42">
-        <v>2.375560612447559</v>
+        <v>2.375560612447569</v>
       </c>
       <c r="I42">
-        <v>0.04700976192915828</v>
+        <v>0.04700976192916646</v>
       </c>
       <c r="J42">
-        <v>0.05966247925201304</v>
+        <v>0.0596624792537978</v>
       </c>
       <c r="K42">
         <v>3</v>
       </c>
       <c r="L42">
-        <v>-0.1428628747304765</v>
+        <v>-0.1428628747361482</v>
       </c>
       <c r="M42">
-        <v>0.2368823985887931</v>
+        <v>0.2368823985944811</v>
       </c>
       <c r="N42">
-        <v>2.018841972838711</v>
+        <v>2.018841972839061</v>
       </c>
       <c r="O42">
-        <v>0.488258676838041</v>
+        <v>0.4882586768498665</v>
       </c>
       <c r="P42">
         <v>1.110223024625157E-15</v>
       </c>
       <c r="Q42">
-        <v>0.5961392227807991</v>
+        <v>0.5961392227840887</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -7615,16 +7615,16 @@
         <v>0</v>
       </c>
       <c r="T42">
-        <v>0.2559390733421441</v>
+        <v>0.2559390733301036</v>
       </c>
       <c r="U42">
-        <v>9.161320106686442E-06</v>
+        <v>9.161359325757038E-06</v>
       </c>
       <c r="V42">
-        <v>0.2746821711812377</v>
+        <v>0.274682171183108</v>
       </c>
       <c r="W42">
-        <v>0.6217993212399696</v>
+        <v>0.6217993212638278</v>
       </c>
     </row>
     <row r="43">
@@ -7657,37 +7657,37 @@
         <v>1</v>
       </c>
       <c r="G43">
-        <v>2.327663122467713</v>
+        <v>2.327663122467758</v>
       </c>
       <c r="H43">
-        <v>2.538140299683224</v>
+        <v>2.538140299683232</v>
       </c>
       <c r="I43">
-        <v>0.2104771772155119</v>
+        <v>0.2104771772154732</v>
       </c>
       <c r="J43">
-        <v>0.04544284397714399</v>
+        <v>0.04544284397700372</v>
       </c>
       <c r="K43">
         <v>3</v>
       </c>
       <c r="L43">
-        <v>0.06585776629886597</v>
+        <v>0.0658577662992737</v>
       </c>
       <c r="M43">
-        <v>0.3550965881321578</v>
+        <v>0.3550965881316727</v>
       </c>
       <c r="N43">
-        <v>9.042424360462043</v>
+        <v>9.042424360460204</v>
       </c>
       <c r="O43">
-        <v>0.01895754807943828</v>
+        <v>0.01895754807928951</v>
       </c>
       <c r="P43">
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>0.4128154230454026</v>
+        <v>0.4128154230396275</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -7698,16 +7698,16 @@
         <v>1</v>
       </c>
       <c r="T43">
-        <v>0.2082215536335159</v>
+        <v>0.2082215536537118</v>
       </c>
       <c r="U43">
-        <v>1.061044944927652E-05</v>
+        <v>1.061050320862189E-05</v>
       </c>
       <c r="V43">
-        <v>0.2474846319089718</v>
+        <v>0.2474846319081728</v>
       </c>
       <c r="W43">
-        <v>1.762531035009725E-07</v>
+        <v>1.762666022693574E-07</v>
       </c>
     </row>
     <row r="44">
@@ -7740,37 +7740,37 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>2.538140299683228</v>
+        <v>2.538140299683223</v>
       </c>
       <c r="H44">
-        <v>2.586284951871236</v>
+        <v>2.586284951871228</v>
       </c>
       <c r="I44">
-        <v>0.04814465218800856</v>
+        <v>0.04814465218800511</v>
       </c>
       <c r="J44">
-        <v>0.04326797383925318</v>
+        <v>0.0432679738392537</v>
       </c>
       <c r="K44">
         <v>3</v>
       </c>
       <c r="L44">
-        <v>-0.08955335129383485</v>
+        <v>-0.08955335129383994</v>
       </c>
       <c r="M44">
-        <v>0.185842655669852</v>
+        <v>0.1858426556698501</v>
       </c>
       <c r="N44">
-        <v>1.896847553857336</v>
+        <v>1.896847553857203</v>
       </c>
       <c r="O44">
-        <v>0.3469707721733717</v>
+        <v>0.3469707721734031</v>
       </c>
       <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0.7680312217992304</v>
+        <v>0.7680312217998135</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -7781,16 +7781,16 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>0.1515341484476359</v>
+        <v>0.1515341484457677</v>
       </c>
       <c r="U44">
-        <v>1.078021459609665E-05</v>
+        <v>1.078007767749796E-05</v>
       </c>
       <c r="V44">
-        <v>0.2356415116585248</v>
+        <v>0.2356415116586208</v>
       </c>
       <c r="W44">
-        <v>7.588110882760172E-35</v>
+        <v>7.488341161604567E-35</v>
       </c>
     </row>
     <row r="45">
@@ -7823,37 +7823,37 @@
         <v>1</v>
       </c>
       <c r="G45">
-        <v>2.538140299683226</v>
+        <v>2.538140299683234</v>
       </c>
       <c r="H45">
-        <v>2.640380226043094</v>
+        <v>2.640380226043109</v>
       </c>
       <c r="I45">
-        <v>0.1022399263598679</v>
+        <v>0.1022399263598751</v>
       </c>
       <c r="J45">
-        <v>0.04311210817496341</v>
+        <v>0.04311210817494532</v>
       </c>
       <c r="K45">
         <v>3</v>
       </c>
       <c r="L45">
-        <v>-0.03496204301453591</v>
+        <v>-0.03496204301447114</v>
       </c>
       <c r="M45">
-        <v>0.2394418957342717</v>
+        <v>0.2394418957342214</v>
       </c>
       <c r="N45">
-        <v>4.0281432185852</v>
+        <v>4.02814321858547</v>
       </c>
       <c r="O45">
-        <v>0.09837134235166967</v>
+        <v>0.09837134235156719</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0.5294091879953482</v>
+        <v>0.5294091879943162</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -7864,16 +7864,16 @@
         <v>0</v>
       </c>
       <c r="T45">
-        <v>0.1467270453113538</v>
+        <v>0.1467270453135921</v>
       </c>
       <c r="U45">
-        <v>6.433555858032521E-06</v>
+        <v>6.433596662958342E-06</v>
       </c>
       <c r="V45">
-        <v>0.2347928400546581</v>
+        <v>0.2347928400545427</v>
       </c>
       <c r="W45">
-        <v>1.578499308437495E-20</v>
+        <v>1.577800434419853E-20</v>
       </c>
     </row>
     <row r="46">
@@ -7906,37 +7906,37 @@
         <v>1</v>
       </c>
       <c r="G46">
-        <v>2.538140299683227</v>
+        <v>2.538140299683226</v>
       </c>
       <c r="H46">
-        <v>2.697934368694882</v>
+        <v>2.697934368694944</v>
       </c>
       <c r="I46">
-        <v>0.1597940690116546</v>
+        <v>0.1597940690117191</v>
       </c>
       <c r="J46">
-        <v>0.04515801808724427</v>
+        <v>0.0451580180870263</v>
       </c>
       <c r="K46">
         <v>3</v>
       </c>
       <c r="L46">
-        <v>0.01608110119596926</v>
+        <v>0.0160811011967274</v>
       </c>
       <c r="M46">
-        <v>0.30350703682734</v>
+        <v>0.3035070368267108</v>
       </c>
       <c r="N46">
-        <v>6.295714584083383</v>
+        <v>6.295714584085927</v>
       </c>
       <c r="O46">
-        <v>0.03840340273559473</v>
+        <v>0.03840340273508602</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0.3531781092826729</v>
+        <v>0.3531781092717563</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -7947,16 +7947,16 @@
         <v>1</v>
       </c>
       <c r="T46">
-        <v>0.1537915796924391</v>
+        <v>0.1537915797164838</v>
       </c>
       <c r="U46">
-        <v>8.404839976621E-06</v>
+        <v>8.404980639363739E-06</v>
       </c>
       <c r="V46">
-        <v>0.2431636978254815</v>
+        <v>0.2431636978242331</v>
       </c>
       <c r="W46">
-        <v>6.965466081998401E-14</v>
+        <v>6.962113799093861E-14</v>
       </c>
     </row>
     <row r="47">
@@ -7989,37 +7989,37 @@
         <v>1</v>
       </c>
       <c r="G47">
-        <v>6.848290622806104</v>
+        <v>6.848290622803901</v>
       </c>
       <c r="H47">
-        <v>5.441696710889639</v>
+        <v>5.441696710889643</v>
       </c>
       <c r="I47">
-        <v>-1.406593911916465</v>
+        <v>-1.406593911914258</v>
       </c>
       <c r="J47">
-        <v>0.9388554700839137</v>
+        <v>0.9388554701954553</v>
       </c>
       <c r="K47">
         <v>3</v>
       </c>
       <c r="L47">
-        <v>-4.394451033880415</v>
+        <v>-4.394451034233184</v>
       </c>
       <c r="M47">
-        <v>1.581263210047484</v>
+        <v>1.581263210404667</v>
       </c>
       <c r="N47">
-        <v>-20.53934316444225</v>
+        <v>-20.53934316441663</v>
       </c>
       <c r="O47">
-        <v>0.2310162060949046</v>
+        <v>0.2310162061382826</v>
       </c>
       <c r="P47">
-        <v>0.001147655820704196</v>
+        <v>0.001147655820493254</v>
       </c>
       <c r="Q47">
-        <v>0.7522300431538997</v>
+        <v>0.7522300431411013</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -8030,16 +8030,16 @@
         <v>0</v>
       </c>
       <c r="T47">
-        <v>0.0001696739183667463</v>
+        <v>0.0001696603883548957</v>
       </c>
       <c r="U47">
-        <v>0.7043926674745991</v>
+        <v>0.704392667787722</v>
       </c>
       <c r="V47">
-        <v>4.334532267039343</v>
+        <v>4.334532267002111</v>
       </c>
       <c r="W47">
-        <v>0.001473560510274669</v>
+        <v>0.001473445386142282</v>
       </c>
     </row>
     <row r="48">
@@ -8072,37 +8072,37 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>6.85296048599002</v>
+        <v>6.852960485995165</v>
       </c>
       <c r="H48">
-        <v>6.591158548346779</v>
+        <v>6.591158548346657</v>
       </c>
       <c r="I48">
-        <v>-0.2618019376432418</v>
+        <v>-0.2618019376485092</v>
       </c>
       <c r="J48">
-        <v>0.8949743110348225</v>
+        <v>0.8949743110770713</v>
       </c>
       <c r="K48">
         <v>3</v>
       </c>
       <c r="L48">
-        <v>-3.110009627119845</v>
+        <v>-3.110009627259566</v>
       </c>
       <c r="M48">
-        <v>2.586405751833361</v>
+        <v>2.586405751962548</v>
       </c>
       <c r="N48">
-        <v>-3.820275020970303</v>
+        <v>-3.820275021044297</v>
       </c>
       <c r="O48">
-        <v>0.788950567247475</v>
+        <v>0.7889505672529816</v>
       </c>
       <c r="P48">
-        <v>0.01049884660837797</v>
+        <v>0.0104988466107595</v>
       </c>
       <c r="Q48">
-        <v>0.9313837563336225</v>
+        <v>0.9313837563421024</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -8113,16 +8113,16 @@
         <v>0</v>
       </c>
       <c r="T48">
-        <v>0.5555110355306663</v>
+        <v>0.5555110352850318</v>
       </c>
       <c r="U48">
-        <v>0.0002226524409372536</v>
+        <v>0.0002226720112165021</v>
       </c>
       <c r="V48">
-        <v>4.691700290034032</v>
+        <v>4.691700290063939</v>
       </c>
       <c r="W48">
-        <v>0.4044534384408248</v>
+        <v>0.4044534385610952</v>
       </c>
     </row>
     <row r="49">
@@ -8155,37 +8155,37 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>6.591660462000718</v>
+        <v>6.591660461972968</v>
       </c>
       <c r="H49">
-        <v>6.053370927575157</v>
+        <v>6.053370927566542</v>
       </c>
       <c r="I49">
-        <v>-0.5382895344255604</v>
+        <v>-0.5382895344064257</v>
       </c>
       <c r="J49">
-        <v>0.6045762189487724</v>
+        <v>0.6045762190477729</v>
       </c>
       <c r="K49">
         <v>3</v>
       </c>
       <c r="L49">
-        <v>-2.462320888681475</v>
+        <v>-2.462320888977404</v>
       </c>
       <c r="M49">
-        <v>1.385741819830355</v>
+        <v>1.385741820164553</v>
       </c>
       <c r="N49">
-        <v>-8.166220598416219</v>
+        <v>-8.166220598160313</v>
       </c>
       <c r="O49">
-        <v>0.4388653682256807</v>
+        <v>0.4388653683072901</v>
       </c>
       <c r="P49">
-        <v>0.03234940551320209</v>
+        <v>0.03234940551171972</v>
       </c>
       <c r="Q49">
-        <v>0.9997089461463154</v>
+        <v>0.9997089461462456</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -8196,16 +8196,16 @@
         <v>0</v>
       </c>
       <c r="T49">
-        <v>0.8482979060135416</v>
+        <v>0.8482979057518689</v>
       </c>
       <c r="U49">
-        <v>1.032011499291239E-06</v>
+        <v>1.03242320365715E-06</v>
       </c>
       <c r="V49">
-        <v>3.292743782125353</v>
+        <v>3.292743782160414</v>
       </c>
       <c r="W49">
-        <v>0.01017631574701714</v>
+        <v>0.01017767387959923</v>
       </c>
     </row>
     <row r="50">
@@ -8238,37 +8238,37 @@
         <v>1</v>
       </c>
       <c r="G50">
-        <v>6.591163326493771</v>
+        <v>6.591163326493835</v>
       </c>
       <c r="H50">
-        <v>6.437592986622431</v>
+        <v>6.437592986621416</v>
       </c>
       <c r="I50">
-        <v>-0.1535703398713409</v>
+        <v>-0.1535703398724186</v>
       </c>
       <c r="J50">
-        <v>0.6476159501841904</v>
+        <v>0.6476159501703926</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50">
-        <v>-2.214573327777816</v>
+        <v>-2.214573327734982</v>
       </c>
       <c r="M50">
-        <v>1.907432648035134</v>
+        <v>1.907432647990145</v>
       </c>
       <c r="N50">
-        <v>-2.329942868416736</v>
+        <v>-2.329942868433063</v>
       </c>
       <c r="O50">
-        <v>0.8278253196050767</v>
+        <v>0.8278253196003207</v>
       </c>
       <c r="P50">
-        <v>0.03569133451614737</v>
+        <v>0.0356913345172174</v>
       </c>
       <c r="Q50">
-        <v>0.6219832346611236</v>
+        <v>0.6219832346644401</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -8279,16 +8279,16 @@
         <v>0</v>
       </c>
       <c r="T50">
-        <v>0.4178949391316461</v>
+        <v>0.4178949390046705</v>
       </c>
       <c r="U50">
-        <v>0.0002049121693434036</v>
+        <v>0.0002049067527487142</v>
       </c>
       <c r="V50">
-        <v>3.40922191962078</v>
+        <v>3.409221919627245</v>
       </c>
       <c r="W50">
-        <v>0.3907137829158505</v>
+        <v>0.3907137828408926</v>
       </c>
     </row>
     <row r="51">
@@ -8321,37 +8321,37 @@
         <v>1</v>
       </c>
       <c r="G51">
-        <v>6.59158001012565</v>
+        <v>6.59158001013266</v>
       </c>
       <c r="H51">
-        <v>6.242144985201877</v>
+        <v>6.242144985203292</v>
       </c>
       <c r="I51">
-        <v>-0.3494350249237726</v>
+        <v>-0.3494350249293684</v>
       </c>
       <c r="J51">
-        <v>0.6154101807456512</v>
+        <v>0.6154101806493649</v>
       </c>
       <c r="K51">
         <v>3</v>
       </c>
       <c r="L51">
-        <v>-2.307944880871749</v>
+        <v>-2.307944880570919</v>
       </c>
       <c r="M51">
-        <v>1.609074831024204</v>
+        <v>1.609074830712182</v>
       </c>
       <c r="N51">
-        <v>-5.301233154827648</v>
+        <v>-5.301233154906902</v>
       </c>
       <c r="O51">
-        <v>0.6098816503173572</v>
+        <v>0.6098816502586638</v>
       </c>
       <c r="P51">
-        <v>0.0451666505899091</v>
+        <v>0.04516665057248748</v>
       </c>
       <c r="Q51">
-        <v>0.5475309935857016</v>
+        <v>0.547530993451675</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -8362,16 +8362,16 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>0.3244914924248572</v>
+        <v>0.3244914930714116</v>
       </c>
       <c r="U51">
-        <v>0.000896951675221648</v>
+        <v>0.000896952497384903</v>
       </c>
       <c r="V51">
-        <v>3.311514875500126</v>
+        <v>3.311514875445636</v>
       </c>
       <c r="W51">
-        <v>0.1393926278953399</v>
+        <v>0.1393926226377443</v>
       </c>
     </row>
     <row r="52">
@@ -8404,37 +8404,37 @@
         <v>1</v>
       </c>
       <c r="G52">
-        <v>0.3153365870082135</v>
+        <v>0.315336587008214</v>
       </c>
       <c r="H52">
-        <v>0.3159451172153055</v>
+        <v>0.3159451172153056</v>
       </c>
       <c r="I52">
-        <v>0.0006085302070919936</v>
+        <v>0.000608530207091618</v>
       </c>
       <c r="J52">
-        <v>0.0009012963075103166</v>
+        <v>0.0009012963073971902</v>
       </c>
       <c r="K52">
         <v>3</v>
       </c>
       <c r="L52">
-        <v>-0.002259796896710062</v>
+        <v>-0.002259796896350418</v>
       </c>
       <c r="M52">
-        <v>0.003476857310894049</v>
+        <v>0.003476857310533655</v>
       </c>
       <c r="N52">
-        <v>0.1929779899203841</v>
+        <v>0.1929779899202647</v>
       </c>
       <c r="O52">
-        <v>0.5479469244852728</v>
+        <v>0.5479469244385434</v>
       </c>
       <c r="P52">
-        <v>0.5278068224242688</v>
+        <v>0.5278068224571375</v>
       </c>
       <c r="Q52">
-        <v>0.5518506953633422</v>
+        <v>0.5518506953782982</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -8445,16 +8445,16 @@
         <v>0</v>
       </c>
       <c r="T52">
-        <v>1.866262540839544E-07</v>
+        <v>1.869069812036049E-07</v>
       </c>
       <c r="U52">
-        <v>5.863810682847987E-08</v>
+        <v>5.874039267512797E-08</v>
       </c>
       <c r="V52">
-        <v>0.003974797638334275</v>
+        <v>0.003974797638232185</v>
       </c>
       <c r="W52">
-        <v>0.6626581820516271</v>
+        <v>0.6626581819626366</v>
       </c>
     </row>
     <row r="53">
@@ -8487,37 +8487,37 @@
         <v>1</v>
       </c>
       <c r="G53">
-        <v>0.3153355993269266</v>
+        <v>0.3153355993272437</v>
       </c>
       <c r="H53">
-        <v>0.3157231349448583</v>
+        <v>0.3157231349461231</v>
       </c>
       <c r="I53">
-        <v>0.0003875356179316792</v>
+        <v>0.0003875356188793529</v>
       </c>
       <c r="J53">
-        <v>0.0009442373966484307</v>
+        <v>0.0009442374299881536</v>
       </c>
       <c r="K53">
         <v>3</v>
       </c>
       <c r="L53">
-        <v>-0.002617449196342826</v>
+        <v>-0.00261744930149703</v>
       </c>
       <c r="M53">
-        <v>0.003392520432206184</v>
+        <v>0.003392520539255736</v>
       </c>
       <c r="N53">
-        <v>0.1228962472866563</v>
+        <v>0.1228962475870612</v>
       </c>
       <c r="O53">
-        <v>0.7090485268710752</v>
+        <v>0.7090485357599001</v>
       </c>
       <c r="P53">
-        <v>0.004960061780001634</v>
+        <v>0.004960061082535661</v>
       </c>
       <c r="Q53">
-        <v>0.3458447435348703</v>
+        <v>0.3458447272586079</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -8528,16 +8528,16 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>0.0002129661770556073</v>
+        <v>0.0002129659157101916</v>
       </c>
       <c r="U53">
-        <v>1.777906671431392E-06</v>
+        <v>1.777067762232534E-06</v>
       </c>
       <c r="V53">
-        <v>0.003868360726175327</v>
+        <v>0.003868360764759008</v>
       </c>
       <c r="W53">
-        <v>0.7134183815953973</v>
+        <v>0.7134183998808797</v>
       </c>
     </row>
     <row r="54">
@@ -8570,37 +8570,37 @@
         <v>1</v>
       </c>
       <c r="G54">
-        <v>0.3157230535705683</v>
+        <v>0.3157230535705502</v>
       </c>
       <c r="H54">
-        <v>0.3154075004466768</v>
+        <v>0.3154075004466786</v>
       </c>
       <c r="I54">
-        <v>-0.0003155531238915595</v>
+        <v>-0.0003155531238716422</v>
       </c>
       <c r="J54">
-        <v>0.00121538529617114</v>
+        <v>0.001215385295587757</v>
       </c>
       <c r="K54">
         <v>3</v>
       </c>
       <c r="L54">
-        <v>-0.00418345156918755</v>
+        <v>-0.004183451567311045</v>
       </c>
       <c r="M54">
-        <v>0.003552345321404431</v>
+        <v>0.003552345319567761</v>
       </c>
       <c r="N54">
-        <v>-0.09994617761449882</v>
+        <v>-0.09994617760819607</v>
       </c>
       <c r="O54">
-        <v>0.8119454255999564</v>
+        <v>0.8119454255237746</v>
       </c>
       <c r="P54">
-        <v>5.701614397901622E-05</v>
+        <v>5.701614414843625E-05</v>
       </c>
       <c r="Q54">
-        <v>0.04229615594091818</v>
+        <v>0.04229615597581859</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -8611,16 +8611,16 @@
         <v>0</v>
       </c>
       <c r="T54">
-        <v>1.189408923508858E-06</v>
+        <v>1.189696786237807E-06</v>
       </c>
       <c r="U54">
-        <v>1.667889245460987E-08</v>
+        <v>1.668466918898754E-08</v>
       </c>
       <c r="V54">
-        <v>0.005050414898735915</v>
+        <v>0.00505041489817106</v>
       </c>
       <c r="W54">
-        <v>0.7031866242503675</v>
+        <v>0.7031866239805585</v>
       </c>
     </row>
     <row r="55">
@@ -8653,37 +8653,37 @@
         <v>1</v>
       </c>
       <c r="G55">
-        <v>0.3157046821594313</v>
+        <v>0.3157046821594244</v>
       </c>
       <c r="H55">
-        <v>0.3162806761833875</v>
+        <v>0.3162806761833847</v>
       </c>
       <c r="I55">
-        <v>0.0005759940239561061</v>
+        <v>0.0005759940239603648</v>
       </c>
       <c r="J55">
-        <v>0.0007732939981516492</v>
+        <v>0.0007732939981426408</v>
       </c>
       <c r="K55">
         <v>3</v>
       </c>
       <c r="L55">
-        <v>-0.001884972603359676</v>
+        <v>-0.001884972603326749</v>
       </c>
       <c r="M55">
-        <v>0.003036960651271888</v>
+        <v>0.003036960651247478</v>
       </c>
       <c r="N55">
-        <v>0.1824470958163453</v>
+        <v>0.1824470958176983</v>
       </c>
       <c r="O55">
-        <v>0.510401006251353</v>
+        <v>0.5104010062440915</v>
       </c>
       <c r="P55">
-        <v>0.01972209931570124</v>
+        <v>0.01972209931172753</v>
       </c>
       <c r="Q55">
-        <v>0.9165832287037617</v>
+        <v>0.916583228695367</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -8694,16 +8694,16 @@
         <v>0</v>
       </c>
       <c r="T55">
-        <v>0.000860573164816012</v>
+        <v>0.0008605731654238511</v>
       </c>
       <c r="U55">
-        <v>1.703832976428355E-07</v>
+        <v>1.703986438653003E-07</v>
       </c>
       <c r="V55">
-        <v>0.004143841892857442</v>
+        <v>0.004143841892799715</v>
       </c>
       <c r="W55">
-        <v>7.856510003764466E-64</v>
+        <v>7.898994042120962E-64</v>
       </c>
     </row>
     <row r="56">
@@ -8736,37 +8736,37 @@
         <v>1</v>
       </c>
       <c r="G56">
-        <v>0.3157231357166116</v>
+        <v>0.3157231357166184</v>
       </c>
       <c r="H56">
-        <v>0.3151123796484233</v>
+        <v>0.3151123796484406</v>
       </c>
       <c r="I56">
-        <v>-0.0006107560681883037</v>
+        <v>-0.0006107560681777322</v>
       </c>
       <c r="J56">
-        <v>0.001216761001410712</v>
+        <v>0.001216761001392869</v>
       </c>
       <c r="K56">
         <v>3</v>
       </c>
       <c r="L56">
-        <v>-0.004483032621541129</v>
+        <v>-0.004483032621473771</v>
       </c>
       <c r="M56">
-        <v>0.003261520485164522</v>
+        <v>0.003261520485118307</v>
       </c>
       <c r="N56">
-        <v>-0.1934467256579224</v>
+        <v>-0.1934467256545699</v>
       </c>
       <c r="O56">
-        <v>0.6502258100567</v>
+        <v>0.6502258100576246</v>
       </c>
       <c r="P56">
-        <v>0.07013399335151482</v>
+        <v>0.0701339933399493</v>
       </c>
       <c r="Q56">
-        <v>0.5368706021608186</v>
+        <v>0.5368706021295284</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -8777,13 +8777,13 @@
         <v>0</v>
       </c>
       <c r="T56">
-        <v>0.001163103106423304</v>
+        <v>0.001163103107385138</v>
       </c>
       <c r="U56">
-        <v>2.882279882673617E-07</v>
+        <v>2.882195261948886E-07</v>
       </c>
       <c r="V56">
-        <v>0.006484610301817457</v>
+        <v>0.006484610301725857</v>
       </c>
       <c r="W56">
         <v>0</v>
@@ -8819,37 +8819,37 @@
         <v>1</v>
       </c>
       <c r="G57">
-        <v>430.0425100089752</v>
+        <v>430.0425100089135</v>
       </c>
       <c r="H57">
-        <v>436.428524200925</v>
+        <v>436.4285242009247</v>
       </c>
       <c r="I57">
-        <v>6.38601419194977</v>
+        <v>6.386014192011181</v>
       </c>
       <c r="J57">
-        <v>9.578863921583523</v>
+        <v>9.578863918604011</v>
       </c>
       <c r="K57">
         <v>3</v>
       </c>
       <c r="L57">
-        <v>-24.09820590410912</v>
+        <v>-24.09820589456557</v>
       </c>
       <c r="M57">
-        <v>36.87023428800866</v>
+        <v>36.87023427858793</v>
       </c>
       <c r="N57">
-        <v>1.484972774393045</v>
+        <v>1.484972774407539</v>
       </c>
       <c r="O57">
-        <v>0.5526682063523424</v>
+        <v>0.5526682062331189</v>
       </c>
       <c r="P57">
-        <v>9.838599100975287E-07</v>
+        <v>9.838599082101496E-07</v>
       </c>
       <c r="Q57">
-        <v>0.9724332632352244</v>
+        <v>0.9724332632279405</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -8860,16 +8860,16 @@
         <v>0</v>
       </c>
       <c r="T57">
-        <v>9.766564970421994</v>
+        <v>9.766564989987234</v>
       </c>
       <c r="U57">
-        <v>6.393435703618719</v>
+        <v>6.393435697204969</v>
       </c>
       <c r="V57">
-        <v>28.58440526669363</v>
+        <v>28.5844052651175</v>
       </c>
       <c r="W57">
-        <v>0.8175426806418415</v>
+        <v>0.817542680618315</v>
       </c>
     </row>
     <row r="58">
@@ -8902,37 +8902,37 @@
         <v>1</v>
       </c>
       <c r="G58">
-        <v>430.2111944878761</v>
+        <v>430.2111944878837</v>
       </c>
       <c r="H58">
-        <v>409.7197413723746</v>
+        <v>409.719741372384</v>
       </c>
       <c r="I58">
-        <v>-20.49145311550153</v>
+        <v>-20.49145311549982</v>
       </c>
       <c r="J58">
-        <v>3.65953245729074</v>
+        <v>3.659532457323773</v>
       </c>
       <c r="K58">
         <v>3</v>
       </c>
       <c r="L58">
-        <v>-32.13771866327225</v>
+        <v>-32.13771866337567</v>
       </c>
       <c r="M58">
-        <v>-8.845187567730809</v>
+        <v>-8.845187567623974</v>
       </c>
       <c r="N58">
-        <v>-4.763114809203089</v>
+        <v>-4.763114809202607</v>
       </c>
       <c r="O58">
-        <v>0.01125339679424764</v>
+        <v>0.01125339679453341</v>
       </c>
       <c r="P58">
         <v>1.554312234475219E-14</v>
       </c>
       <c r="Q58">
-        <v>0.6943840068632192</v>
+        <v>0.6943840068664153</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -8943,16 +8943,16 @@
         <v>1</v>
       </c>
       <c r="T58">
-        <v>7.791175452312109</v>
+        <v>7.791175451652052</v>
       </c>
       <c r="U58">
-        <v>0.001900912141996036</v>
+        <v>0.001901006866306922</v>
       </c>
       <c r="V58">
-        <v>19.60900153079593</v>
+        <v>19.60900153084086</v>
       </c>
       <c r="W58">
-        <v>1.516613109513699E-08</v>
+        <v>1.51711935354114E-08</v>
       </c>
     </row>
     <row r="59">
@@ -8985,37 +8985,37 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>409.6221705240998</v>
+        <v>409.622170524124</v>
       </c>
       <c r="H59">
-        <v>400.7567577842041</v>
+        <v>400.7567577842185</v>
       </c>
       <c r="I59">
-        <v>-8.865412739895726</v>
+        <v>-8.86541273990559</v>
       </c>
       <c r="J59">
-        <v>4.429857669673783</v>
+        <v>4.429857669730576</v>
       </c>
       <c r="K59">
         <v>3</v>
       </c>
       <c r="L59">
-        <v>-22.96319691368175</v>
+        <v>-22.96319691387236</v>
       </c>
       <c r="M59">
-        <v>5.2323714338903</v>
+        <v>5.232371434061177</v>
       </c>
       <c r="N59">
-        <v>-2.164290260107915</v>
+        <v>-2.164290260110195</v>
       </c>
       <c r="O59">
-        <v>0.1391524428721533</v>
+        <v>0.1391524428753107</v>
       </c>
       <c r="P59">
         <v>1.998401444325282E-15</v>
       </c>
       <c r="Q59">
-        <v>0.981373034243701</v>
+        <v>0.9813730342446082</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -9026,16 +9026,16 @@
         <v>0</v>
       </c>
       <c r="T59">
-        <v>9.928060706650204</v>
+        <v>9.928060705068173</v>
       </c>
       <c r="U59">
-        <v>0.001166043017281025</v>
+        <v>0.0011663166488086</v>
       </c>
       <c r="V59">
-        <v>23.73657677077998</v>
+        <v>23.73657677089098</v>
       </c>
       <c r="W59">
-        <v>4.447460214716355E-06</v>
+        <v>4.450583619880312E-06</v>
       </c>
     </row>
     <row r="60">
@@ -9068,37 +9068,37 @@
         <v>1</v>
       </c>
       <c r="G60">
-        <v>409.6276692313696</v>
+        <v>409.627669231335</v>
       </c>
       <c r="H60">
-        <v>397.4039510399183</v>
+        <v>397.4039510398969</v>
       </c>
       <c r="I60">
-        <v>-12.22371819145127</v>
+        <v>-12.2237181914381</v>
       </c>
       <c r="J60">
-        <v>4.260233123261384</v>
+        <v>4.26023312324332</v>
       </c>
       <c r="K60">
         <v>3</v>
       </c>
       <c r="L60">
-        <v>-25.78168135422173</v>
+        <v>-25.78168135415108</v>
       </c>
       <c r="M60">
-        <v>1.334244971319192</v>
+        <v>1.33424497127487</v>
       </c>
       <c r="N60">
-        <v>-2.984104617343844</v>
+        <v>-2.984104617340882</v>
       </c>
       <c r="O60">
-        <v>0.06408908599892915</v>
+        <v>0.06408908599845142</v>
       </c>
       <c r="P60">
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0.8915837031122363</v>
+        <v>0.8915837031056246</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -9109,16 +9109,16 @@
         <v>0</v>
       </c>
       <c r="T60">
-        <v>10.31233309575644</v>
+        <v>10.31233309826335</v>
       </c>
       <c r="U60">
-        <v>0.001197997497276893</v>
+        <v>0.001198096178399145</v>
       </c>
       <c r="V60">
-        <v>22.82756009919908</v>
+        <v>22.82756009902734</v>
       </c>
       <c r="W60">
-        <v>1.655888002363566E-06</v>
+        <v>1.656251806462896E-06</v>
       </c>
     </row>
     <row r="61">
@@ -9151,37 +9151,37 @@
         <v>1</v>
       </c>
       <c r="G61">
-        <v>409.6140990578638</v>
+        <v>409.6140990578524</v>
       </c>
       <c r="H61">
-        <v>390.5933372272714</v>
+        <v>390.593337227264</v>
       </c>
       <c r="I61">
-        <v>-19.02076183059244</v>
+        <v>-19.02076183058843</v>
       </c>
       <c r="J61">
-        <v>4.098041476080591</v>
+        <v>4.098041476069388</v>
       </c>
       <c r="K61">
         <v>3</v>
       </c>
       <c r="L61">
-        <v>-32.06255878504451</v>
+        <v>-32.06255878500485</v>
       </c>
       <c r="M61">
-        <v>-5.978964876140372</v>
+        <v>-5.978964876172014</v>
       </c>
       <c r="N61">
-        <v>-4.643580842149062</v>
+        <v>-4.643580842148212</v>
       </c>
       <c r="O61">
-        <v>0.0188502051065631</v>
+        <v>0.01885020510643454</v>
       </c>
       <c r="P61">
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0.2323660201964053</v>
+        <v>0.2323660201923865</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -9192,16 +9192,16 @@
         <v>1</v>
       </c>
       <c r="T61">
-        <v>9.886247682603386</v>
+        <v>9.88624768341209</v>
       </c>
       <c r="U61">
-        <v>0.001334008897427888</v>
+        <v>0.001334003575691423</v>
       </c>
       <c r="V61">
-        <v>21.83446937293683</v>
+        <v>21.83446937288144</v>
       </c>
       <c r="W61">
-        <v>3.228114732745678E-05</v>
+        <v>3.2284563039027E-05</v>
       </c>
     </row>
     <row r="62">
@@ -9234,37 +9234,37 @@
         <v>1</v>
       </c>
       <c r="G62">
-        <v>1.948222356401741</v>
+        <v>1.948222356401677</v>
       </c>
       <c r="H62">
-        <v>1.952893290192556</v>
+        <v>1.952893290192558</v>
       </c>
       <c r="I62">
-        <v>0.004670933790814945</v>
+        <v>0.004670933790880949</v>
       </c>
       <c r="J62">
-        <v>0.003591675349732499</v>
+        <v>0.003591675349615229</v>
       </c>
       <c r="K62">
         <v>3</v>
       </c>
       <c r="L62">
-        <v>-0.006759380155719816</v>
+        <v>-0.006759380155280606</v>
       </c>
       <c r="M62">
-        <v>0.01610124773734971</v>
+        <v>0.0161012477370425</v>
       </c>
       <c r="N62">
-        <v>0.2397536285048028</v>
+        <v>0.2397536285081986</v>
       </c>
       <c r="O62">
-        <v>0.2843205093377064</v>
+        <v>0.2843205093194051</v>
       </c>
       <c r="P62">
         <v>6.776257333029889E-11</v>
       </c>
       <c r="Q62">
-        <v>0.9983910750317936</v>
+        <v>0.9983910750305389</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -9275,16 +9275,16 @@
         <v>0</v>
       </c>
       <c r="T62">
-        <v>0.01592514432654245</v>
+        <v>0.01592514436943529</v>
       </c>
       <c r="U62">
-        <v>5.192562383726642E-07</v>
+        <v>5.286292923509553E-07</v>
       </c>
       <c r="V62">
-        <v>0.01715441148839713</v>
+        <v>0.01715441148647065</v>
       </c>
       <c r="W62">
-        <v>0.5803028079595449</v>
+        <v>0.5803028078203827</v>
       </c>
     </row>
     <row r="63">
@@ -9317,37 +9317,37 @@
         <v>1</v>
       </c>
       <c r="G63">
-        <v>1.948268149331444</v>
+        <v>1.948268149331924</v>
       </c>
       <c r="H63">
-        <v>1.943024357262547</v>
+        <v>1.943024357263128</v>
       </c>
       <c r="I63">
-        <v>-0.005243792068897846</v>
+        <v>-0.00524379206879628</v>
       </c>
       <c r="J63">
-        <v>0.00395341135296859</v>
+        <v>0.003953411392643144</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63">
-        <v>-0.0178253114224194</v>
+        <v>-0.01782531154857997</v>
       </c>
       <c r="M63">
-        <v>0.007337727284623705</v>
+        <v>0.007337727410987411</v>
       </c>
       <c r="N63">
-        <v>-0.2691514548804421</v>
+        <v>-0.2691514548751626</v>
       </c>
       <c r="O63">
-        <v>0.2766432049024888</v>
+        <v>0.2766432087978002</v>
       </c>
       <c r="P63">
         <v>1.913775804496254E-10</v>
       </c>
       <c r="Q63">
-        <v>0.9936804683851606</v>
+        <v>0.9936804682547112</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -9358,16 +9358,16 @@
         <v>0</v>
       </c>
       <c r="T63">
-        <v>0.01423032159608152</v>
+        <v>0.01423032162681809</v>
       </c>
       <c r="U63">
-        <v>3.872702853816933E-07</v>
+        <v>5.376115281604507E-07</v>
       </c>
       <c r="V63">
-        <v>0.01725347763232016</v>
+        <v>0.0172534776599471</v>
       </c>
       <c r="W63">
-        <v>0.6639040904267909</v>
+        <v>0.6639040958908912</v>
       </c>
     </row>
     <row r="64">
@@ -9400,37 +9400,37 @@
         <v>1</v>
       </c>
       <c r="G64">
-        <v>1.943039652383848</v>
+        <v>1.943039652383867</v>
       </c>
       <c r="H64">
-        <v>1.941265305603689</v>
+        <v>1.941265305603797</v>
       </c>
       <c r="I64">
-        <v>-0.001774346780159246</v>
+        <v>-0.00177434678006975</v>
       </c>
       <c r="J64">
-        <v>0.004339328273256299</v>
+        <v>0.004339328278691033</v>
       </c>
       <c r="K64">
         <v>3</v>
       </c>
       <c r="L64">
-        <v>-0.01558402601079689</v>
+        <v>-0.01558402602800314</v>
       </c>
       <c r="M64">
-        <v>0.01203533245047839</v>
+        <v>0.01203533246786364</v>
       </c>
       <c r="N64">
-        <v>-0.09131809420267679</v>
+        <v>-0.09131809419806994</v>
       </c>
       <c r="O64">
-        <v>0.7100525161946403</v>
+        <v>0.7100525165459641</v>
       </c>
       <c r="P64">
         <v>4.154676602752261E-12</v>
       </c>
       <c r="Q64">
-        <v>0.9999468365282022</v>
+        <v>0.99994683652827</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -9441,16 +9441,16 @@
         <v>0</v>
       </c>
       <c r="T64">
-        <v>0.01357137758440435</v>
+        <v>0.01357137757161643</v>
       </c>
       <c r="U64">
-        <v>5.527996758154257E-07</v>
+        <v>5.93773902386992E-07</v>
       </c>
       <c r="V64">
-        <v>0.0167728681833216</v>
+        <v>0.01677286818663838</v>
       </c>
       <c r="W64">
-        <v>0.7504836361725349</v>
+        <v>0.7504836364244967</v>
       </c>
     </row>
     <row r="65">
@@ -9483,37 +9483,37 @@
         <v>1</v>
       </c>
       <c r="G65">
-        <v>1.943056409485904</v>
+        <v>1.943056409485883</v>
       </c>
       <c r="H65">
-        <v>1.939257543721848</v>
+        <v>1.939257543721702</v>
       </c>
       <c r="I65">
-        <v>-0.003798865764056357</v>
+        <v>-0.003798865764180969</v>
       </c>
       <c r="J65">
-        <v>0.003881662319766748</v>
+        <v>0.003881662316996381</v>
       </c>
       <c r="K65">
         <v>3</v>
       </c>
       <c r="L65">
-        <v>-0.01615204767195703</v>
+        <v>-0.0161520476632651</v>
       </c>
       <c r="M65">
-        <v>0.008554316143844314</v>
+        <v>0.008554316134903159</v>
       </c>
       <c r="N65">
-        <v>-0.1955098032929196</v>
+        <v>-0.1955098032993349</v>
       </c>
       <c r="O65">
-        <v>0.3999165719756286</v>
+        <v>0.3999165716671191</v>
       </c>
       <c r="P65">
         <v>2.005284827077958E-09</v>
       </c>
       <c r="Q65">
-        <v>0.9991148718578572</v>
+        <v>0.999114871858075</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -9524,16 +9524,16 @@
         <v>0</v>
       </c>
       <c r="T65">
-        <v>0.01186007359014262</v>
+        <v>0.01186007359056078</v>
       </c>
       <c r="U65">
-        <v>5.989753612094821E-07</v>
+        <v>5.991932744776056E-07</v>
       </c>
       <c r="V65">
-        <v>0.01632935563743027</v>
+        <v>0.01632935563465338</v>
       </c>
       <c r="W65">
-        <v>0.6939229874032908</v>
+        <v>0.6939229869839398</v>
       </c>
     </row>
     <row r="66">
@@ -9566,37 +9566,37 @@
         <v>1</v>
       </c>
       <c r="G66">
-        <v>1.943043816760048</v>
+        <v>1.943043816759888</v>
       </c>
       <c r="H66">
-        <v>1.936367353769539</v>
+        <v>1.936367353770543</v>
       </c>
       <c r="I66">
-        <v>-0.006676462990508372</v>
+        <v>-0.006676462989344632</v>
       </c>
       <c r="J66">
-        <v>0.004159744098925673</v>
+        <v>0.004159744104884571</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66">
-        <v>-0.01991462522906009</v>
+        <v>-0.01991462524686022</v>
       </c>
       <c r="M66">
-        <v>0.006561699248043343</v>
+        <v>0.006561699268170957</v>
       </c>
       <c r="N66">
-        <v>-0.3436084628107421</v>
+        <v>-0.3436084627508776</v>
       </c>
       <c r="O66">
-        <v>0.2068339959552066</v>
+        <v>0.2068339965039547</v>
       </c>
       <c r="P66">
-        <v>7.282284042453568E-08</v>
+        <v>7.282283842613424E-08</v>
       </c>
       <c r="Q66">
-        <v>0.9861669451483582</v>
+        <v>0.9861669451029793</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -9607,16 +9607,16 @@
         <v>0</v>
       </c>
       <c r="T66">
-        <v>0.01157268002780117</v>
+        <v>0.01157268013398052</v>
       </c>
       <c r="U66">
-        <v>5.761505357913786E-07</v>
+        <v>5.763115460050453E-07</v>
       </c>
       <c r="V66">
-        <v>0.01704898102523114</v>
+        <v>0.01704898102758481</v>
       </c>
       <c r="W66">
-        <v>0.7106239570934786</v>
+        <v>0.7106239580137147</v>
       </c>
     </row>
     <row r="67">
@@ -9649,37 +9649,37 @@
         <v>1</v>
       </c>
       <c r="G67">
-        <v>2.771264664201397</v>
+        <v>2.771264664201385</v>
       </c>
       <c r="H67">
-        <v>2.629540280219728</v>
+        <v>2.629540280219723</v>
       </c>
       <c r="I67">
-        <v>-0.1417243839816695</v>
+        <v>-0.1417243839816619</v>
       </c>
       <c r="J67">
-        <v>0.03996945896593233</v>
+        <v>0.03996945896594218</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67">
-        <v>-0.2689250409919897</v>
+        <v>-0.2689250409920134</v>
       </c>
       <c r="M67">
-        <v>-0.0145237269713494</v>
+        <v>-0.01452372697131044</v>
       </c>
       <c r="N67">
-        <v>-5.114068887480677</v>
+        <v>-5.114068887480426</v>
       </c>
       <c r="O67">
-        <v>0.03820459707087376</v>
+        <v>0.03820459707090262</v>
       </c>
       <c r="P67">
         <v>0</v>
       </c>
       <c r="Q67">
-        <v>0.9915086422509133</v>
+        <v>0.9915086422509709</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -9690,16 +9690,16 @@
         <v>1</v>
       </c>
       <c r="T67">
-        <v>0.1445183452992132</v>
+        <v>0.1445183452965272</v>
       </c>
       <c r="U67">
-        <v>7.34337430487315E-06</v>
+        <v>7.343216421658641E-06</v>
       </c>
       <c r="V67">
-        <v>0.2176773047876187</v>
+        <v>0.2176773047877515</v>
       </c>
       <c r="W67">
-        <v>1.755276874910597E-75</v>
+        <v>1.766064243391617E-75</v>
       </c>
     </row>
     <row r="68">
@@ -9732,37 +9732,37 @@
         <v>1</v>
       </c>
       <c r="G68">
-        <v>2.771225627884647</v>
+        <v>2.771225627884546</v>
       </c>
       <c r="H68">
-        <v>2.841602092123697</v>
+        <v>2.841602092123555</v>
       </c>
       <c r="I68">
-        <v>0.07037646423904924</v>
+        <v>0.07037646423900969</v>
       </c>
       <c r="J68">
-        <v>0.04244239874291431</v>
+        <v>0.04244239874310623</v>
       </c>
       <c r="K68">
         <v>3</v>
       </c>
       <c r="L68">
-        <v>-0.06469419082771628</v>
+        <v>-0.06469419082836662</v>
       </c>
       <c r="M68">
-        <v>0.2054471193058148</v>
+        <v>0.205447119306386</v>
       </c>
       <c r="N68">
-        <v>2.539542920320405</v>
+        <v>2.53954292031907</v>
       </c>
       <c r="O68">
-        <v>0.1958647064789756</v>
+        <v>0.1958647064806621</v>
       </c>
       <c r="P68">
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0.9736762231780339</v>
+        <v>0.9736762231794301</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -9773,16 +9773,16 @@
         <v>0</v>
       </c>
       <c r="T68">
-        <v>0.1110889755476437</v>
+        <v>0.1110889755322012</v>
       </c>
       <c r="U68">
-        <v>5.494599637595938E-06</v>
+        <v>5.494710475748625E-06</v>
       </c>
       <c r="V68">
-        <v>0.227417600703178</v>
+        <v>0.2274176007041696</v>
       </c>
       <c r="W68">
-        <v>6.74566118116012E-56</v>
+        <v>6.672654773435305E-56</v>
       </c>
     </row>
     <row r="69">
@@ -9815,37 +9815,37 @@
         <v>1</v>
       </c>
       <c r="G69">
-        <v>2.839335005286982</v>
+        <v>2.839335005286892</v>
       </c>
       <c r="H69">
-        <v>2.867045763636906</v>
+        <v>2.86704576363682</v>
       </c>
       <c r="I69">
-        <v>0.02771075834992368</v>
+        <v>0.0277107583499275</v>
       </c>
       <c r="J69">
-        <v>0.0527290528164912</v>
+        <v>0.05272905281620509</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69">
-        <v>-0.1400966209670282</v>
+        <v>-0.1400966209661139</v>
       </c>
       <c r="M69">
-        <v>0.1955181376668756</v>
+        <v>0.1955181376659689</v>
       </c>
       <c r="N69">
-        <v>0.9759594517140415</v>
+        <v>0.9759594517142067</v>
       </c>
       <c r="O69">
-        <v>0.6355829920326592</v>
+        <v>0.6355829920308547</v>
       </c>
       <c r="P69">
         <v>1.509903313490213E-13</v>
       </c>
       <c r="Q69">
-        <v>0.9919686581441736</v>
+        <v>0.991968658144788</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -9856,16 +9856,16 @@
         <v>0</v>
       </c>
       <c r="T69">
-        <v>0.08479109487427292</v>
+        <v>0.08479109486025831</v>
       </c>
       <c r="U69">
-        <v>7.211887267379338E-06</v>
+        <v>7.211908076161837E-06</v>
       </c>
       <c r="V69">
-        <v>0.2499702431169322</v>
+        <v>0.2499702431176397</v>
       </c>
       <c r="W69">
-        <v>0.574964626894791</v>
+        <v>0.5749646268837605</v>
       </c>
     </row>
     <row r="70">
@@ -9898,37 +9898,37 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <v>2.840525949985915</v>
+        <v>2.840525949986456</v>
       </c>
       <c r="H70">
-        <v>2.843171654728137</v>
+        <v>2.843171654728482</v>
       </c>
       <c r="I70">
-        <v>0.002645704742222092</v>
+        <v>0.002645704742025528</v>
       </c>
       <c r="J70">
-        <v>0.04929439677502849</v>
+        <v>0.04929439677464202</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70">
-        <v>-0.1542310661456565</v>
+        <v>-0.1542310661446231</v>
       </c>
       <c r="M70">
-        <v>0.1595224756301006</v>
+        <v>0.1595224756286741</v>
       </c>
       <c r="N70">
-        <v>0.09314136849322609</v>
+        <v>0.09314136848628836</v>
       </c>
       <c r="O70">
-        <v>0.9605710281647692</v>
+        <v>0.9605710281673863</v>
       </c>
       <c r="P70">
         <v>8.72368843829463E-12</v>
       </c>
       <c r="Q70">
-        <v>0.9581093717078429</v>
+        <v>0.95810937170445</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -9939,16 +9939,16 @@
         <v>0</v>
       </c>
       <c r="T70">
-        <v>0.07169998638733877</v>
+        <v>0.07169998641067622</v>
       </c>
       <c r="U70">
-        <v>7.731137828142773E-06</v>
+        <v>7.731144241133527E-06</v>
       </c>
       <c r="V70">
-        <v>0.2641451022928179</v>
+        <v>0.2641451022907346</v>
       </c>
       <c r="W70">
-        <v>2.573658936546256E-44</v>
+        <v>2.57567345497727E-44</v>
       </c>
     </row>
     <row r="71">
@@ -9981,37 +9981,37 @@
         <v>1</v>
       </c>
       <c r="G71">
-        <v>2.841758573885818</v>
+        <v>2.841758573884985</v>
       </c>
       <c r="H71">
-        <v>2.926898197668097</v>
+        <v>2.926898197667955</v>
       </c>
       <c r="I71">
-        <v>0.08513962378227811</v>
+        <v>0.08513962378297039</v>
       </c>
       <c r="J71">
-        <v>0.04799092515099855</v>
+        <v>0.0479909251515636</v>
       </c>
       <c r="K71">
         <v>3</v>
       </c>
       <c r="L71">
-        <v>-0.06758891865166418</v>
+        <v>-0.06758891865277016</v>
       </c>
       <c r="M71">
-        <v>0.2378681662162204</v>
+        <v>0.2378681662187109</v>
       </c>
       <c r="N71">
-        <v>2.996018893535289</v>
+        <v>2.996018893560529</v>
       </c>
       <c r="O71">
-        <v>0.1741509923544055</v>
+        <v>0.1741509923555374</v>
       </c>
       <c r="P71">
         <v>1.103117597267556E-12</v>
       </c>
       <c r="Q71">
-        <v>0.7951163346153158</v>
+        <v>0.7951163346389026</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -10022,16 +10022,16 @@
         <v>0</v>
       </c>
       <c r="T71">
-        <v>0.0847206736700806</v>
+        <v>0.08472067363348257</v>
       </c>
       <c r="U71">
-        <v>6.920233036956555E-06</v>
+        <v>6.920258430123838E-06</v>
       </c>
       <c r="V71">
-        <v>0.2557138602433586</v>
+        <v>0.2557138602463883</v>
       </c>
       <c r="W71">
-        <v>3.603745126692791E-12</v>
+        <v>3.60384401082165E-12</v>
       </c>
     </row>
     <row r="72">
@@ -10064,37 +10064,37 @@
         <v>1</v>
       </c>
       <c r="G72">
-        <v>5.582817420022018</v>
+        <v>5.582817420021843</v>
       </c>
       <c r="H72">
-        <v>5.692826753212736</v>
+        <v>5.692826753212589</v>
       </c>
       <c r="I72">
-        <v>0.1100093331907174</v>
+        <v>0.1100093331907465</v>
       </c>
       <c r="J72">
-        <v>0.3419019039532005</v>
+        <v>0.3419019039393285</v>
       </c>
       <c r="K72">
         <v>3</v>
       </c>
       <c r="L72">
-        <v>-0.9780751178146107</v>
+        <v>-0.9780751177704347</v>
       </c>
       <c r="M72">
-        <v>1.198093784196046</v>
+        <v>1.198093784151928</v>
       </c>
       <c r="N72">
-        <v>1.970498494114886</v>
+        <v>1.970498494115469</v>
       </c>
       <c r="O72">
-        <v>0.7687526528055507</v>
+        <v>0.7687526527965265</v>
       </c>
       <c r="P72">
-        <v>1.550249759341149E-06</v>
+        <v>1.550249758786038E-06</v>
       </c>
       <c r="Q72">
-        <v>0.99969527353034</v>
+        <v>0.9996952735303613</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -10105,16 +10105,16 @@
         <v>0</v>
       </c>
       <c r="T72">
-        <v>5.907689276687453E-05</v>
+        <v>5.907710196461294E-05</v>
       </c>
       <c r="U72">
-        <v>1.194103721734331E-05</v>
+        <v>1.194112823834826E-05</v>
       </c>
       <c r="V72">
-        <v>1.709473443401822</v>
+        <v>1.709473443395312</v>
       </c>
       <c r="W72">
-        <v>0.513177350112491</v>
+        <v>0.5131773500484971</v>
       </c>
     </row>
     <row r="73">
@@ -10147,37 +10147,37 @@
         <v>1</v>
       </c>
       <c r="G73">
-        <v>5.583867041106891</v>
+        <v>5.583867041105841</v>
       </c>
       <c r="H73">
-        <v>5.525482094822082</v>
+        <v>5.525482094818368</v>
       </c>
       <c r="I73">
-        <v>-0.05838494628480872</v>
+        <v>-0.05838494628747413</v>
       </c>
       <c r="J73">
-        <v>0.3184944237163126</v>
+        <v>0.3184944237185825</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73">
-        <v>-1.071976348294252</v>
+        <v>-1.071976348304141</v>
       </c>
       <c r="M73">
-        <v>0.9552064557246343</v>
+        <v>0.9552064557291924</v>
       </c>
       <c r="N73">
-        <v>-1.045600582087554</v>
+        <v>-1.045600582135485</v>
       </c>
       <c r="O73">
-        <v>0.866240143403847</v>
+        <v>0.8662401433987721</v>
       </c>
       <c r="P73">
-        <v>7.05723019533977E-06</v>
+        <v>7.057230197116127E-06</v>
       </c>
       <c r="Q73">
-        <v>0.9984314835720902</v>
+        <v>0.9984314835722887</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -10188,16 +10188,16 @@
         <v>0</v>
       </c>
       <c r="T73">
-        <v>0.2606927709776479</v>
+        <v>0.2606927708304726</v>
       </c>
       <c r="U73">
-        <v>0.0001049598823473409</v>
+        <v>0.0001049582654523172</v>
       </c>
       <c r="V73">
-        <v>1.706776731023411</v>
+        <v>1.706776731037123</v>
       </c>
       <c r="W73">
-        <v>1.782743646967094E-58</v>
+        <v>1.782644942593974E-58</v>
       </c>
     </row>
     <row r="74">
@@ -10230,37 +10230,37 @@
         <v>1</v>
       </c>
       <c r="G74">
-        <v>5.523315766741651</v>
+        <v>5.523315766740235</v>
       </c>
       <c r="H74">
-        <v>5.714420479699132</v>
+        <v>5.714420479698197</v>
       </c>
       <c r="I74">
-        <v>0.1911047129574807</v>
+        <v>0.1911047129579628</v>
       </c>
       <c r="J74">
-        <v>0.4592324826357594</v>
+        <v>0.4592324826215018</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74">
-        <v>-1.270378004672956</v>
+        <v>-1.2703780046271</v>
       </c>
       <c r="M74">
-        <v>1.652587430587918</v>
+        <v>1.652587430543026</v>
       </c>
       <c r="N74">
-        <v>3.459963562253809</v>
+        <v>3.459963562263425</v>
       </c>
       <c r="O74">
-        <v>0.7052861346182906</v>
+        <v>0.7052861346091143</v>
       </c>
       <c r="P74">
-        <v>0.0002991728792437476</v>
+        <v>0.0002991728792167692</v>
       </c>
       <c r="Q74">
-        <v>0.6633184133242938</v>
+        <v>0.663318413328859</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -10271,16 +10271,16 @@
         <v>0</v>
       </c>
       <c r="T74">
-        <v>9.666124694152863E-05</v>
+        <v>9.666117474354326E-05</v>
       </c>
       <c r="U74">
-        <v>2.052309294197494E-05</v>
+        <v>2.052302649965805E-05</v>
       </c>
       <c r="V74">
-        <v>2.289913624531239</v>
+        <v>2.28991362452534</v>
       </c>
       <c r="W74">
-        <v>0.4934940153048543</v>
+        <v>0.4934940152480488</v>
       </c>
     </row>
     <row r="75">
@@ -10313,37 +10313,37 @@
         <v>1</v>
       </c>
       <c r="G75">
-        <v>5.522953577646966</v>
+        <v>5.522953577512842</v>
       </c>
       <c r="H75">
-        <v>5.840061574013717</v>
+        <v>5.840061574115506</v>
       </c>
       <c r="I75">
-        <v>0.3171079963667504</v>
+        <v>0.3171079966026632</v>
       </c>
       <c r="J75">
-        <v>0.3918914010068345</v>
+        <v>0.391891399234844</v>
       </c>
       <c r="K75">
         <v>3</v>
       </c>
       <c r="L75">
-        <v>-0.9300653448399058</v>
+        <v>-0.9300653389647285</v>
       </c>
       <c r="M75">
-        <v>1.564281337573406</v>
+        <v>1.564281332170055</v>
       </c>
       <c r="N75">
-        <v>5.741637910015768</v>
+        <v>5.7416379144267</v>
       </c>
       <c r="O75">
-        <v>0.477636974852492</v>
+        <v>0.4776369727421054</v>
       </c>
       <c r="P75">
-        <v>7.223239127940317E-07</v>
+        <v>7.223239208986598E-07</v>
       </c>
       <c r="Q75">
-        <v>0.8622167179367171</v>
+        <v>0.8622167181625052</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>0</v>
       </c>
       <c r="T75">
-        <v>7.906078332264772E-05</v>
+        <v>7.910360931826291E-05</v>
       </c>
       <c r="U75">
-        <v>0.2298283607450661</v>
+        <v>0.2298283543443495</v>
       </c>
       <c r="V75">
-        <v>1.910632196623129</v>
+        <v>1.910632197267715</v>
       </c>
       <c r="W75">
-        <v>1.012831927775592E-13</v>
+        <v>1.018988721670083E-13</v>
       </c>
     </row>
     <row r="76">
@@ -10396,37 +10396,37 @@
         <v>1</v>
       </c>
       <c r="G76">
-        <v>5.525669808318205</v>
+        <v>5.525669808315548</v>
       </c>
       <c r="H76">
-        <v>5.644751024458977</v>
+        <v>5.644751024459976</v>
       </c>
       <c r="I76">
-        <v>0.1190812161407718</v>
+        <v>0.1190812161444288</v>
       </c>
       <c r="J76">
-        <v>0.3997687792803676</v>
+        <v>0.3997687792368437</v>
       </c>
       <c r="K76">
         <v>3</v>
       </c>
       <c r="L76">
-        <v>-1.153161458447812</v>
+        <v>-1.153161458305643</v>
       </c>
       <c r="M76">
-        <v>1.391323890729356</v>
+        <v>1.3913238905945</v>
       </c>
       <c r="N76">
-        <v>2.155054867040914</v>
+        <v>2.155054867108133</v>
       </c>
       <c r="O76">
-        <v>0.7852361682214175</v>
+        <v>0.7852361681925821</v>
       </c>
       <c r="P76">
         <v>4.652565599450043E-08</v>
       </c>
       <c r="Q76">
-        <v>0.7873021624975396</v>
+        <v>0.7873021625055505</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -10437,16 +10437,16 @@
         <v>0</v>
       </c>
       <c r="T76">
-        <v>0.0001538642355636808</v>
+        <v>0.0001538674803317717</v>
       </c>
       <c r="U76">
-        <v>0.3255448918350435</v>
+        <v>0.3255448917230016</v>
       </c>
       <c r="V76">
-        <v>1.741354265437481</v>
+        <v>1.741354265451647</v>
       </c>
       <c r="W76">
-        <v>1.597215779198067E-50</v>
+        <v>1.598717939305513E-50</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/mixed_model_results.xlsx
+++ b/output/tables/mixed_model_results.xlsx
@@ -439,25 +439,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3190629929315109</v>
+        <v>0.319129660769912</v>
       </c>
       <c r="E2">
-        <v>0.3206914106929256</v>
+        <v>0.320691410692911</v>
       </c>
       <c r="F2">
-        <v>0.00162841776141463</v>
+        <v>0.001561749922998903</v>
       </c>
       <c r="G2">
-        <v>-0.002299408682489893</v>
+        <v>-0.002478910721049641</v>
       </c>
       <c r="H2">
-        <v>0.005556244205319152</v>
+        <v>0.005602410567047448</v>
       </c>
       <c r="I2">
-        <v>0.5103750035229504</v>
+        <v>0.4893778657963426</v>
       </c>
       <c r="J2">
-        <v>0.2786964623461505</v>
+        <v>0.3063421102248072</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0.4834879092884048</v>
+        <v>0.4662949776441857</v>
       </c>
     </row>
     <row r="3">
@@ -488,25 +488,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.3190628451357968</v>
+        <v>0.3191293578435881</v>
       </c>
       <c r="E3">
-        <v>0.3176096175964226</v>
+        <v>0.3176120218266411</v>
       </c>
       <c r="F3">
-        <v>-0.001453227539374158</v>
+        <v>-0.001517336016947011</v>
       </c>
       <c r="G3">
-        <v>-0.00418592456331422</v>
+        <v>-0.004277825189460927</v>
       </c>
       <c r="H3">
-        <v>0.001279469484565903</v>
+        <v>0.001243153155566904</v>
       </c>
       <c r="I3">
-        <v>-0.4554674922288893</v>
+        <v>-0.4754611193404177</v>
       </c>
       <c r="J3">
-        <v>0.1891462214569604</v>
+        <v>0.1785569185590977</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0.4911506851626125</v>
+        <v>0.4869804593347412</v>
       </c>
     </row>
     <row r="4">
@@ -537,25 +537,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.3176092318311073</v>
+        <v>0.3176116667510588</v>
       </c>
       <c r="E4">
-        <v>0.3178343161300924</v>
+        <v>0.3178552138619586</v>
       </c>
       <c r="F4">
-        <v>0.0002250842989850668</v>
+        <v>0.0002435471108998467</v>
       </c>
       <c r="G4">
-        <v>-0.00303055612458806</v>
+        <v>-0.003004712189956147</v>
       </c>
       <c r="H4">
-        <v>0.003480724722558193</v>
+        <v>0.00349180641175584</v>
       </c>
       <c r="I4">
-        <v>0.0708683112538612</v>
+        <v>0.07668078235008184</v>
       </c>
       <c r="J4">
-        <v>0.8399743913592389</v>
+        <v>0.8267767079075976</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0.825251035653417</v>
+        <v>0.8270419102634639</v>
       </c>
     </row>
     <row r="5">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.3176091753203997</v>
+        <v>0.3176116123449689</v>
       </c>
       <c r="E5">
-        <v>0.3185644779285982</v>
+        <v>0.3185645082059152</v>
       </c>
       <c r="F5">
-        <v>0.0009553026081983861</v>
+        <v>0.0009528958609462405</v>
       </c>
       <c r="G5">
-        <v>-0.002708898722691901</v>
+        <v>-0.002710950768712229</v>
       </c>
       <c r="H5">
-        <v>0.004619503939088674</v>
+        <v>0.00461674249060471</v>
       </c>
       <c r="I5">
-        <v>0.3007792854959842</v>
+        <v>0.3000192133753811</v>
       </c>
       <c r="J5">
-        <v>0.4675607208059289</v>
+        <v>0.4685391854583187</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.4734218038422473</v>
+        <v>0.4735724180152905</v>
       </c>
     </row>
     <row r="6">
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.3176092357715212</v>
+        <v>0.3176116955031084</v>
       </c>
       <c r="E6">
-        <v>0.3180293554112534</v>
+        <v>0.3179737349769436</v>
       </c>
       <c r="F6">
-        <v>0.0004201196397321896</v>
+        <v>0.0003620394738352333</v>
       </c>
       <c r="G6">
-        <v>-0.002675307069720221</v>
+        <v>-0.002708731564640725</v>
       </c>
       <c r="H6">
-        <v>0.0035155463491846</v>
+        <v>0.003432810512311192</v>
       </c>
       <c r="I6">
-        <v>0.1322756369825503</v>
+        <v>0.1139880800868336</v>
       </c>
       <c r="J6">
-        <v>0.6949539644488112</v>
+        <v>0.7324641077731635</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0.4355566929311028</v>
+        <v>0.4262503465949887</v>
       </c>
     </row>
     <row r="7">
@@ -684,25 +684,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>439.9038217031748</v>
+        <v>439.9031505492183</v>
       </c>
       <c r="E7">
-        <v>422.229408753444</v>
+        <v>422.2294088587337</v>
       </c>
       <c r="F7">
-        <v>-17.67441294973086</v>
+        <v>-17.67374169048453</v>
       </c>
       <c r="G7">
-        <v>-38.36366422257507</v>
+        <v>-38.3633910128579</v>
       </c>
       <c r="H7">
-        <v>3.014838323113359</v>
+        <v>3.01590763188884</v>
       </c>
       <c r="I7">
-        <v>-4.017790270905324</v>
+        <v>-4.017643808283459</v>
       </c>
       <c r="J7">
-        <v>0.07262898000982476</v>
+        <v>0.07263851181477721</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0.9889160873100195</v>
+        <v>0.9889183151319325</v>
       </c>
     </row>
     <row r="8">
@@ -733,25 +733,25 @@
         </is>
       </c>
       <c r="D8">
-        <v>439.9024129871332</v>
+        <v>439.901753770717</v>
       </c>
       <c r="E8">
-        <v>429.8342967628469</v>
+        <v>429.8208487878458</v>
       </c>
       <c r="F8">
-        <v>-10.06811622428629</v>
+        <v>-10.08090498287113</v>
       </c>
       <c r="G8">
-        <v>-40.11797127933664</v>
+        <v>-40.13312069272344</v>
       </c>
       <c r="H8">
-        <v>19.98173883076407</v>
+        <v>19.97131072698119</v>
       </c>
       <c r="I8">
-        <v>-2.288715844025337</v>
+        <v>-2.291626458967344</v>
       </c>
       <c r="J8">
-        <v>0.3644975258807731</v>
+        <v>0.3640066876838972</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0.8708491495458119</v>
+        <v>0.870939103515934</v>
       </c>
     </row>
     <row r="9">
@@ -782,25 +782,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>429.8313277409174</v>
+        <v>429.8179204027277</v>
       </c>
       <c r="E9">
-        <v>423.541584995228</v>
+        <v>423.6243151788966</v>
       </c>
       <c r="F9">
-        <v>-6.289742745689423</v>
+        <v>-6.193605223831154</v>
       </c>
       <c r="G9">
-        <v>-18.62907727702702</v>
+        <v>-18.58677084182337</v>
       </c>
       <c r="H9">
-        <v>6.04959178564817</v>
+        <v>6.199560394161056</v>
       </c>
       <c r="I9">
-        <v>-1.463304868620602</v>
+        <v>-1.44098347924347</v>
       </c>
       <c r="J9">
-        <v>0.2032155511158824</v>
+        <v>0.2099580241358029</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0.999716615452511</v>
+        <v>0.9997384097691355</v>
       </c>
     </row>
     <row r="10">
@@ -831,25 +831,25 @@
         </is>
       </c>
       <c r="D10">
-        <v>429.8315844705177</v>
+        <v>429.818154479843</v>
       </c>
       <c r="E10">
-        <v>417.9183058985104</v>
+        <v>417.9171882895802</v>
       </c>
       <c r="F10">
-        <v>-11.91327857200735</v>
+        <v>-11.90096619026277</v>
       </c>
       <c r="G10">
-        <v>-28.00835632009727</v>
+        <v>-28.01521964851236</v>
       </c>
       <c r="H10">
-        <v>4.181799176082567</v>
+        <v>4.213287267986829</v>
       </c>
       <c r="I10">
-        <v>-2.771615442518624</v>
+        <v>-2.768837487719678</v>
       </c>
       <c r="J10">
-        <v>0.09979838255768392</v>
+        <v>0.1002736403778501</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0.9954420644577676</v>
+        <v>0.9954862188980136</v>
       </c>
     </row>
     <row r="11">
@@ -880,25 +880,25 @@
         </is>
       </c>
       <c r="D11">
-        <v>429.8315096897875</v>
+        <v>429.8181014408388</v>
       </c>
       <c r="E11">
-        <v>415.0544834054531</v>
+        <v>414.8878855619794</v>
       </c>
       <c r="F11">
-        <v>-14.77702628433436</v>
+        <v>-14.93021587885936</v>
       </c>
       <c r="G11">
-        <v>-32.60945195737904</v>
+        <v>-32.89006314653237</v>
       </c>
       <c r="H11">
-        <v>3.055399388710329</v>
+        <v>3.029631388813646</v>
       </c>
       <c r="I11">
-        <v>-3.437864826382561</v>
+        <v>-3.473612634928637</v>
       </c>
       <c r="J11">
-        <v>0.07784478151375762</v>
+        <v>0.07728415986197656</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.9952212450447355</v>
+        <v>0.9942812013322158</v>
       </c>
     </row>
     <row r="12">
@@ -929,25 +929,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>1.981685256768479</v>
+        <v>1.981770928487437</v>
       </c>
       <c r="E12">
-        <v>1.963191854770372</v>
+        <v>1.96319183985796</v>
       </c>
       <c r="F12">
-        <v>-0.01849340199810703</v>
+        <v>-0.01857908862947774</v>
       </c>
       <c r="G12">
-        <v>-0.05165414644730448</v>
+        <v>-0.05173473047373914</v>
       </c>
       <c r="H12">
-        <v>0.01466734245109041</v>
+        <v>0.01457655321478366</v>
       </c>
       <c r="I12">
-        <v>-0.9332159047428198</v>
+        <v>-0.9374993023869819</v>
       </c>
       <c r="J12">
-        <v>0.174021562970222</v>
+        <v>0.1725423786905823</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.4613569056096266</v>
+        <v>0.4611980438975091</v>
       </c>
     </row>
     <row r="13">
@@ -978,25 +978,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>1.981684675825401</v>
+        <v>1.981770357912117</v>
       </c>
       <c r="E13">
-        <v>1.96565106944436</v>
+        <v>1.965645695376775</v>
       </c>
       <c r="F13">
-        <v>-0.01603360638104076</v>
+        <v>-0.01612466253534137</v>
       </c>
       <c r="G13">
-        <v>-0.05039143350350458</v>
+        <v>-0.05047476352523281</v>
       </c>
       <c r="H13">
-        <v>0.01832422074142305</v>
+        <v>0.01822543845455006</v>
       </c>
       <c r="I13">
-        <v>-0.8090896890224238</v>
+        <v>-0.8136493953986385</v>
       </c>
       <c r="J13">
-        <v>0.234181874912321</v>
+        <v>0.232051382153142</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0.9977664570309991</v>
+        <v>0.9978515334228961</v>
       </c>
     </row>
     <row r="14">
@@ -1027,25 +1027,25 @@
         </is>
       </c>
       <c r="D14">
-        <v>1.965659275306108</v>
+        <v>1.96565382311872</v>
       </c>
       <c r="E14">
-        <v>1.961540952445237</v>
+        <v>1.961245739520491</v>
       </c>
       <c r="F14">
-        <v>-0.004118322860870968</v>
+        <v>-0.004408083598229564</v>
       </c>
       <c r="G14">
-        <v>-0.02189110728602746</v>
+        <v>-0.02204373678179956</v>
       </c>
       <c r="H14">
-        <v>0.01365446156428552</v>
+        <v>0.01322756958534043</v>
       </c>
       <c r="I14">
-        <v>-0.2095135669038894</v>
+        <v>-0.2242553366408978</v>
       </c>
       <c r="J14">
-        <v>0.5142972548535101</v>
+        <v>0.4844695136216154</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0.9985126838186595</v>
+        <v>0.9989753961912664</v>
       </c>
     </row>
     <row r="15">
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>1.965659554720974</v>
+        <v>1.965654187375057</v>
       </c>
       <c r="E15">
-        <v>1.95569627098797</v>
+        <v>1.955696099288568</v>
       </c>
       <c r="F15">
-        <v>-0.009963283733004312</v>
+        <v>-0.009958088086488305</v>
       </c>
       <c r="G15">
-        <v>-0.02722022575549572</v>
+        <v>-0.02721477156735205</v>
       </c>
       <c r="H15">
-        <v>0.007293658289487094</v>
+        <v>0.007298595394375438</v>
       </c>
       <c r="I15">
-        <v>-0.5068672094857546</v>
+        <v>-0.5066042720254055</v>
       </c>
       <c r="J15">
-        <v>0.1634630942915104</v>
+        <v>0.1636146299982981</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0.9479401742957627</v>
+        <v>0.947902883270848</v>
       </c>
     </row>
     <row r="16">
@@ -1125,25 +1125,25 @@
         </is>
       </c>
       <c r="D16">
-        <v>1.965659414533604</v>
+        <v>1.965654040586146</v>
       </c>
       <c r="E16">
-        <v>1.952705883946115</v>
+        <v>1.952651135075837</v>
       </c>
       <c r="F16">
-        <v>-0.01295353058748931</v>
+        <v>-0.01300290551030944</v>
       </c>
       <c r="G16">
-        <v>-0.02987359521608061</v>
+        <v>-0.02991900429485496</v>
       </c>
       <c r="H16">
-        <v>0.003966534041102003</v>
+        <v>0.003913193274236075</v>
       </c>
       <c r="I16">
-        <v>-0.65899160819591</v>
+        <v>-0.6615052924792427</v>
       </c>
       <c r="J16">
-        <v>0.09279855678501803</v>
+        <v>0.09198599418337317</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0.9121962359954086</v>
+        <v>0.9139542549941249</v>
       </c>
     </row>
     <row r="17">
@@ -1174,25 +1174,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>2.16706874689131</v>
+        <v>2.163640521475306</v>
       </c>
       <c r="E17">
-        <v>2.377924955682624</v>
+        <v>2.377927281212483</v>
       </c>
       <c r="F17">
-        <v>0.2108562087913147</v>
+        <v>0.2142867597371765</v>
       </c>
       <c r="G17">
-        <v>-0.006022623638297586</v>
+        <v>-0.004227904756393092</v>
       </c>
       <c r="H17">
-        <v>0.427735041220927</v>
+        <v>0.4328014242307461</v>
       </c>
       <c r="I17">
-        <v>9.730019368042239</v>
+        <v>9.903990871416212</v>
       </c>
       <c r="J17">
-        <v>0.05354293974221414</v>
+        <v>0.05243600897163925</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0.1934635983299994</v>
+        <v>0.1681064272229661</v>
       </c>
     </row>
     <row r="18">
@@ -1223,25 +1223,25 @@
         </is>
       </c>
       <c r="D18">
-        <v>2.167036359080486</v>
+        <v>2.163598170749241</v>
       </c>
       <c r="E18">
-        <v>2.323636537722987</v>
+        <v>2.323841333631367</v>
       </c>
       <c r="F18">
-        <v>0.1566001786425012</v>
+        <v>0.1602431628821263</v>
       </c>
       <c r="G18">
-        <v>-0.00252174740915731</v>
+        <v>0.001383139319044407</v>
       </c>
       <c r="H18">
-        <v>0.3157221046941596</v>
+        <v>0.3191031864452083</v>
       </c>
       <c r="I18">
-        <v>7.226467520321143</v>
+        <v>7.406327341580027</v>
       </c>
       <c r="J18">
-        <v>0.05198437459152316</v>
+        <v>0.04895046368035283</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="L18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>0.4481444809641534</v>
+        <v>0.454240610056921</v>
       </c>
     </row>
     <row r="19">
@@ -1272,25 +1272,25 @@
         </is>
       </c>
       <c r="D19">
-        <v>2.323636537722984</v>
+        <v>2.323841333631361</v>
       </c>
       <c r="E19">
-        <v>2.348369878112605</v>
+        <v>2.344301323210374</v>
       </c>
       <c r="F19">
-        <v>0.02473334038962182</v>
+        <v>0.02045998957901286</v>
       </c>
       <c r="G19">
-        <v>-0.1356712701752076</v>
+        <v>-0.1408228166113614</v>
       </c>
       <c r="H19">
-        <v>0.1851379509544513</v>
+        <v>0.1817427957693871</v>
       </c>
       <c r="I19">
-        <v>1.064423802435941</v>
+        <v>0.8804383192135141</v>
       </c>
       <c r="J19">
-        <v>0.6572819459222934</v>
+        <v>0.7134739315936419</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0.8301008524302518</v>
+        <v>0.8141304205449362</v>
       </c>
     </row>
     <row r="20">
@@ -1321,25 +1321,25 @@
         </is>
       </c>
       <c r="D20">
-        <v>2.323636537722988</v>
+        <v>2.323841333631361</v>
       </c>
       <c r="E20">
-        <v>2.442352776688102</v>
+        <v>2.442359499375551</v>
       </c>
       <c r="F20">
-        <v>0.118716238965114</v>
+        <v>0.1185181657441905</v>
       </c>
       <c r="G20">
-        <v>-0.03575685979426968</v>
+        <v>-0.03594335492419543</v>
       </c>
       <c r="H20">
-        <v>0.2731893377244977</v>
+        <v>0.2729796864125764</v>
       </c>
       <c r="I20">
-        <v>5.109070934193872</v>
+        <v>5.100097155040596</v>
       </c>
       <c r="J20">
-        <v>0.09202428553228659</v>
+        <v>0.09234460705520453</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0.2648323013414869</v>
+        <v>0.2653250806389098</v>
       </c>
     </row>
     <row r="21">
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="D21">
-        <v>2.323636537722989</v>
+        <v>2.323841333631369</v>
       </c>
       <c r="E21">
-        <v>2.474549123644997</v>
+        <v>2.473563828517284</v>
       </c>
       <c r="F21">
-        <v>0.150912585922009</v>
+        <v>0.149722494885915</v>
       </c>
       <c r="G21">
-        <v>-0.006672177662350676</v>
+        <v>-0.007820075113647657</v>
       </c>
       <c r="H21">
-        <v>0.3084973495063686</v>
+        <v>0.3072650648854777</v>
       </c>
       <c r="I21">
-        <v>6.494672616479572</v>
+        <v>6.442888019895488</v>
       </c>
       <c r="J21">
-        <v>0.05552863374485917</v>
+        <v>0.05655796804226987</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0.254146496835586</v>
+        <v>0.2489194808068158</v>
       </c>
     </row>
     <row r="22">
@@ -1419,25 +1419,25 @@
         </is>
       </c>
       <c r="D22">
-        <v>5.715657023779298</v>
+        <v>5.714628726423102</v>
       </c>
       <c r="E22">
-        <v>4.475082483533146</v>
+        <v>4.475082483533145</v>
       </c>
       <c r="F22">
-        <v>-1.240574540246152</v>
+        <v>-1.239546242889958</v>
       </c>
       <c r="G22">
-        <v>-2.574207131143766</v>
+        <v>-2.573020303875271</v>
       </c>
       <c r="H22">
-        <v>0.09305805065146089</v>
+        <v>0.09392781809535444</v>
       </c>
       <c r="I22">
-        <v>-21.70484574362829</v>
+        <v>-21.69075721680023</v>
       </c>
       <c r="J22">
-        <v>0.05952571919031668</v>
+        <v>0.05962632431722903</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0.5685524937685535</v>
+        <v>0.5685831163907287</v>
       </c>
     </row>
     <row r="23">
@@ -1468,25 +1468,25 @@
         </is>
       </c>
       <c r="D23">
-        <v>5.716450412948245</v>
+        <v>5.715409560583304</v>
       </c>
       <c r="E23">
-        <v>6.281438179490992</v>
+        <v>6.281598457486055</v>
       </c>
       <c r="F23">
-        <v>0.5649877665427475</v>
+        <v>0.5661888969027509</v>
       </c>
       <c r="G23">
-        <v>-1.705914417349804</v>
+        <v>-1.704296482497543</v>
       </c>
       <c r="H23">
-        <v>2.835889950435299</v>
+        <v>2.836674276303045</v>
       </c>
       <c r="I23">
-        <v>9.883541808794533</v>
+        <v>9.906357381761575</v>
       </c>
       <c r="J23">
-        <v>0.4863208835977372</v>
+        <v>0.4854017722898045</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0.9463393348786391</v>
+        <v>0.9463818144290322</v>
       </c>
     </row>
     <row r="24">
@@ -1517,25 +1517,25 @@
         </is>
       </c>
       <c r="D24">
-        <v>6.281363940122243</v>
+        <v>6.281523829079963</v>
       </c>
       <c r="E24">
-        <v>6.182479792008519</v>
+        <v>6.179770908579557</v>
       </c>
       <c r="F24">
-        <v>-0.09888414811372354</v>
+        <v>-0.1017529205004058</v>
       </c>
       <c r="G24">
-        <v>-2.508565185856439</v>
+        <v>-2.510463120922029</v>
       </c>
       <c r="H24">
-        <v>2.310796889628992</v>
+        <v>2.306957279921217</v>
       </c>
       <c r="I24">
-        <v>-1.574246438454243</v>
+        <v>-1.619876375050054</v>
       </c>
       <c r="J24">
-        <v>0.9043605698369798</v>
+        <v>0.901568399431441</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0.8311648906587366</v>
+        <v>0.8313800782433334</v>
       </c>
     </row>
     <row r="25">
@@ -1566,25 +1566,25 @@
         </is>
       </c>
       <c r="D25">
-        <v>6.281298995275222</v>
+        <v>6.281459153583775</v>
       </c>
       <c r="E25">
-        <v>6.918865152854911</v>
+        <v>6.918865155357377</v>
       </c>
       <c r="F25">
-        <v>0.6375661575796896</v>
+        <v>0.6374060017736022</v>
       </c>
       <c r="G25">
-        <v>-2.719222156449216</v>
+        <v>-2.719397022799591</v>
       </c>
       <c r="H25">
-        <v>3.994354471608596</v>
+        <v>3.994209026346795</v>
       </c>
       <c r="I25">
-        <v>10.15022781210169</v>
+        <v>10.14741935255508</v>
       </c>
       <c r="J25">
-        <v>0.5881959312493291</v>
+        <v>0.5882861800337852</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.5118438171490337</v>
+        <v>0.5118463177016355</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         </is>
       </c>
       <c r="D26">
-        <v>6.281496054994521</v>
+        <v>6.281656063622581</v>
       </c>
       <c r="E26">
-        <v>6.384748469060736</v>
+        <v>6.364855050671586</v>
       </c>
       <c r="F26">
-        <v>0.1032524140662161</v>
+        <v>0.083198987049005</v>
       </c>
       <c r="G26">
-        <v>-2.331481319615513</v>
+        <v>-2.353267653410596</v>
       </c>
       <c r="H26">
-        <v>2.537986147747945</v>
+        <v>2.519665627508606</v>
       </c>
       <c r="I26">
-        <v>1.643755136710122</v>
+        <v>1.324475364558957</v>
       </c>
       <c r="J26">
-        <v>0.90118850947977</v>
+        <v>0.9203233745559203</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0.3970272446204093</v>
+        <v>0.39851281150133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.3181513304352998</v>
+        <v>0.3180416700753945</v>
       </c>
       <c r="E27">
-        <v>0.3184091075185365</v>
+        <v>0.3184091075185366</v>
       </c>
       <c r="F27">
-        <v>0.0002577770832367278</v>
+        <v>0.0003674374431422021</v>
       </c>
       <c r="G27">
-        <v>-0.002681013398857472</v>
+        <v>-0.002557421630053303</v>
       </c>
       <c r="H27">
-        <v>0.003196567565330927</v>
+        <v>0.003292296516337707</v>
       </c>
       <c r="I27">
-        <v>0.08102341828463613</v>
+        <v>0.1155312267902184</v>
       </c>
       <c r="J27">
-        <v>0.7982681553501167</v>
+        <v>0.7160696468483081</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1693,13 +1693,13 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0.9866556012932424</v>
+        <v>0.9729458591714493</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1713,25 +1713,25 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.3181408563298728</v>
+        <v>0.318041674857422</v>
       </c>
       <c r="E28">
-        <v>0.3171571133163644</v>
+        <v>0.3171572569945293</v>
       </c>
       <c r="F28">
-        <v>-0.0009837430135084845</v>
+        <v>-0.0008844178628927238</v>
       </c>
       <c r="G28">
-        <v>-0.00384853087937032</v>
+        <v>-0.003578549775520663</v>
       </c>
       <c r="H28">
-        <v>0.001881044852353351</v>
+        <v>0.001809714049735215</v>
       </c>
       <c r="I28">
-        <v>-0.3092161833148724</v>
+        <v>-0.2780823812757268</v>
       </c>
       <c r="J28">
-        <v>0.3543718195693368</v>
+        <v>0.3729211039065696</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0.1106425824672489</v>
+        <v>0.1162282288077902</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1762,25 +1762,25 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.317156376642493</v>
+        <v>0.3171563709957552</v>
       </c>
       <c r="E29">
-        <v>0.3175283304419296</v>
+        <v>0.3175975398139458</v>
       </c>
       <c r="F29">
-        <v>0.0003719537994366687</v>
+        <v>0.0004411688181906017</v>
       </c>
       <c r="G29">
-        <v>-0.002513151900273034</v>
+        <v>-0.002448030407029417</v>
       </c>
       <c r="H29">
-        <v>0.003257059499146371</v>
+        <v>0.00333036804341062</v>
       </c>
       <c r="I29">
-        <v>0.1172777301135411</v>
+        <v>0.1391013577326203</v>
       </c>
       <c r="J29">
-        <v>0.7091369972620301</v>
+        <v>0.6602884480698676</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1791,13 +1791,13 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0.01385623970414773</v>
+        <v>0.01627724657325258</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.3171564401370906</v>
+        <v>0.317156327464711</v>
       </c>
       <c r="E31">
-        <v>0.3168147616816879</v>
+        <v>0.3168120282081159</v>
       </c>
       <c r="F31">
-        <v>-0.0003416784554026475</v>
+        <v>-0.0003442992565950189</v>
       </c>
       <c r="G31">
-        <v>-0.003245858253491779</v>
+        <v>-0.003394587977353712</v>
       </c>
       <c r="H31">
-        <v>0.002562501342686484</v>
+        <v>0.002705989464163674</v>
       </c>
       <c r="I31">
-        <v>-0.1077318358268107</v>
+        <v>-0.1085582177556675</v>
       </c>
       <c r="J31">
-        <v>0.7329934791869043</v>
+        <v>0.7432284421311537</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1889,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0.7744304315875609</v>
+        <v>0.4173734537772777</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,25 +1909,25 @@
         </is>
       </c>
       <c r="D32">
-        <v>439.0329017272575</v>
+        <v>438.8724215098236</v>
       </c>
       <c r="E32">
-        <v>428.5560578434248</v>
+        <v>428.5560329973286</v>
       </c>
       <c r="F32">
-        <v>-10.47684388383265</v>
+        <v>-10.31638851249501</v>
       </c>
       <c r="G32">
-        <v>-39.51048655409504</v>
+        <v>-39.35062215157068</v>
       </c>
       <c r="H32">
-        <v>18.55679878642975</v>
+        <v>18.71784512658066</v>
       </c>
       <c r="I32">
-        <v>-2.38634595325642</v>
+        <v>-2.350657732605804</v>
       </c>
       <c r="J32">
-        <v>0.3340716888700744</v>
+        <v>0.3403770868833369</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -1938,13 +1938,13 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0.9972508176715205</v>
+        <v>0.997199951980236</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1958,25 +1958,25 @@
         </is>
       </c>
       <c r="D33">
-        <v>439.115161743403</v>
+        <v>438.8712951327661</v>
       </c>
       <c r="E33">
-        <v>419.9439712850209</v>
+        <v>419.9440471554524</v>
       </c>
       <c r="F33">
-        <v>-19.17119045838206</v>
+        <v>-18.92724797731363</v>
       </c>
       <c r="G33">
-        <v>-56.59647366188492</v>
+        <v>-56.45800668579103</v>
       </c>
       <c r="H33">
-        <v>18.25409274512079</v>
+        <v>18.60351073116378</v>
       </c>
       <c r="I33">
-        <v>-4.365868484765451</v>
+        <v>-4.312710397609352</v>
       </c>
       <c r="J33">
-        <v>0.2015493919116456</v>
+        <v>0.2068486374336809</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -1987,13 +1987,13 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0.4793425431134143</v>
+        <v>0.4045125851636293</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2007,25 +2007,25 @@
         </is>
       </c>
       <c r="D34">
-        <v>419.94342358187</v>
+        <v>419.9435926044553</v>
       </c>
       <c r="E34">
-        <v>414.5899778585058</v>
+        <v>414.4258175877889</v>
       </c>
       <c r="F34">
-        <v>-5.353445723364242</v>
+        <v>-5.517775016666352</v>
       </c>
       <c r="G34">
-        <v>-18.44377569496977</v>
+        <v>-18.41716768106246</v>
       </c>
       <c r="H34">
-        <v>7.736884248241282</v>
+        <v>7.381617647729755</v>
       </c>
       <c r="I34">
-        <v>-1.274801657257186</v>
+        <v>-1.313932421839221</v>
       </c>
       <c r="J34">
-        <v>0.2840169663976808</v>
+        <v>0.2666431786646385</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0.9974110775454158</v>
+        <v>0.9966983271179078</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2105,25 +2105,25 @@
         </is>
       </c>
       <c r="D36">
-        <v>419.9430405774364</v>
+        <v>419.9430942541685</v>
       </c>
       <c r="E36">
-        <v>409.0229283264894</v>
+        <v>407.3324254838149</v>
       </c>
       <c r="F36">
-        <v>-10.92011225094705</v>
+        <v>-12.61066877035361</v>
       </c>
       <c r="G36">
-        <v>-24.02106226202772</v>
+        <v>-25.61343380928219</v>
       </c>
       <c r="H36">
-        <v>2.180837760133613</v>
+        <v>0.3920962685749654</v>
       </c>
       <c r="I36">
-        <v>-2.600379383816319</v>
+        <v>-3.002947052326349</v>
       </c>
       <c r="J36">
-        <v>0.07681735295222714</v>
+        <v>0.0538618176670641</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2134,13 +2134,13 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0.7870335122044502</v>
+        <v>0.8683615664809332</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2154,25 +2154,25 @@
         </is>
       </c>
       <c r="D37">
-        <v>1.977043737016501</v>
+        <v>1.976952970187362</v>
       </c>
       <c r="E37">
-        <v>1.965222678620959</v>
+        <v>1.965222673773879</v>
       </c>
       <c r="F37">
-        <v>-0.01182105839554173</v>
+        <v>-0.01173029641348285</v>
       </c>
       <c r="G37">
-        <v>-0.04346164696580174</v>
+        <v>-0.04300914317825905</v>
       </c>
       <c r="H37">
-        <v>0.01981953017471827</v>
+        <v>0.01954855035129335</v>
       </c>
       <c r="I37">
-        <v>-0.5979158768323733</v>
+        <v>-0.5933523250363986</v>
       </c>
       <c r="J37">
-        <v>0.3199840945275008</v>
+        <v>0.3184540776294043</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0.5775376647891546</v>
+        <v>0.5643314792529246</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2203,25 +2203,25 @@
         </is>
       </c>
       <c r="D38">
-        <v>1.977019663765039</v>
+        <v>1.976952079631702</v>
       </c>
       <c r="E38">
-        <v>1.959981697463381</v>
+        <v>1.959981687279842</v>
       </c>
       <c r="F38">
-        <v>-0.01703796630165793</v>
+        <v>-0.01697039235186026</v>
       </c>
       <c r="G38">
-        <v>-0.04958378083047689</v>
+        <v>-0.04914468988432914</v>
       </c>
       <c r="H38">
-        <v>0.01550784822716102</v>
+        <v>0.01520390518060861</v>
       </c>
       <c r="I38">
-        <v>-0.8618005482662123</v>
+        <v>-0.8584119224084468</v>
       </c>
       <c r="J38">
-        <v>0.1942969021797325</v>
+        <v>0.1918250610876104</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0.9964476621430448</v>
+        <v>0.9962008182189269</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2252,25 +2252,25 @@
         </is>
       </c>
       <c r="D39">
-        <v>1.95999115844225</v>
+        <v>1.959991086730867</v>
       </c>
       <c r="E39">
-        <v>1.955058475168531</v>
+        <v>1.954967124087597</v>
       </c>
       <c r="F39">
-        <v>-0.00493268327371874</v>
+        <v>-0.00502396264327041</v>
       </c>
       <c r="G39">
-        <v>-0.02180391178091621</v>
+        <v>-0.02183700351005611</v>
       </c>
       <c r="H39">
-        <v>0.01193854523347873</v>
+        <v>0.01178907822351529</v>
       </c>
       <c r="I39">
-        <v>-0.2516686492422297</v>
+        <v>-0.256325790320304</v>
       </c>
       <c r="J39">
-        <v>0.4207676176129129</v>
+        <v>0.411782198458145</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2281,13 +2281,13 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0.9990343225677822</v>
+        <v>0.999078546750874</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2336,7 +2336,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2350,25 +2350,25 @@
         </is>
       </c>
       <c r="D41">
-        <v>1.959991412684328</v>
+        <v>1.959991218367615</v>
       </c>
       <c r="E41">
-        <v>1.94738561641093</v>
+        <v>1.946571185492213</v>
       </c>
       <c r="F41">
-        <v>-0.01260579627339727</v>
+        <v>-0.01342003287540265</v>
       </c>
       <c r="G41">
-        <v>-0.02927415558964218</v>
+        <v>-0.02939413065498341</v>
       </c>
       <c r="H41">
-        <v>0.004062563042847633</v>
+        <v>0.002554064904178097</v>
       </c>
       <c r="I41">
-        <v>-0.6431556889391095</v>
+        <v>-0.6846986226080936</v>
       </c>
       <c r="J41">
-        <v>0.0952911029045802</v>
+        <v>0.0754579352146586</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2379,13 +2379,13 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0.9120278248754501</v>
+        <v>0.9097796690258328</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2399,25 +2399,25 @@
         </is>
       </c>
       <c r="D42">
-        <v>2.328550850518403</v>
+        <v>2.332214657937738</v>
       </c>
       <c r="E42">
-        <v>2.375560612447569</v>
+        <v>2.375561307067098</v>
       </c>
       <c r="F42">
-        <v>0.04700976192916646</v>
+        <v>0.04334664912936008</v>
       </c>
       <c r="G42">
-        <v>-0.1428628747361482</v>
+        <v>-0.1457337787391516</v>
       </c>
       <c r="H42">
-        <v>0.2368823985944811</v>
+        <v>0.2324270769978718</v>
       </c>
       <c r="I42">
-        <v>2.018841972839061</v>
+        <v>1.858604609221064</v>
       </c>
       <c r="J42">
-        <v>0.4882586768498665</v>
+        <v>0.5184534277647421</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>0.5961392227840887</v>
+        <v>0.5949432329953592</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2448,25 +2448,25 @@
         </is>
       </c>
       <c r="D43">
-        <v>2.327663122467758</v>
+        <v>2.332160229988872</v>
       </c>
       <c r="E43">
-        <v>2.538140299683232</v>
+        <v>2.538140299683225</v>
       </c>
       <c r="F43">
-        <v>0.2104771772154732</v>
+        <v>0.2059800696943536</v>
       </c>
       <c r="G43">
-        <v>0.0658577662992737</v>
+        <v>0.06236048639855499</v>
       </c>
       <c r="H43">
-        <v>0.3550965881316727</v>
+        <v>0.3495996529901523</v>
       </c>
       <c r="I43">
-        <v>9.042424360460204</v>
+        <v>8.832157715653032</v>
       </c>
       <c r="J43">
-        <v>0.01895754807928951</v>
+        <v>0.01972283558073018</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2477,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="M43">
-        <v>0.4128154230396275</v>
+        <v>0.445115907946472</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2497,25 +2497,25 @@
         </is>
       </c>
       <c r="D44">
-        <v>2.538140299683223</v>
+        <v>2.538140299683222</v>
       </c>
       <c r="E44">
-        <v>2.586284951871228</v>
+        <v>2.590051534073125</v>
       </c>
       <c r="F44">
-        <v>0.04814465218800511</v>
+        <v>0.05191123438990367</v>
       </c>
       <c r="G44">
-        <v>-0.08955335129383994</v>
+        <v>-0.08339429313368812</v>
       </c>
       <c r="H44">
-        <v>0.1858426556698501</v>
+        <v>0.1872167619134955</v>
       </c>
       <c r="I44">
-        <v>1.896847553857203</v>
+        <v>2.045246844564998</v>
       </c>
       <c r="J44">
-        <v>0.3469707721734031</v>
+        <v>0.3093020865654894</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2526,13 +2526,13 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>0.7680312217998135</v>
+        <v>0.7421500050895999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2581,7 +2581,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2595,25 +2595,25 @@
         </is>
       </c>
       <c r="D46">
-        <v>2.538140299683226</v>
+        <v>2.538140299683231</v>
       </c>
       <c r="E46">
-        <v>2.697934368694944</v>
+        <v>2.712621292854394</v>
       </c>
       <c r="F46">
-        <v>0.1597940690117191</v>
+        <v>0.1744809931711638</v>
       </c>
       <c r="G46">
-        <v>0.0160811011967274</v>
+        <v>0.02964940556077814</v>
       </c>
       <c r="H46">
-        <v>0.3035070368267108</v>
+        <v>0.3193125807815496</v>
       </c>
       <c r="I46">
-        <v>6.295714584085927</v>
+        <v>6.874363611536357</v>
       </c>
       <c r="J46">
-        <v>0.03840340273508602</v>
+        <v>0.03127700490537189</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2624,13 +2624,13 @@
         <v>1</v>
       </c>
       <c r="M46">
-        <v>0.3531781092717563</v>
+        <v>0.3834856310619161</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2644,25 +2644,25 @@
         </is>
       </c>
       <c r="D47">
-        <v>6.848290622803901</v>
+        <v>6.866563139462621</v>
       </c>
       <c r="E47">
-        <v>5.441696710889643</v>
+        <v>5.441696710876834</v>
       </c>
       <c r="F47">
-        <v>-1.406593911914258</v>
+        <v>-1.424866428585787</v>
       </c>
       <c r="G47">
-        <v>-4.394451034233184</v>
+        <v>-4.378449716363695</v>
       </c>
       <c r="H47">
-        <v>1.581263210404667</v>
+        <v>1.528716859192122</v>
       </c>
       <c r="I47">
-        <v>-20.53934316441663</v>
+        <v>-20.75079482480805</v>
       </c>
       <c r="J47">
-        <v>0.2310162061382826</v>
+        <v>0.2222853661014497</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>0.7522300431411013</v>
+        <v>0.747857720600035</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2693,25 +2693,25 @@
         </is>
       </c>
       <c r="D48">
-        <v>6.852960485995165</v>
+        <v>6.866552638690923</v>
       </c>
       <c r="E48">
-        <v>6.591158548346657</v>
+        <v>6.591152817823406</v>
       </c>
       <c r="F48">
-        <v>-0.2618019376485092</v>
+        <v>-0.2753998208675161</v>
       </c>
       <c r="G48">
-        <v>-3.110009627259566</v>
+        <v>-3.100653302627117</v>
       </c>
       <c r="H48">
-        <v>2.586405751962548</v>
+        <v>2.549853660892085</v>
       </c>
       <c r="I48">
-        <v>-3.820275021044297</v>
+        <v>-4.010743605397013</v>
       </c>
       <c r="J48">
-        <v>0.7889505672529816</v>
+        <v>0.7766971845925295</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>0.9313837563421024</v>
+        <v>0.9295452980219808</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2742,25 +2742,25 @@
         </is>
       </c>
       <c r="D49">
-        <v>6.591660461972968</v>
+        <v>6.591514466481987</v>
       </c>
       <c r="E49">
-        <v>6.053370927566542</v>
+        <v>6.069143955707469</v>
       </c>
       <c r="F49">
-        <v>-0.5382895344064257</v>
+        <v>-0.522370510774518</v>
       </c>
       <c r="G49">
-        <v>-2.462320888977404</v>
+        <v>-2.451837779706402</v>
       </c>
       <c r="H49">
-        <v>1.385741820164553</v>
+        <v>1.407096758157366</v>
       </c>
       <c r="I49">
-        <v>-8.166220598160313</v>
+        <v>-7.924893640616051</v>
       </c>
       <c r="J49">
-        <v>0.4388653683072901</v>
+        <v>0.4522742782606974</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2771,13 +2771,13 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>0.9997089461462456</v>
+        <v>0.9996376335563179</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2826,7 +2826,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2840,25 +2840,25 @@
         </is>
       </c>
       <c r="D51">
-        <v>6.59158001013266</v>
+        <v>6.591660520323245</v>
       </c>
       <c r="E51">
-        <v>6.242144985203292</v>
+        <v>6.266672674985772</v>
       </c>
       <c r="F51">
-        <v>-0.3494350249293684</v>
+        <v>-0.3249878453374726</v>
       </c>
       <c r="G51">
-        <v>-2.307944880570919</v>
+        <v>-2.238889713972483</v>
       </c>
       <c r="H51">
-        <v>1.609074830712182</v>
+        <v>1.588914023297538</v>
       </c>
       <c r="I51">
-        <v>-5.301233154906902</v>
+        <v>-4.930287965156551</v>
       </c>
       <c r="J51">
-        <v>0.6098816502586638</v>
+        <v>0.6264670499699984</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>0.547530993451675</v>
+        <v>0.5200086538958213</v>
       </c>
     </row>
     <row r="52">
@@ -2938,25 +2938,25 @@
         </is>
       </c>
       <c r="D53">
-        <v>0.3153355993272437</v>
+        <v>0.3153352424376289</v>
       </c>
       <c r="E53">
-        <v>0.3157231349461231</v>
+        <v>0.3157304535109755</v>
       </c>
       <c r="F53">
-        <v>0.0003875356188793529</v>
+        <v>0.0003952110733465017</v>
       </c>
       <c r="G53">
-        <v>-0.00261744930149703</v>
+        <v>-0.002655772958540206</v>
       </c>
       <c r="H53">
-        <v>0.003392520539255736</v>
+        <v>0.003446195105233209</v>
       </c>
       <c r="I53">
-        <v>0.1228962475870612</v>
+        <v>0.125330448411478</v>
       </c>
       <c r="J53">
-        <v>0.7090485357599001</v>
+        <v>0.7078507854183568</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>0.3458447272586079</v>
+        <v>0.3452842744354752</v>
       </c>
     </row>
     <row r="54">
@@ -2987,25 +2987,25 @@
         </is>
       </c>
       <c r="D54">
-        <v>0.3157230535705502</v>
+        <v>0.3157304562415406</v>
       </c>
       <c r="E54">
-        <v>0.3154075004466786</v>
+        <v>0.3154071899154539</v>
       </c>
       <c r="F54">
-        <v>-0.0003155531238716422</v>
+        <v>-0.0003232663260867559</v>
       </c>
       <c r="G54">
-        <v>-0.004183451567311045</v>
+        <v>-0.004237315832375632</v>
       </c>
       <c r="H54">
-        <v>0.003552345319567761</v>
+        <v>0.003590783180202121</v>
       </c>
       <c r="I54">
-        <v>-0.09994617760819607</v>
+        <v>-0.1023868048508599</v>
       </c>
       <c r="J54">
-        <v>0.8119454255237746</v>
+        <v>0.8096894602134965</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="M54">
-        <v>0.04229615597581859</v>
+        <v>0.03646049284901376</v>
       </c>
     </row>
     <row r="55">
@@ -3036,25 +3036,25 @@
         </is>
       </c>
       <c r="D55">
-        <v>0.3157046821594244</v>
+        <v>0.3157191284367973</v>
       </c>
       <c r="E55">
-        <v>0.3162806761833847</v>
+        <v>0.3162792612330411</v>
       </c>
       <c r="F55">
-        <v>0.0005759940239603648</v>
+        <v>0.00056013279624383</v>
       </c>
       <c r="G55">
-        <v>-0.001884972603326749</v>
+        <v>-0.001860071839819896</v>
       </c>
       <c r="H55">
-        <v>0.003036960651247478</v>
+        <v>0.002980337432307556</v>
       </c>
       <c r="I55">
-        <v>0.1824470958176983</v>
+        <v>0.1774149064129198</v>
       </c>
       <c r="J55">
-        <v>0.5104010062440915</v>
+        <v>0.5147676674980879</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>0.916583228695367</v>
+        <v>0.9321330704262643</v>
       </c>
     </row>
     <row r="56">
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="D56">
-        <v>0.3157231357166184</v>
+        <v>0.3157333588089347</v>
       </c>
       <c r="E56">
-        <v>0.3151123796484406</v>
+        <v>0.3152920904522567</v>
       </c>
       <c r="F56">
-        <v>-0.0006107560681777322</v>
+        <v>-0.0004412683566780214</v>
       </c>
       <c r="G56">
-        <v>-0.004483032621473771</v>
+        <v>-0.006088231250705574</v>
       </c>
       <c r="H56">
-        <v>0.003261520485118307</v>
+        <v>0.005205694537349531</v>
       </c>
       <c r="I56">
-        <v>-0.1934467256545699</v>
+        <v>-0.1397598145291495</v>
       </c>
       <c r="J56">
-        <v>0.6502258100576246</v>
+        <v>0.8196572960007106</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>0.5368706021295284</v>
+        <v>0.3412674915381697</v>
       </c>
     </row>
     <row r="57">
@@ -3183,25 +3183,25 @@
         </is>
       </c>
       <c r="D58">
-        <v>430.2111944878837</v>
+        <v>430.2137702149078</v>
       </c>
       <c r="E58">
-        <v>409.719741372384</v>
+        <v>409.8348775694029</v>
       </c>
       <c r="F58">
-        <v>-20.49145311549982</v>
+        <v>-20.37889264550478</v>
       </c>
       <c r="G58">
-        <v>-32.13771866337567</v>
+        <v>-31.77094610573647</v>
       </c>
       <c r="H58">
-        <v>-8.845187567623974</v>
+        <v>-8.986839185273084</v>
       </c>
       <c r="I58">
-        <v>-4.763114809202607</v>
+        <v>-4.73692244563087</v>
       </c>
       <c r="J58">
-        <v>0.01125339679453341</v>
+        <v>0.01074480726525029</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="M58">
-        <v>0.6943840068664153</v>
+        <v>0.6675276327245081</v>
       </c>
     </row>
     <row r="59">
@@ -3232,25 +3232,25 @@
         </is>
       </c>
       <c r="D59">
-        <v>409.622170524124</v>
+        <v>409.8034587840996</v>
       </c>
       <c r="E59">
-        <v>400.7567577842185</v>
+        <v>400.7599321827772</v>
       </c>
       <c r="F59">
-        <v>-8.86541273990559</v>
+        <v>-9.043526601322419</v>
       </c>
       <c r="G59">
-        <v>-22.96319691387236</v>
+        <v>-22.83519271858545</v>
       </c>
       <c r="H59">
-        <v>5.232371434061177</v>
+        <v>4.748139515940606</v>
       </c>
       <c r="I59">
-        <v>-2.164290260110195</v>
+        <v>-2.206796064668381</v>
       </c>
       <c r="J59">
-        <v>0.1391524428753107</v>
+        <v>0.128166862355742</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>0.9813730342446082</v>
+        <v>0.9798984110099337</v>
       </c>
     </row>
     <row r="60">
@@ -3281,25 +3281,25 @@
         </is>
       </c>
       <c r="D60">
-        <v>409.627669231335</v>
+        <v>409.7887912303106</v>
       </c>
       <c r="E60">
-        <v>397.4039510398969</v>
+        <v>397.4082034531409</v>
       </c>
       <c r="F60">
-        <v>-12.2237181914381</v>
+        <v>-12.38058777716968</v>
       </c>
       <c r="G60">
-        <v>-25.78168135415108</v>
+        <v>-25.64593790490677</v>
       </c>
       <c r="H60">
-        <v>1.33424497127487</v>
+        <v>0.8847623505674029</v>
       </c>
       <c r="I60">
-        <v>-2.984104617340882</v>
+        <v>-3.021211912604879</v>
       </c>
       <c r="J60">
-        <v>0.06408908599845142</v>
+        <v>0.05905932557481774</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>0.8915837031056246</v>
+        <v>0.8863287092242488</v>
       </c>
     </row>
     <row r="61">
@@ -3330,25 +3330,25 @@
         </is>
       </c>
       <c r="D61">
-        <v>409.6140990578524</v>
+        <v>409.8001771516513</v>
       </c>
       <c r="E61">
-        <v>390.593337227264</v>
+        <v>389.0557932526642</v>
       </c>
       <c r="F61">
-        <v>-19.02076183058843</v>
+        <v>-20.74438389898702</v>
       </c>
       <c r="G61">
-        <v>-32.06255878500485</v>
+        <v>-34.34022806327768</v>
       </c>
       <c r="H61">
-        <v>-5.978964876172014</v>
+        <v>-7.148539734696365</v>
       </c>
       <c r="I61">
-        <v>-4.643580842148212</v>
+        <v>-5.062072945690876</v>
       </c>
       <c r="J61">
-        <v>0.01885020510643454</v>
+        <v>0.0166752522478707</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="M61">
-        <v>0.2323660201923865</v>
+        <v>0.7409446315743013</v>
       </c>
     </row>
     <row r="62">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="D63">
-        <v>1.948268149331924</v>
+        <v>1.948271209719626</v>
       </c>
       <c r="E63">
-        <v>1.943024357263128</v>
+        <v>1.943111261665812</v>
       </c>
       <c r="F63">
-        <v>-0.00524379206879628</v>
+        <v>-0.005159948053814313</v>
       </c>
       <c r="G63">
-        <v>-0.01782531154857997</v>
+        <v>-0.0174324185087292</v>
       </c>
       <c r="H63">
-        <v>0.007337727410987411</v>
+        <v>0.007112522401100572</v>
       </c>
       <c r="I63">
-        <v>-0.2691514548751626</v>
+        <v>-0.2648475236954754</v>
       </c>
       <c r="J63">
-        <v>0.2766432087978002</v>
+        <v>0.2732597245260793</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="M63">
-        <v>0.9936804682547112</v>
+        <v>0.9949529799195193</v>
       </c>
     </row>
     <row r="64">
@@ -3477,25 +3477,25 @@
         </is>
       </c>
       <c r="D64">
-        <v>1.943039652383867</v>
+        <v>1.943139339343058</v>
       </c>
       <c r="E64">
-        <v>1.941265305603797</v>
+        <v>1.941265139922319</v>
       </c>
       <c r="F64">
-        <v>-0.00177434678006975</v>
+        <v>-0.00187419942073911</v>
       </c>
       <c r="G64">
-        <v>-0.01558402602800314</v>
+        <v>-0.01525134800736336</v>
       </c>
       <c r="H64">
-        <v>0.01203533246786364</v>
+        <v>0.01150294916588514</v>
       </c>
       <c r="I64">
-        <v>-0.09131809419806994</v>
+        <v>-0.09645213715722231</v>
       </c>
       <c r="J64">
-        <v>0.7100525165459641</v>
+        <v>0.6859026771126462</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>0.99994683652827</v>
+        <v>0.9999650763886551</v>
       </c>
     </row>
     <row r="65">
@@ -3526,25 +3526,25 @@
         </is>
       </c>
       <c r="D65">
-        <v>1.943056409485883</v>
+        <v>1.943137138087516</v>
       </c>
       <c r="E65">
-        <v>1.939257543721702</v>
+        <v>1.939257354679854</v>
       </c>
       <c r="F65">
-        <v>-0.003798865764180969</v>
+        <v>-0.003879783407662445</v>
       </c>
       <c r="G65">
-        <v>-0.0161520476632651</v>
+        <v>-0.01586723308614525</v>
       </c>
       <c r="H65">
-        <v>0.008554316134903159</v>
+        <v>0.008107666270820355</v>
       </c>
       <c r="I65">
-        <v>-0.1955098032993349</v>
+        <v>-0.1996659593198359</v>
       </c>
       <c r="J65">
-        <v>0.3999165716671191</v>
+        <v>0.3787781174855744</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <v>0.999114871858075</v>
+        <v>0.9990206494416535</v>
       </c>
     </row>
     <row r="66">
@@ -3575,25 +3575,25 @@
         </is>
       </c>
       <c r="D66">
-        <v>1.943043816759888</v>
+        <v>1.943141405492432</v>
       </c>
       <c r="E66">
-        <v>1.936367353770543</v>
+        <v>1.935721994105011</v>
       </c>
       <c r="F66">
-        <v>-0.006676462989344632</v>
+        <v>-0.007419411387421295</v>
       </c>
       <c r="G66">
-        <v>-0.01991462524686022</v>
+        <v>-0.02031028016476231</v>
       </c>
       <c r="H66">
-        <v>0.006561699268170957</v>
+        <v>0.005471457389919725</v>
       </c>
       <c r="I66">
-        <v>-0.3436084627508776</v>
+        <v>-0.3818256029360386</v>
       </c>
       <c r="J66">
-        <v>0.2068339965039547</v>
+        <v>0.1643951673923553</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>0.9861669451029793</v>
+        <v>0.9823710929996634</v>
       </c>
     </row>
     <row r="67">
@@ -3673,25 +3673,25 @@
         </is>
       </c>
       <c r="D68">
-        <v>2.771225627884546</v>
+        <v>2.771240426322375</v>
       </c>
       <c r="E68">
-        <v>2.841602092123555</v>
+        <v>2.841930055237366</v>
       </c>
       <c r="F68">
-        <v>0.07037646423900969</v>
+        <v>0.07068962891499055</v>
       </c>
       <c r="G68">
-        <v>-0.06469419082836662</v>
+        <v>-0.06133031200750678</v>
       </c>
       <c r="H68">
-        <v>0.205447119306386</v>
+        <v>0.2027095698374879</v>
       </c>
       <c r="I68">
-        <v>2.53954292031907</v>
+        <v>2.550829882660181</v>
       </c>
       <c r="J68">
-        <v>0.1958647064806621</v>
+        <v>0.1869238745852355</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>0.9736762231794301</v>
+        <v>0.9641668787557865</v>
       </c>
     </row>
     <row r="69">
@@ -3722,25 +3722,25 @@
         </is>
       </c>
       <c r="D69">
-        <v>2.839335005286892</v>
+        <v>2.840990555052098</v>
       </c>
       <c r="E69">
-        <v>2.86704576363682</v>
+        <v>2.867083444299015</v>
       </c>
       <c r="F69">
-        <v>0.0277107583499275</v>
+        <v>0.02609288924691698</v>
       </c>
       <c r="G69">
-        <v>-0.1400966209661139</v>
+        <v>-0.1386515958365624</v>
       </c>
       <c r="H69">
-        <v>0.1955181376659689</v>
+        <v>0.1908373743303964</v>
       </c>
       <c r="I69">
-        <v>0.9759594517142067</v>
+        <v>0.9184433647805101</v>
       </c>
       <c r="J69">
-        <v>0.6355829920308547</v>
+        <v>0.6489152706289032</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>0.991968658144788</v>
+        <v>0.9886560494352415</v>
       </c>
     </row>
     <row r="70">
@@ -3771,25 +3771,25 @@
         </is>
       </c>
       <c r="D70">
-        <v>2.840525949986456</v>
+        <v>2.841034999317064</v>
       </c>
       <c r="E70">
-        <v>2.843171654728482</v>
+        <v>2.843240340532977</v>
       </c>
       <c r="F70">
-        <v>0.002645704742025528</v>
+        <v>0.002205341215912867</v>
       </c>
       <c r="G70">
-        <v>-0.1542310661446231</v>
+        <v>-0.1511357142191885</v>
       </c>
       <c r="H70">
-        <v>0.1595224756286741</v>
+        <v>0.1555463966510142</v>
       </c>
       <c r="I70">
-        <v>0.09314136848628836</v>
+        <v>0.07762457049782889</v>
       </c>
       <c r="J70">
-        <v>0.9605710281673863</v>
+        <v>0.9663700805915419</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="M70">
-        <v>0.95810937170445</v>
+        <v>0.9439177805828365</v>
       </c>
     </row>
     <row r="71">
@@ -3820,25 +3820,25 @@
         </is>
       </c>
       <c r="D71">
-        <v>2.841758573884985</v>
+        <v>2.841529888670257</v>
       </c>
       <c r="E71">
-        <v>2.926898197667955</v>
+        <v>2.932506021723353</v>
       </c>
       <c r="F71">
-        <v>0.08513962378297039</v>
+        <v>0.09097613305309646</v>
       </c>
       <c r="G71">
-        <v>-0.06758891865277016</v>
+        <v>-0.05794586566120791</v>
       </c>
       <c r="H71">
-        <v>0.2378681662187109</v>
+        <v>0.2398981317674008</v>
       </c>
       <c r="I71">
-        <v>2.996018893560529</v>
+        <v>3.20166025407075</v>
       </c>
       <c r="J71">
-        <v>0.1741509923555374</v>
+        <v>0.1471130267084311</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="M71">
-        <v>0.7951163346389026</v>
+        <v>0.8212913909258585</v>
       </c>
     </row>
     <row r="72">
@@ -3918,25 +3918,25 @@
         </is>
       </c>
       <c r="D73">
-        <v>5.583867041105841</v>
+        <v>5.583311313835311</v>
       </c>
       <c r="E73">
-        <v>5.525482094818368</v>
+        <v>5.483461997581386</v>
       </c>
       <c r="F73">
-        <v>-0.05838494628747413</v>
+        <v>-0.09984931625392426</v>
       </c>
       <c r="G73">
-        <v>-1.071976348304141</v>
+        <v>-1.098583517544416</v>
       </c>
       <c r="H73">
-        <v>0.9552064557291924</v>
+        <v>0.8988848850365675</v>
       </c>
       <c r="I73">
-        <v>-1.045600582135485</v>
+        <v>-1.788353015646827</v>
       </c>
       <c r="J73">
-        <v>0.8662401433987721</v>
+        <v>0.7712198193670468</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>0.9984314835722887</v>
+        <v>0.998167240215236</v>
       </c>
     </row>
     <row r="74">
@@ -3967,25 +3967,25 @@
         </is>
       </c>
       <c r="D74">
-        <v>5.523315766740235</v>
+        <v>5.483450118493105</v>
       </c>
       <c r="E74">
-        <v>5.714420479698197</v>
+        <v>5.714364609931082</v>
       </c>
       <c r="F74">
-        <v>0.1911047129579628</v>
+        <v>0.2309144914379769</v>
       </c>
       <c r="G74">
-        <v>-1.2703780046271</v>
+        <v>-1.203835725514056</v>
       </c>
       <c r="H74">
-        <v>1.652587430543026</v>
+        <v>1.66566470839001</v>
       </c>
       <c r="I74">
-        <v>3.459963562263425</v>
+        <v>4.211116841552195</v>
       </c>
       <c r="J74">
-        <v>0.7052861346091143</v>
+        <v>0.6438377991583484</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>0.663318413328859</v>
+        <v>0.6712364536979576</v>
       </c>
     </row>
     <row r="75">
@@ -4016,25 +4016,25 @@
         </is>
       </c>
       <c r="D75">
-        <v>5.522953577512842</v>
+        <v>5.482791860141587</v>
       </c>
       <c r="E75">
-        <v>5.840061574115506</v>
+        <v>5.840495680439751</v>
       </c>
       <c r="F75">
-        <v>0.3171079966026632</v>
+        <v>0.3577038202981643</v>
       </c>
       <c r="G75">
-        <v>-0.9300653389647285</v>
+        <v>-0.8467873535931619</v>
       </c>
       <c r="H75">
-        <v>1.564281332170055</v>
+        <v>1.562194994189491</v>
       </c>
       <c r="I75">
-        <v>5.7416379144267</v>
+        <v>6.524118175971155</v>
       </c>
       <c r="J75">
-        <v>0.4776369727421054</v>
+        <v>0.4143286704071242</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>0.8622167181625052</v>
+        <v>0.8851316495005027</v>
       </c>
     </row>
     <row r="76">
@@ -4065,25 +4065,25 @@
         </is>
       </c>
       <c r="D76">
-        <v>5.525669808315548</v>
+        <v>5.483082524840212</v>
       </c>
       <c r="E76">
-        <v>5.644751024459976</v>
+        <v>5.622861454890106</v>
       </c>
       <c r="F76">
-        <v>0.1190812161444288</v>
+        <v>0.1397789300498946</v>
       </c>
       <c r="G76">
-        <v>-1.153161458305643</v>
+        <v>-1.059478939217883</v>
       </c>
       <c r="H76">
-        <v>1.3913238905945</v>
+        <v>1.339036799317672</v>
       </c>
       <c r="I76">
-        <v>2.155054867108133</v>
+        <v>2.549276422826921</v>
       </c>
       <c r="J76">
-        <v>0.7852361681925821</v>
+        <v>0.7353357509890049</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="M76">
-        <v>0.7873021625055505</v>
+        <v>0.7981428562763699</v>
       </c>
     </row>
   </sheetData>
@@ -4254,37 +4254,37 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.3190629929315109</v>
+        <v>0.319129660769912</v>
       </c>
       <c r="H2">
-        <v>0.3206914106929256</v>
+        <v>0.320691410692911</v>
       </c>
       <c r="I2">
-        <v>0.00162841776141463</v>
+        <v>0.001561749922998903</v>
       </c>
       <c r="J2">
-        <v>0.001234216092627639</v>
+        <v>0.001269671270600849</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>-0.002299408682489893</v>
+        <v>-0.002478910721049641</v>
       </c>
       <c r="M2">
-        <v>0.005556244205319152</v>
+        <v>0.005602410567047448</v>
       </c>
       <c r="N2">
-        <v>0.5103750035229504</v>
+        <v>0.4893778657963426</v>
       </c>
       <c r="O2">
-        <v>0.2786964623461505</v>
+        <v>0.3063421102248072</v>
       </c>
       <c r="P2">
-        <v>0.04216774238543708</v>
+        <v>0.05063912699643502</v>
       </c>
       <c r="Q2">
-        <v>0.4834879092884048</v>
+        <v>0.4662949776441857</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -4295,16 +4295,16 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0.003422727660973646</v>
+        <v>0.003356809149149321</v>
       </c>
       <c r="U2">
-        <v>0.001309372421206919</v>
+        <v>0.001379212691715506</v>
       </c>
       <c r="V2">
-        <v>0.004470105008608635</v>
+        <v>0.004452924801782839</v>
       </c>
       <c r="W2">
-        <v>0.001542598725996101</v>
+        <v>0.001395556126037248</v>
       </c>
     </row>
     <row r="3">
@@ -4337,37 +4337,37 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>0.3190628451357968</v>
+        <v>0.3191293578435881</v>
       </c>
       <c r="H3">
-        <v>0.3176096175964226</v>
+        <v>0.3176120218266411</v>
       </c>
       <c r="I3">
-        <v>-0.001453227539374158</v>
+        <v>-0.001517336016947011</v>
       </c>
       <c r="J3">
-        <v>0.0008586781242477076</v>
+        <v>0.0008674110755398351</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>-0.00418592456331422</v>
+        <v>-0.004277825189460927</v>
       </c>
       <c r="M3">
-        <v>0.001279469484565903</v>
+        <v>0.001243153155566904</v>
       </c>
       <c r="N3">
-        <v>-0.4554674922288893</v>
+        <v>-0.4754611193404177</v>
       </c>
       <c r="O3">
-        <v>0.1891462214569604</v>
+        <v>0.1785569185590977</v>
       </c>
       <c r="P3">
-        <v>0.2743740238672312</v>
+        <v>0.3082312883903104</v>
       </c>
       <c r="Q3">
-        <v>0.4911506851626125</v>
+        <v>0.4869804593347412</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -4378,16 +4378,16 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0.001814376683462574</v>
+        <v>0.001762310997269195</v>
       </c>
       <c r="U3">
-        <v>3.044557092772668E-07</v>
+        <v>2.608244950331623E-07</v>
       </c>
       <c r="V3">
-        <v>0.004374840810243658</v>
+        <v>0.004352982280195467</v>
       </c>
       <c r="W3">
-        <v>0.4866654511999496</v>
+        <v>0.5143549607521796</v>
       </c>
     </row>
     <row r="4">
@@ -4420,37 +4420,37 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0.3176092318311073</v>
+        <v>0.3176116667510588</v>
       </c>
       <c r="H4">
-        <v>0.3178343161300924</v>
+        <v>0.3178552138619586</v>
       </c>
       <c r="I4">
-        <v>0.0002250842989850668</v>
+        <v>0.0002435471108998467</v>
       </c>
       <c r="J4">
-        <v>0.00102299932544593</v>
+        <v>0.001020680001878749</v>
       </c>
       <c r="K4">
         <v>3</v>
       </c>
       <c r="L4">
-        <v>-0.00303055612458806</v>
+        <v>-0.003004712189956147</v>
       </c>
       <c r="M4">
-        <v>0.003480724722558193</v>
+        <v>0.00349180641175584</v>
       </c>
       <c r="N4">
-        <v>0.0708683112538612</v>
+        <v>0.07668078235008184</v>
       </c>
       <c r="O4">
-        <v>0.8399743913592389</v>
+        <v>0.8267767079075976</v>
       </c>
       <c r="P4">
-        <v>0.1703001167107493</v>
+        <v>0.1647771885861717</v>
       </c>
       <c r="Q4">
-        <v>0.825251035653417</v>
+        <v>0.8270419102634639</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -4461,16 +4461,16 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>0.0009427803450924147</v>
+        <v>0.0009305486352677717</v>
       </c>
       <c r="U4">
-        <v>2.135423372936149E-07</v>
+        <v>2.236154711033322E-07</v>
       </c>
       <c r="V4">
-        <v>0.004472154437293908</v>
+        <v>0.00445835629091325</v>
       </c>
       <c r="W4">
-        <v>0.6722599635497423</v>
+        <v>0.6729247217375458</v>
       </c>
     </row>
     <row r="5">
@@ -4503,37 +4503,37 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.3176091753203997</v>
+        <v>0.3176116123449689</v>
       </c>
       <c r="H5">
-        <v>0.3185644779285982</v>
+        <v>0.3185645082059152</v>
       </c>
       <c r="I5">
-        <v>0.0009553026081983861</v>
+        <v>0.0009528958609462405</v>
       </c>
       <c r="J5">
-        <v>0.001151378838601845</v>
+        <v>0.001151267383074306</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>-0.002708898722691901</v>
+        <v>-0.002710950768712229</v>
       </c>
       <c r="M5">
-        <v>0.004619503939088674</v>
+        <v>0.00461674249060471</v>
       </c>
       <c r="N5">
-        <v>0.3007792854959842</v>
+        <v>0.3000192133753811</v>
       </c>
       <c r="O5">
-        <v>0.4675607208059289</v>
+        <v>0.4685391854583187</v>
       </c>
       <c r="P5">
-        <v>0.199738178848319</v>
+        <v>0.1993029831510756</v>
       </c>
       <c r="Q5">
-        <v>0.4734218038422473</v>
+        <v>0.4735724180152905</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -4544,16 +4544,16 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0.001071377587647318</v>
+        <v>0.00107264271890662</v>
       </c>
       <c r="U5">
-        <v>2.117985653013393E-07</v>
+        <v>2.106766368639928E-07</v>
       </c>
       <c r="V5">
-        <v>0.004762396849982416</v>
+        <v>0.004761105811606246</v>
       </c>
       <c r="W5">
-        <v>0.7114450110293856</v>
+        <v>0.7115648175340038</v>
       </c>
     </row>
     <row r="6">
@@ -4586,37 +4586,37 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0.3176092357715212</v>
+        <v>0.3176116955031084</v>
       </c>
       <c r="H6">
-        <v>0.3180293554112534</v>
+        <v>0.3179737349769436</v>
       </c>
       <c r="I6">
-        <v>0.0004201196397321896</v>
+        <v>0.0003620394738352333</v>
       </c>
       <c r="J6">
-        <v>0.000972656382077265</v>
+        <v>0.0009649089863284297</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
-        <v>-0.002675307069720221</v>
+        <v>-0.002708731564640725</v>
       </c>
       <c r="M6">
-        <v>0.0035155463491846</v>
+        <v>0.003432810512311192</v>
       </c>
       <c r="N6">
-        <v>0.1322756369825503</v>
+        <v>0.1139880800868336</v>
       </c>
       <c r="O6">
-        <v>0.6949539644488112</v>
+        <v>0.7324641077731635</v>
       </c>
       <c r="P6">
-        <v>0.03766431836403239</v>
+        <v>0.04868119341933985</v>
       </c>
       <c r="Q6">
-        <v>0.4355566929311028</v>
+        <v>0.4262503465949887</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -4627,16 +4627,16 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0.0004635366584902323</v>
+        <v>0.0005126477169282288</v>
       </c>
       <c r="U6">
-        <v>4.163919606032297E-07</v>
+        <v>3.794845769166137E-07</v>
       </c>
       <c r="V6">
-        <v>0.004410094511171526</v>
+        <v>0.004428041391931863</v>
       </c>
       <c r="W6">
-        <v>0.6370246948414546</v>
+        <v>0.6250817970165854</v>
       </c>
     </row>
     <row r="7">
@@ -4669,37 +4669,37 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>439.9038217031748</v>
+        <v>439.9031505492183</v>
       </c>
       <c r="H7">
-        <v>422.229408753444</v>
+        <v>422.2294088587337</v>
       </c>
       <c r="I7">
-        <v>-17.67441294973086</v>
+        <v>-17.67374169048453</v>
       </c>
       <c r="J7">
-        <v>6.501052739992676</v>
+        <v>6.50117781658187</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>-38.36366422257507</v>
+        <v>-38.3633910128579</v>
       </c>
       <c r="M7">
-        <v>3.014838323113359</v>
+        <v>3.01590763188884</v>
       </c>
       <c r="N7">
-        <v>-4.017790270905324</v>
+        <v>-4.017643808283459</v>
       </c>
       <c r="O7">
-        <v>0.07262898000982476</v>
+        <v>0.07263851181477721</v>
       </c>
       <c r="P7">
-        <v>8.036492108010052E-06</v>
+        <v>8.034090669850613E-06</v>
       </c>
       <c r="Q7">
-        <v>0.9889160873100195</v>
+        <v>0.9889183151319325</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -4710,16 +4710,16 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>21.27219037150927</v>
+        <v>21.27253423023153</v>
       </c>
       <c r="U7">
-        <v>0.002196826223954745</v>
+        <v>0.002196995671296426</v>
       </c>
       <c r="V7">
-        <v>28.69535233375088</v>
+        <v>28.69534510815162</v>
       </c>
       <c r="W7">
-        <v>0.6643814892471324</v>
+        <v>0.6643973226884328</v>
       </c>
     </row>
     <row r="8">
@@ -4752,37 +4752,37 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>439.9024129871332</v>
+        <v>439.901753770717</v>
       </c>
       <c r="H8">
-        <v>429.8342967628469</v>
+        <v>429.8208487878458</v>
       </c>
       <c r="I8">
-        <v>-10.06811622428629</v>
+        <v>-10.08090498287113</v>
       </c>
       <c r="J8">
-        <v>9.442376138494339</v>
+        <v>9.443117912141249</v>
       </c>
       <c r="K8">
         <v>3</v>
       </c>
       <c r="L8">
-        <v>-40.11797127933664</v>
+        <v>-40.13312069272344</v>
       </c>
       <c r="M8">
-        <v>19.98173883076407</v>
+        <v>19.97131072698119</v>
       </c>
       <c r="N8">
-        <v>-2.288715844025337</v>
+        <v>-2.291626458967344</v>
       </c>
       <c r="O8">
-        <v>0.3644975258807731</v>
+        <v>0.3640066876838972</v>
       </c>
       <c r="P8">
-        <v>9.870648043364127E-07</v>
+        <v>9.772872351376805E-07</v>
       </c>
       <c r="Q8">
-        <v>0.8708491495458119</v>
+        <v>0.870939103515934</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4793,16 +4793,16 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>17.84068337721665</v>
+        <v>17.86175149524822</v>
       </c>
       <c r="U8">
-        <v>0.003898200315043696</v>
+        <v>0.003894834515565287</v>
       </c>
       <c r="V8">
-        <v>31.45176072163853</v>
+        <v>31.45082015676517</v>
       </c>
       <c r="W8">
-        <v>0.824236257636354</v>
+        <v>0.8242787419905112</v>
       </c>
     </row>
     <row r="9">
@@ -4835,37 +4835,37 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>429.8313277409174</v>
+        <v>429.8179204027277</v>
       </c>
       <c r="H9">
-        <v>423.541584995228</v>
+        <v>423.6243151788966</v>
       </c>
       <c r="I9">
-        <v>-6.289742745689423</v>
+        <v>-6.193605223831154</v>
       </c>
       <c r="J9">
-        <v>3.877311146098841</v>
+        <v>3.894226148424329</v>
       </c>
       <c r="K9">
         <v>3</v>
       </c>
       <c r="L9">
-        <v>-18.62907727702702</v>
+        <v>-18.58677084182337</v>
       </c>
       <c r="M9">
-        <v>6.04959178564817</v>
+        <v>6.199560394161056</v>
       </c>
       <c r="N9">
-        <v>-1.463304868620602</v>
+        <v>-1.44098347924347</v>
       </c>
       <c r="O9">
-        <v>0.2032155511158824</v>
+        <v>0.2099580241358029</v>
       </c>
       <c r="P9">
-        <v>2.844391389089651E-13</v>
+        <v>3.155253835984695E-13</v>
       </c>
       <c r="Q9">
-        <v>0.999716615452511</v>
+        <v>0.9997384097691355</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -4876,16 +4876,16 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>8.73158762328424</v>
+        <v>8.654947774763064</v>
       </c>
       <c r="U9">
-        <v>0.001059616580743435</v>
+        <v>0.001068452164497085</v>
       </c>
       <c r="V9">
-        <v>21.23690737530573</v>
+        <v>21.32955465376184</v>
       </c>
       <c r="W9">
-        <v>0.0001360065020195579</v>
+        <v>0.0001179764788901852</v>
       </c>
     </row>
     <row r="10">
@@ -4918,37 +4918,37 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>429.8315844705177</v>
+        <v>429.818154479843</v>
       </c>
       <c r="H10">
-        <v>417.9183058985104</v>
+        <v>417.9171882895802</v>
       </c>
       <c r="I10">
-        <v>-11.91327857200735</v>
+        <v>-11.90096619026277</v>
       </c>
       <c r="J10">
-        <v>5.057454613253901</v>
+        <v>5.063480075530465</v>
       </c>
       <c r="K10">
         <v>3</v>
       </c>
       <c r="L10">
-        <v>-28.00835632009727</v>
+        <v>-28.01521964851236</v>
       </c>
       <c r="M10">
-        <v>4.181799176082567</v>
+        <v>4.213287267986829</v>
       </c>
       <c r="N10">
-        <v>-2.771615442518624</v>
+        <v>-2.768837487719678</v>
       </c>
       <c r="O10">
-        <v>0.09979838255768392</v>
+        <v>0.1002736403778501</v>
       </c>
       <c r="P10">
-        <v>2.646438623798986E-12</v>
+        <v>2.630229367639458E-12</v>
       </c>
       <c r="Q10">
-        <v>0.9954420644577676</v>
+        <v>0.9954862188980136</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>8.833951335290674</v>
+        <v>8.855283373337283</v>
       </c>
       <c r="U10">
-        <v>0.002581773914008793</v>
+        <v>0.002639751718604118</v>
       </c>
       <c r="V10">
-        <v>22.64631558202587</v>
+        <v>22.65125028610274</v>
       </c>
       <c r="W10">
-        <v>0.6487351295428624</v>
+        <v>0.649623131242683</v>
       </c>
     </row>
     <row r="11">
@@ -5001,37 +5001,37 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>429.8315096897875</v>
+        <v>429.8181014408388</v>
       </c>
       <c r="H11">
-        <v>415.0544834054531</v>
+        <v>414.8878855619794</v>
       </c>
       <c r="I11">
-        <v>-14.77702628433436</v>
+        <v>-14.93021587885936</v>
       </c>
       <c r="J11">
-        <v>5.603370477433701</v>
+        <v>5.643409360231745</v>
       </c>
       <c r="K11">
         <v>3</v>
       </c>
       <c r="L11">
-        <v>-32.60945195737904</v>
+        <v>-32.89006314653237</v>
       </c>
       <c r="M11">
-        <v>3.055399388710329</v>
+        <v>3.029631388813646</v>
       </c>
       <c r="N11">
-        <v>-3.437864826382561</v>
+        <v>-3.473612634928637</v>
       </c>
       <c r="O11">
-        <v>0.07784478151375762</v>
+        <v>0.07728415986197656</v>
       </c>
       <c r="P11">
-        <v>3.610667320685934E-12</v>
+        <v>3.601119402674158E-12</v>
       </c>
       <c r="Q11">
-        <v>0.9952212450447355</v>
+        <v>0.9942812013322158</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -5042,16 +5042,16 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>5.889483408377254</v>
+        <v>6.172208611326779</v>
       </c>
       <c r="U11">
-        <v>4.652426021855286</v>
+        <v>4.564078792168846</v>
       </c>
       <c r="V11">
-        <v>22.47827459127926</v>
+        <v>22.5634168386414</v>
       </c>
       <c r="W11">
-        <v>0.5275292459860681</v>
+        <v>0.5528175850000676</v>
       </c>
     </row>
     <row r="12">
@@ -5084,37 +5084,37 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>1.981685256768479</v>
+        <v>1.981770928487437</v>
       </c>
       <c r="H12">
-        <v>1.963191854770372</v>
+        <v>1.96319183985796</v>
       </c>
       <c r="I12">
-        <v>-0.01849340199810703</v>
+        <v>-0.01857908862947774</v>
       </c>
       <c r="J12">
-        <v>0.01041989126231031</v>
+        <v>0.0104182879029928</v>
       </c>
       <c r="K12">
         <v>3</v>
       </c>
       <c r="L12">
-        <v>-0.05165414644730448</v>
+        <v>-0.05173473047373914</v>
       </c>
       <c r="M12">
-        <v>0.01466734245109041</v>
+        <v>0.01457655321478366</v>
       </c>
       <c r="N12">
-        <v>-0.9332159047428198</v>
+        <v>-0.9374993023869819</v>
       </c>
       <c r="O12">
-        <v>0.174021562970222</v>
+        <v>0.1725423786905823</v>
       </c>
       <c r="P12">
-        <v>0.2117555388874715</v>
+        <v>0.2131638646223143</v>
       </c>
       <c r="Q12">
-        <v>0.4613569056096266</v>
+        <v>0.4611980438975091</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -5125,16 +5125,16 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0.0123875752442685</v>
+        <v>0.01237386403430062</v>
       </c>
       <c r="U12">
-        <v>3.004756511691673E-06</v>
+        <v>3.843317883997402E-06</v>
       </c>
       <c r="V12">
-        <v>0.05699224802231811</v>
+        <v>0.05698548557055548</v>
       </c>
       <c r="W12">
-        <v>0.145836569111762</v>
+        <v>0.1446663460663185</v>
       </c>
     </row>
     <row r="13">
@@ -5167,37 +5167,37 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1.981684675825401</v>
+        <v>1.981770357912117</v>
       </c>
       <c r="H13">
-        <v>1.96565106944436</v>
+        <v>1.965645695376775</v>
       </c>
       <c r="I13">
-        <v>-0.01603360638104076</v>
+        <v>-0.01612466253534137</v>
       </c>
       <c r="J13">
-        <v>0.01079604298913722</v>
+        <v>0.01079361525530254</v>
       </c>
       <c r="K13">
         <v>3</v>
       </c>
       <c r="L13">
-        <v>-0.05039143350350458</v>
+        <v>-0.05047476352523281</v>
       </c>
       <c r="M13">
-        <v>0.01832422074142305</v>
+        <v>0.01822543845455006</v>
       </c>
       <c r="N13">
-        <v>-0.8090896890224238</v>
+        <v>-0.8136493953986385</v>
       </c>
       <c r="O13">
-        <v>0.234181874912321</v>
+        <v>0.232051382153142</v>
       </c>
       <c r="P13">
-        <v>0.01118395163182817</v>
+        <v>0.01116844649055193</v>
       </c>
       <c r="Q13">
-        <v>0.9977664570309991</v>
+        <v>0.9978515334228961</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -5208,16 +5208,16 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0.01369726946739424</v>
+        <v>0.01371184721497436</v>
       </c>
       <c r="U13">
-        <v>5.688290709761192E-06</v>
+        <v>5.707948059922477E-06</v>
       </c>
       <c r="V13">
-        <v>0.05910306897425976</v>
+        <v>0.05909111169159674</v>
       </c>
       <c r="W13">
-        <v>0.1048045974279482</v>
+        <v>0.1032550161458478</v>
       </c>
     </row>
     <row r="14">
@@ -5250,37 +5250,37 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>1.965659275306108</v>
+        <v>1.96565382311872</v>
       </c>
       <c r="H14">
-        <v>1.961540952445237</v>
+        <v>1.961245739520491</v>
       </c>
       <c r="I14">
-        <v>-0.004118322860870968</v>
+        <v>-0.004408083598229564</v>
       </c>
       <c r="J14">
-        <v>0.005584629784844738</v>
+        <v>0.005541539901015805</v>
       </c>
       <c r="K14">
         <v>3</v>
       </c>
       <c r="L14">
-        <v>-0.02189110728602746</v>
+        <v>-0.02204373678179956</v>
       </c>
       <c r="M14">
-        <v>0.01365446156428552</v>
+        <v>0.01322756958534043</v>
       </c>
       <c r="N14">
-        <v>-0.2095135669038894</v>
+        <v>-0.2242553366408978</v>
       </c>
       <c r="O14">
-        <v>0.5142972548535101</v>
+        <v>0.4844695136216154</v>
       </c>
       <c r="P14">
-        <v>4.203193683771644E-06</v>
+        <v>3.993069004337713E-06</v>
       </c>
       <c r="Q14">
-        <v>0.9985126838186595</v>
+        <v>0.9989753961912664</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -5291,16 +5291,16 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>0.01378509965474239</v>
+        <v>0.01403636913784548</v>
       </c>
       <c r="U14">
-        <v>7.432206917985261E-07</v>
+        <v>7.146468571123269E-07</v>
       </c>
       <c r="V14">
-        <v>0.02877296467823919</v>
+        <v>0.02859895846279228</v>
       </c>
       <c r="W14">
-        <v>0.4632309026152645</v>
+        <v>0.4594446271394926</v>
       </c>
     </row>
     <row r="15">
@@ -5333,37 +5333,37 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>1.965659554720974</v>
+        <v>1.965654187375057</v>
       </c>
       <c r="H15">
-        <v>1.95569627098797</v>
+        <v>1.955696099288568</v>
       </c>
       <c r="I15">
-        <v>-0.009963283733004312</v>
+        <v>-0.009958088086488305</v>
       </c>
       <c r="J15">
-        <v>0.005422539885069008</v>
+        <v>0.005422458645166474</v>
       </c>
       <c r="K15">
         <v>3</v>
       </c>
       <c r="L15">
-        <v>-0.02722022575549572</v>
+        <v>-0.02721477156735205</v>
       </c>
       <c r="M15">
-        <v>0.007293658289487094</v>
+        <v>0.007298595394375438</v>
       </c>
       <c r="N15">
-        <v>-0.5068672094857546</v>
+        <v>-0.5066042720254055</v>
       </c>
       <c r="O15">
-        <v>0.1634630942915104</v>
+        <v>0.1636146299982981</v>
       </c>
       <c r="P15">
-        <v>5.803985777763643E-06</v>
+        <v>5.771733641468657E-06</v>
       </c>
       <c r="Q15">
-        <v>0.9479401742957627</v>
+        <v>0.947902883270848</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -5374,16 +5374,16 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>0.01373435692962461</v>
+        <v>0.01373895633744279</v>
       </c>
       <c r="U15">
-        <v>6.799860030275971E-07</v>
+        <v>7.748787700283259E-07</v>
       </c>
       <c r="V15">
-        <v>0.02767522938378442</v>
+        <v>0.02767493318527492</v>
       </c>
       <c r="W15">
-        <v>0.4730807772014515</v>
+        <v>0.4730717271985554</v>
       </c>
     </row>
     <row r="16">
@@ -5416,37 +5416,37 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>1.965659414533604</v>
+        <v>1.965654040586146</v>
       </c>
       <c r="H16">
-        <v>1.952705883946115</v>
+        <v>1.952651135075837</v>
       </c>
       <c r="I16">
-        <v>-0.01295353058748931</v>
+        <v>-0.01300290551030944</v>
       </c>
       <c r="J16">
-        <v>0.005316685029531998</v>
+        <v>0.005315438867408474</v>
       </c>
       <c r="K16">
         <v>3</v>
       </c>
       <c r="L16">
-        <v>-0.02987359521608061</v>
+        <v>-0.02991900429485496</v>
       </c>
       <c r="M16">
-        <v>0.003966534041102003</v>
+        <v>0.003913193274236075</v>
       </c>
       <c r="N16">
-        <v>-0.65899160819591</v>
+        <v>-0.6615052924792427</v>
       </c>
       <c r="O16">
-        <v>0.09279855678501803</v>
+        <v>0.09198599418337317</v>
       </c>
       <c r="P16">
-        <v>1.369626127156742E-05</v>
+        <v>1.305301486798083E-05</v>
       </c>
       <c r="Q16">
-        <v>0.9121962359954086</v>
+        <v>0.9139542549941249</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -5457,16 +5457,16 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>0.01352914144995473</v>
+        <v>0.01357406870735058</v>
       </c>
       <c r="U16">
-        <v>8.05376751109937E-07</v>
+        <v>7.892768126821153E-07</v>
       </c>
       <c r="V16">
-        <v>0.0272073235150266</v>
+        <v>0.02720541384191594</v>
       </c>
       <c r="W16">
-        <v>0.4672432849072362</v>
+        <v>0.4669070076825549</v>
       </c>
     </row>
     <row r="17">
@@ -5499,37 +5499,37 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>2.16706874689131</v>
+        <v>2.163640521475306</v>
       </c>
       <c r="H17">
-        <v>2.377924955682624</v>
+        <v>2.377927281212483</v>
       </c>
       <c r="I17">
-        <v>0.2108562087913147</v>
+        <v>0.2142867597371765</v>
       </c>
       <c r="J17">
-        <v>0.06814846555919442</v>
+        <v>0.06866248273561665</v>
       </c>
       <c r="K17">
         <v>3</v>
       </c>
       <c r="L17">
-        <v>-0.006022623638297586</v>
+        <v>-0.004227904756393092</v>
       </c>
       <c r="M17">
-        <v>0.427735041220927</v>
+        <v>0.4328014242307461</v>
       </c>
       <c r="N17">
-        <v>9.730019368042239</v>
+        <v>9.903990871416212</v>
       </c>
       <c r="O17">
-        <v>0.05354293974221414</v>
+        <v>0.05243600897163925</v>
       </c>
       <c r="P17">
-        <v>5.809730474481967E-11</v>
+        <v>7.35982386146361E-11</v>
       </c>
       <c r="Q17">
-        <v>0.1934635983299994</v>
+        <v>0.1681064272229661</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -5540,16 +5540,16 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>0.2389574825170981</v>
+        <v>0.2358738420400225</v>
       </c>
       <c r="U17">
-        <v>1.457457155045578E-05</v>
+        <v>1.57509280423666E-05</v>
       </c>
       <c r="V17">
-        <v>0.3399273294327436</v>
+        <v>0.340347648413049</v>
       </c>
       <c r="W17">
-        <v>0.5245440654254153</v>
+        <v>0.5344834612633094</v>
       </c>
     </row>
     <row r="18">
@@ -5582,37 +5582,37 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>2.167036359080486</v>
+        <v>2.163598170749241</v>
       </c>
       <c r="H18">
-        <v>2.323636537722987</v>
+        <v>2.323841333631367</v>
       </c>
       <c r="I18">
-        <v>0.1566001786425012</v>
+        <v>0.1602431628821263</v>
       </c>
       <c r="J18">
-        <v>0.0499998777002062</v>
+        <v>0.04991758173557619</v>
       </c>
       <c r="K18">
         <v>3</v>
       </c>
       <c r="L18">
-        <v>-0.00252174740915731</v>
+        <v>0.001383139319044407</v>
       </c>
       <c r="M18">
-        <v>0.3157221046941596</v>
+        <v>0.3191031864452083</v>
       </c>
       <c r="N18">
-        <v>7.226467520321143</v>
+        <v>7.406327341580027</v>
       </c>
       <c r="O18">
-        <v>0.05198437459152316</v>
+        <v>0.04895046368035283</v>
       </c>
       <c r="P18">
-        <v>3.321787289678468E-13</v>
+        <v>3.366196210663475E-13</v>
       </c>
       <c r="Q18">
-        <v>0.4481444809641534</v>
+        <v>0.454240610056921</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -5620,19 +5620,19 @@
         </is>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18">
-        <v>0.1896254632669268</v>
+        <v>0.187461801738728</v>
       </c>
       <c r="U18">
-        <v>6.983750823041532E-06</v>
+        <v>6.778883609911766E-06</v>
       </c>
       <c r="V18">
-        <v>0.2738606075533238</v>
+        <v>0.27340985406627</v>
       </c>
       <c r="W18">
-        <v>1.013680136728262E-07</v>
+        <v>4.2170588116255E-08</v>
       </c>
     </row>
     <row r="19">
@@ -5665,37 +5665,37 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>2.323636537722984</v>
+        <v>2.323841333631361</v>
       </c>
       <c r="H19">
-        <v>2.348369878112605</v>
+        <v>2.344301323210374</v>
       </c>
       <c r="I19">
-        <v>0.02473334038962182</v>
+        <v>0.02045998957901286</v>
       </c>
       <c r="J19">
-        <v>0.05040292755246652</v>
+        <v>0.05067887741659673</v>
       </c>
       <c r="K19">
         <v>3</v>
       </c>
       <c r="L19">
-        <v>-0.1356712701752076</v>
+        <v>-0.1408228166113614</v>
       </c>
       <c r="M19">
-        <v>0.1851379509544513</v>
+        <v>0.1817427957693871</v>
       </c>
       <c r="N19">
-        <v>1.064423802435941</v>
+        <v>0.8804383192135141</v>
       </c>
       <c r="O19">
-        <v>0.6572819459222934</v>
+        <v>0.7134739315936419</v>
       </c>
       <c r="P19">
-        <v>1.998401444325282E-15</v>
+        <v>1.887379141862766E-15</v>
       </c>
       <c r="Q19">
-        <v>0.8301008524302518</v>
+        <v>0.8141304205449362</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -5706,16 +5706,16 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0.1734239219924387</v>
+        <v>0.1716612887716008</v>
       </c>
       <c r="U19">
-        <v>8.326511634792292E-06</v>
+        <v>7.221291587487033E-06</v>
       </c>
       <c r="V19">
-        <v>0.2760682019643222</v>
+        <v>0.2775796420921162</v>
       </c>
       <c r="W19">
-        <v>4.808843242668202E-09</v>
+        <v>2.105436109862942E-09</v>
       </c>
     </row>
     <row r="20">
@@ -5748,37 +5748,37 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>2.323636537722988</v>
+        <v>2.323841333631361</v>
       </c>
       <c r="H20">
-        <v>2.442352776688102</v>
+        <v>2.442359499375551</v>
       </c>
       <c r="I20">
-        <v>0.118716238965114</v>
+        <v>0.1185181657441905</v>
       </c>
       <c r="J20">
-        <v>0.04853910606533006</v>
+        <v>0.04853546795493098</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20">
-        <v>-0.03575685979426968</v>
+        <v>-0.03594335492419543</v>
       </c>
       <c r="M20">
-        <v>0.2731893377244977</v>
+        <v>0.2729796864125764</v>
       </c>
       <c r="N20">
-        <v>5.109070934193872</v>
+        <v>5.100097155040596</v>
       </c>
       <c r="O20">
-        <v>0.09202428553228659</v>
+        <v>0.09234460705520453</v>
       </c>
       <c r="P20">
         <v>1.332267629550188E-15</v>
       </c>
       <c r="Q20">
-        <v>0.2648323013414869</v>
+        <v>0.2653250806389098</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -5789,16 +5789,16 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>0.1692602372384586</v>
+        <v>0.1693506541226867</v>
       </c>
       <c r="U20">
-        <v>6.972762850649347E-06</v>
+        <v>6.980029658353662E-06</v>
       </c>
       <c r="V20">
-        <v>0.2643486340900547</v>
+        <v>0.2643288162265744</v>
       </c>
       <c r="W20">
-        <v>1.339370581077944E-12</v>
+        <v>1.361207953437027E-12</v>
       </c>
     </row>
     <row r="21">
@@ -5831,37 +5831,37 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>2.323636537722989</v>
+        <v>2.323841333631369</v>
       </c>
       <c r="H21">
-        <v>2.474549123644997</v>
+        <v>2.473563828517284</v>
       </c>
       <c r="I21">
-        <v>0.150912585922009</v>
+        <v>0.149722494885915</v>
       </c>
       <c r="J21">
-        <v>0.04951686484787725</v>
+        <v>0.04950360662425006</v>
       </c>
       <c r="K21">
         <v>3</v>
       </c>
       <c r="L21">
-        <v>-0.006672177662350676</v>
+        <v>-0.007820075113647657</v>
       </c>
       <c r="M21">
-        <v>0.3084973495063686</v>
+        <v>0.3072650648854777</v>
       </c>
       <c r="N21">
-        <v>6.494672616479572</v>
+        <v>6.442888019895488</v>
       </c>
       <c r="O21">
-        <v>0.05552863374485917</v>
+        <v>0.05655796804226987</v>
       </c>
       <c r="P21">
-        <v>1.110223024625157E-14</v>
+        <v>1.265654248072678E-14</v>
       </c>
       <c r="Q21">
-        <v>0.254146496835586</v>
+        <v>0.2489194808068158</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -5872,16 +5872,16 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>0.1636676990688068</v>
+        <v>0.1633192644482944</v>
       </c>
       <c r="U21">
-        <v>6.803253732255091E-06</v>
+        <v>6.84661898534196E-06</v>
       </c>
       <c r="V21">
-        <v>0.2696740120302848</v>
+        <v>0.2696018212634279</v>
       </c>
       <c r="W21">
-        <v>4.883386411699965E-09</v>
+        <v>5.402354966337749E-09</v>
       </c>
     </row>
     <row r="22">
@@ -5914,37 +5914,37 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>5.715657023779298</v>
+        <v>5.714628726423102</v>
       </c>
       <c r="H22">
-        <v>4.475082483533146</v>
+        <v>4.475082483533145</v>
       </c>
       <c r="I22">
-        <v>-1.240574540246152</v>
+        <v>-1.239546242889958</v>
       </c>
       <c r="J22">
-        <v>0.4190589449014201</v>
+        <v>0.4190091310484613</v>
       </c>
       <c r="K22">
         <v>3</v>
       </c>
       <c r="L22">
-        <v>-2.574207131143766</v>
+        <v>-2.573020303875271</v>
       </c>
       <c r="M22">
-        <v>0.09305805065146089</v>
+        <v>0.09392781809535444</v>
       </c>
       <c r="N22">
-        <v>-21.70484574362829</v>
+        <v>-21.69075721680023</v>
       </c>
       <c r="O22">
-        <v>0.05952571919031668</v>
+        <v>0.05962632431722903</v>
       </c>
       <c r="P22">
-        <v>6.985755918820225E-05</v>
+        <v>6.948207311063825E-05</v>
       </c>
       <c r="Q22">
-        <v>0.5685524937685535</v>
+        <v>0.5685831163907287</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -5955,16 +5955,16 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>0.5086165070319885</v>
+        <v>0.5080557323737145</v>
       </c>
       <c r="U22">
-        <v>0.0001458748969931011</v>
+        <v>0.0001480239008428772</v>
       </c>
       <c r="V22">
-        <v>2.295280300935914</v>
+        <v>2.295007457154217</v>
       </c>
       <c r="W22">
-        <v>7.268969538949591E-08</v>
+        <v>5.153485132386175E-08</v>
       </c>
     </row>
     <row r="23">
@@ -5997,37 +5997,37 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>5.716450412948245</v>
+        <v>5.715409560583304</v>
       </c>
       <c r="H23">
-        <v>6.281438179490992</v>
+        <v>6.281598457486055</v>
       </c>
       <c r="I23">
-        <v>0.5649877665427475</v>
+        <v>0.5661888969027509</v>
       </c>
       <c r="J23">
-        <v>0.7135712486718941</v>
+        <v>0.7134402788291146</v>
       </c>
       <c r="K23">
         <v>3</v>
       </c>
       <c r="L23">
-        <v>-1.705914417349804</v>
+        <v>-1.704296482497543</v>
       </c>
       <c r="M23">
-        <v>2.835889950435299</v>
+        <v>2.836674276303045</v>
       </c>
       <c r="N23">
-        <v>9.883541808794533</v>
+        <v>9.906357381761575</v>
       </c>
       <c r="O23">
-        <v>0.4863208835977372</v>
+        <v>0.4854017722898045</v>
       </c>
       <c r="P23">
-        <v>0.002785151782864093</v>
+        <v>0.002782760964731845</v>
       </c>
       <c r="Q23">
-        <v>0.9463393348786391</v>
+        <v>0.9463818144290322</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -6038,16 +6038,16 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>0.0001678020502344692</v>
+        <v>0.0001695544713796431</v>
       </c>
       <c r="U23">
-        <v>0.0002169289287681086</v>
+        <v>0.0002146421248987938</v>
       </c>
       <c r="V23">
-        <v>3.502826415310855</v>
+        <v>3.50260145624439</v>
       </c>
       <c r="W23">
-        <v>0.5488864132246087</v>
+        <v>0.5487132442849563</v>
       </c>
     </row>
     <row r="24">
@@ -6080,37 +6080,37 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>6.281363940122243</v>
+        <v>6.281523829079963</v>
       </c>
       <c r="H24">
-        <v>6.182479792008519</v>
+        <v>6.179770908579557</v>
       </c>
       <c r="I24">
-        <v>-0.09888414811372354</v>
+        <v>-0.1017529205004058</v>
       </c>
       <c r="J24">
-        <v>0.757178851294994</v>
+        <v>0.7568737912160602</v>
       </c>
       <c r="K24">
         <v>3</v>
       </c>
       <c r="L24">
-        <v>-2.508565185856439</v>
+        <v>-2.510463120922029</v>
       </c>
       <c r="M24">
-        <v>2.310796889628992</v>
+        <v>2.306957279921217</v>
       </c>
       <c r="N24">
-        <v>-1.574246438454243</v>
+        <v>-1.619876375050054</v>
       </c>
       <c r="O24">
-        <v>0.9043605698369798</v>
+        <v>0.901568399431441</v>
       </c>
       <c r="P24">
-        <v>0.07292238618551405</v>
+        <v>0.0723799184639593</v>
       </c>
       <c r="Q24">
-        <v>0.8311648906587366</v>
+        <v>0.8313800782433334</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -6121,16 +6121,16 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>0.9058948050375422</v>
+        <v>0.9070257915004885</v>
       </c>
       <c r="U24">
-        <v>0.0002319083323328616</v>
+        <v>0.0002207785842929135</v>
       </c>
       <c r="V24">
-        <v>4.000145887397047</v>
+        <v>4.000250576574317</v>
       </c>
       <c r="W24">
-        <v>0.3961713666530482</v>
+        <v>0.3947528568870304</v>
       </c>
     </row>
     <row r="25">
@@ -6163,37 +6163,37 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>6.281298995275222</v>
+        <v>6.281459153583775</v>
       </c>
       <c r="H25">
-        <v>6.918865152854911</v>
+        <v>6.918865155357377</v>
       </c>
       <c r="I25">
-        <v>0.6375661575796896</v>
+        <v>0.6374060017736022</v>
       </c>
       <c r="J25">
-        <v>1.054782388144537</v>
+        <v>1.054787010545946</v>
       </c>
       <c r="K25">
         <v>3</v>
       </c>
       <c r="L25">
-        <v>-2.719222156449216</v>
+        <v>-2.719397022799591</v>
       </c>
       <c r="M25">
-        <v>3.994354471608596</v>
+        <v>3.994209026346795</v>
       </c>
       <c r="N25">
-        <v>10.15022781210169</v>
+        <v>10.14741935255508</v>
       </c>
       <c r="O25">
-        <v>0.5881959312493291</v>
+        <v>0.5882861800337852</v>
       </c>
       <c r="P25">
-        <v>0.2053806799595039</v>
+        <v>0.2054218088026871</v>
       </c>
       <c r="Q25">
-        <v>0.5118438171490337</v>
+        <v>0.5118463177016355</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -6204,16 +6204,16 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>0.000218380394267238</v>
+        <v>0.0002180032154628903</v>
       </c>
       <c r="U25">
-        <v>0.0001280531088997812</v>
+        <v>0.0001277073442751021</v>
       </c>
       <c r="V25">
-        <v>5.628494834646911</v>
+        <v>5.628504314144367</v>
       </c>
       <c r="W25">
-        <v>0.3356135815467887</v>
+        <v>0.3356270181323229</v>
       </c>
     </row>
     <row r="26">
@@ -6246,37 +6246,37 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>6.281496054994521</v>
+        <v>6.281656063622581</v>
       </c>
       <c r="H26">
-        <v>6.384748469060736</v>
+        <v>6.364855050671586</v>
       </c>
       <c r="I26">
-        <v>0.1032524140662161</v>
+        <v>0.083198987049005</v>
       </c>
       <c r="J26">
-        <v>0.7650510016899337</v>
+        <v>0.7655955220405191</v>
       </c>
       <c r="K26">
         <v>3</v>
       </c>
       <c r="L26">
-        <v>-2.331481319615513</v>
+        <v>-2.353267653410596</v>
       </c>
       <c r="M26">
-        <v>2.537986147747945</v>
+        <v>2.519665627508606</v>
       </c>
       <c r="N26">
-        <v>1.643755136710122</v>
+        <v>1.324475364558957</v>
       </c>
       <c r="O26">
-        <v>0.90118850947977</v>
+        <v>0.9203233745559203</v>
       </c>
       <c r="P26">
-        <v>0.03660609310719154</v>
+        <v>0.03501561965449085</v>
       </c>
       <c r="Q26">
-        <v>0.3970272446204093</v>
+        <v>0.39851281150133</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -6287,22 +6287,22 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>8.306195834474859E-17</v>
+        <v>4.47419419344024E-10</v>
       </c>
       <c r="U26">
-        <v>1.568397145701247E-16</v>
+        <v>6.476909170441963E-10</v>
       </c>
       <c r="V26">
-        <v>4.167269341827359</v>
+        <v>4.170235375962111</v>
       </c>
       <c r="W26">
-        <v>0.002718898046545157</v>
+        <v>0.002531927721162116</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6329,37 +6329,37 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>0.3181513304352998</v>
+        <v>0.3180416700753945</v>
       </c>
       <c r="H27">
-        <v>0.3184091075185365</v>
+        <v>0.3184091075185366</v>
       </c>
       <c r="I27">
-        <v>0.0002577770832367278</v>
+        <v>0.0003674374431422021</v>
       </c>
       <c r="J27">
-        <v>0.0009234375697761263</v>
+        <v>0.0009190599911582044</v>
       </c>
       <c r="K27">
         <v>3</v>
       </c>
       <c r="L27">
-        <v>-0.002681013398857472</v>
+        <v>-0.002557421630053303</v>
       </c>
       <c r="M27">
-        <v>0.003196567565330927</v>
+        <v>0.003292296516337707</v>
       </c>
       <c r="N27">
-        <v>0.08102341828463613</v>
+        <v>0.1155312267902184</v>
       </c>
       <c r="O27">
-        <v>0.7982681553501167</v>
+        <v>0.7160696468483081</v>
       </c>
       <c r="P27">
-        <v>0.109429041781189</v>
+        <v>0.1221904419457923</v>
       </c>
       <c r="Q27">
-        <v>0.9866556012932424</v>
+        <v>0.9729458591714493</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -6370,22 +6370,22 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>0.001580600482743718</v>
+        <v>0.001612405214475325</v>
       </c>
       <c r="U27">
-        <v>1.844365809805105E-07</v>
+        <v>1.929353930846077E-07</v>
       </c>
       <c r="V27">
-        <v>0.005029302278480572</v>
+        <v>0.005033898833118374</v>
       </c>
       <c r="W27">
-        <v>9.378194156565162E-19</v>
+        <v>8.227526080415387E-13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6412,37 +6412,37 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>0.3181408563298728</v>
+        <v>0.318041674857422</v>
       </c>
       <c r="H28">
-        <v>0.3171571133163644</v>
+        <v>0.3171572569945293</v>
       </c>
       <c r="I28">
-        <v>-0.0009837430135084845</v>
+        <v>-0.0008844178628927238</v>
       </c>
       <c r="J28">
-        <v>0.0009001841951286106</v>
+        <v>0.0008465600529237408</v>
       </c>
       <c r="K28">
         <v>3</v>
       </c>
       <c r="L28">
-        <v>-0.00384853087937032</v>
+        <v>-0.003578549775520663</v>
       </c>
       <c r="M28">
-        <v>0.001881044852353351</v>
+        <v>0.001809714049735215</v>
       </c>
       <c r="N28">
-        <v>-0.3092161833148724</v>
+        <v>-0.2780823812757268</v>
       </c>
       <c r="O28">
-        <v>0.3543718195693368</v>
+        <v>0.3729211039065696</v>
       </c>
       <c r="P28">
-        <v>0.4971386725833122</v>
+        <v>0.4705681248342058</v>
       </c>
       <c r="Q28">
-        <v>0.1106425824672489</v>
+        <v>0.1162282288077902</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -6453,22 +6453,22 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>0.001278537278212777</v>
+        <v>0.00139196171825139</v>
       </c>
       <c r="U28">
-        <v>0.0005359748981150795</v>
+        <v>0.0003733734986791763</v>
       </c>
       <c r="V28">
-        <v>0.00439918125654726</v>
+        <v>0.004404917588617385</v>
       </c>
       <c r="W28">
-        <v>0.2756842871582819</v>
+        <v>0.07019506549937686</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6495,37 +6495,37 @@
         <v>1</v>
       </c>
       <c r="G29">
-        <v>0.317156376642493</v>
+        <v>0.3171563709957552</v>
       </c>
       <c r="H29">
-        <v>0.3175283304419296</v>
+        <v>0.3175975398139458</v>
       </c>
       <c r="I29">
-        <v>0.0003719537994366687</v>
+        <v>0.0004411688181906017</v>
       </c>
       <c r="J29">
-        <v>0.0009065685397172795</v>
+        <v>0.0009078548223808769</v>
       </c>
       <c r="K29">
         <v>3</v>
       </c>
       <c r="L29">
-        <v>-0.002513151900273034</v>
+        <v>-0.002448030407029417</v>
       </c>
       <c r="M29">
-        <v>0.003257059499146371</v>
+        <v>0.00333036804341062</v>
       </c>
       <c r="N29">
-        <v>0.1172777301135411</v>
+        <v>0.1391013577326203</v>
       </c>
       <c r="O29">
-        <v>0.7091369972620301</v>
+        <v>0.6602884480698676</v>
       </c>
       <c r="P29">
-        <v>0.2613794034399521</v>
+        <v>0.3171381949925645</v>
       </c>
       <c r="Q29">
-        <v>0.01385623970414773</v>
+        <v>0.01627724657325258</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -6536,22 +6536,22 @@
         <v>0</v>
       </c>
       <c r="T29">
-        <v>0.0004517039795848431</v>
+        <v>0.0003248162061871725</v>
       </c>
       <c r="U29">
-        <v>2.45098018648587E-07</v>
+        <v>3.574645199951249E-07</v>
       </c>
       <c r="V29">
-        <v>0.004010536095739664</v>
+        <v>0.004020382856871123</v>
       </c>
       <c r="W29">
-        <v>0.6595978327165216</v>
+        <v>0.6586976899149259</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6634,7 +6634,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6661,37 +6661,37 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>0.3171564401370906</v>
+        <v>0.317156327464711</v>
       </c>
       <c r="H31">
-        <v>0.3168147616816879</v>
+        <v>0.3168120282081159</v>
       </c>
       <c r="I31">
-        <v>-0.0003416784554026475</v>
+        <v>-0.0003442992565950189</v>
       </c>
       <c r="J31">
-        <v>0.0009125620731659855</v>
+        <v>0.0009584729570124726</v>
       </c>
       <c r="K31">
         <v>3</v>
       </c>
       <c r="L31">
-        <v>-0.003245858253491779</v>
+        <v>-0.003394587977353712</v>
       </c>
       <c r="M31">
-        <v>0.002562501342686484</v>
+        <v>0.002705989464163674</v>
       </c>
       <c r="N31">
-        <v>-0.1077318358268107</v>
+        <v>-0.1085582177556675</v>
       </c>
       <c r="O31">
-        <v>0.7329934791869043</v>
+        <v>0.7432284421311537</v>
       </c>
       <c r="P31">
-        <v>0.01119289628672138</v>
+        <v>0.01756197676047799</v>
       </c>
       <c r="Q31">
-        <v>0.7744304315875609</v>
+        <v>0.4173734537772777</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -6702,22 +6702,22 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>0.0003813839506608239</v>
+        <v>3.787592890432427E-07</v>
       </c>
       <c r="U31">
-        <v>3.037262782511067E-07</v>
+        <v>5.943858999666583E-08</v>
       </c>
       <c r="V31">
-        <v>0.004152731679652062</v>
+        <v>0.004169870523958194</v>
       </c>
       <c r="W31">
-        <v>0.6247842947165358</v>
+        <v>0.6736659931259201</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6744,37 +6744,37 @@
         <v>1</v>
       </c>
       <c r="G32">
-        <v>439.0329017272575</v>
+        <v>438.8724215098236</v>
       </c>
       <c r="H32">
-        <v>428.5560578434248</v>
+        <v>428.5560329973286</v>
       </c>
       <c r="I32">
-        <v>-10.47684388383265</v>
+        <v>-10.31638851249501</v>
       </c>
       <c r="J32">
-        <v>9.123058139915456</v>
+        <v>9.123243836312687</v>
       </c>
       <c r="K32">
         <v>3</v>
       </c>
       <c r="L32">
-        <v>-39.51048655409504</v>
+        <v>-39.35062215157068</v>
       </c>
       <c r="M32">
-        <v>18.55679878642975</v>
+        <v>18.71784512658066</v>
       </c>
       <c r="N32">
-        <v>-2.38634595325642</v>
+        <v>-2.350657732605804</v>
       </c>
       <c r="O32">
-        <v>0.3340716888700744</v>
+        <v>0.3403770868833369</v>
       </c>
       <c r="P32">
-        <v>4.730516418360864E-05</v>
+        <v>4.009492768775047E-05</v>
       </c>
       <c r="Q32">
-        <v>0.9972508176715205</v>
+        <v>0.997199951980236</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -6785,22 +6785,22 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>24.43059746433977</v>
+        <v>24.57655087378663</v>
       </c>
       <c r="U32">
-        <v>0.002285345364736415</v>
+        <v>0.002651980686652503</v>
       </c>
       <c r="V32">
-        <v>35.00623374873532</v>
+        <v>34.89138969031175</v>
       </c>
       <c r="W32">
-        <v>0.7577387413989322</v>
+        <v>0.7606620048666444</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6827,37 +6827,37 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>439.115161743403</v>
+        <v>438.8712951327661</v>
       </c>
       <c r="H33">
-        <v>419.9439712850209</v>
+        <v>419.9440471554524</v>
       </c>
       <c r="I33">
-        <v>-19.17119045838206</v>
+        <v>-18.92724797731363</v>
       </c>
       <c r="J33">
-        <v>11.75991033732979</v>
+        <v>11.79305323900245</v>
       </c>
       <c r="K33">
         <v>3</v>
       </c>
       <c r="L33">
-        <v>-56.59647366188492</v>
+        <v>-56.45800668579103</v>
       </c>
       <c r="M33">
-        <v>18.25409274512079</v>
+        <v>18.60351073116378</v>
       </c>
       <c r="N33">
-        <v>-4.365868484765451</v>
+        <v>-4.312710397609352</v>
       </c>
       <c r="O33">
-        <v>0.2015493919116456</v>
+        <v>0.2068486374336809</v>
       </c>
       <c r="P33">
-        <v>6.311311273599074E-08</v>
+        <v>5.48893883678403E-08</v>
       </c>
       <c r="Q33">
-        <v>0.4793425431134143</v>
+        <v>0.4045125851636293</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -6868,22 +6868,22 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>17.91034988214612</v>
+        <v>18.1363103556512</v>
       </c>
       <c r="U33">
-        <v>0.006811502086809066</v>
+        <v>0.009148717207512322</v>
       </c>
       <c r="V33">
-        <v>35.50589093718587</v>
+        <v>35.45984905126075</v>
       </c>
       <c r="W33">
-        <v>0.8588515702815531</v>
+        <v>0.8604312999943511</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6910,37 +6910,37 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>419.94342358187</v>
+        <v>419.9435926044553</v>
       </c>
       <c r="H34">
-        <v>414.5899778585058</v>
+        <v>414.4258175877889</v>
       </c>
       <c r="I34">
-        <v>-5.353445723364242</v>
+        <v>-5.517775016666352</v>
       </c>
       <c r="J34">
-        <v>4.113291699492963</v>
+        <v>4.05329467553928</v>
       </c>
       <c r="K34">
         <v>3</v>
       </c>
       <c r="L34">
-        <v>-18.44377569496977</v>
+        <v>-18.41716768106246</v>
       </c>
       <c r="M34">
-        <v>7.736884248241282</v>
+        <v>7.381617647729755</v>
       </c>
       <c r="N34">
-        <v>-1.274801657257186</v>
+        <v>-1.313932421839221</v>
       </c>
       <c r="O34">
-        <v>0.2840169663976808</v>
+        <v>0.2666431786646385</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0.9974110775454158</v>
+        <v>0.9966983271179078</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -6951,22 +6951,22 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>7.778182024092115</v>
+        <v>7.959016249065644</v>
       </c>
       <c r="U34">
-        <v>0.001020110285450408</v>
+        <v>0.001152958323936794</v>
       </c>
       <c r="V34">
-        <v>21.61573390045852</v>
+        <v>21.43659826195661</v>
       </c>
       <c r="W34">
-        <v>0.3963314477939908</v>
+        <v>0.3736753739949171</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7049,7 +7049,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7076,37 +7076,37 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>419.9430405774364</v>
+        <v>419.9430942541685</v>
       </c>
       <c r="H36">
-        <v>409.0229283264894</v>
+        <v>407.3324254838149</v>
       </c>
       <c r="I36">
-        <v>-10.92011225094705</v>
+        <v>-12.61066877035361</v>
       </c>
       <c r="J36">
-        <v>4.116628767413799</v>
+        <v>4.085776723817942</v>
       </c>
       <c r="K36">
         <v>3</v>
       </c>
       <c r="L36">
-        <v>-24.02106226202772</v>
+        <v>-25.61343380928219</v>
       </c>
       <c r="M36">
-        <v>2.180837760133613</v>
+        <v>0.3920962685749654</v>
       </c>
       <c r="N36">
-        <v>-2.600379383816319</v>
+        <v>-3.002947052326349</v>
       </c>
       <c r="O36">
-        <v>0.07681735295222714</v>
+        <v>0.0538618176670641</v>
       </c>
       <c r="P36">
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0.7870335122044502</v>
+        <v>0.8683615664809332</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -7117,22 +7117,22 @@
         <v>0</v>
       </c>
       <c r="T36">
-        <v>8.37839930800795</v>
+        <v>7.73500645102264</v>
       </c>
       <c r="U36">
-        <v>0.004288166877257681</v>
+        <v>0.007122512691949018</v>
       </c>
       <c r="V36">
-        <v>21.22038576521224</v>
+        <v>21.39256052801779</v>
       </c>
       <c r="W36">
-        <v>0.4227210318186112</v>
+        <v>0.4080084069177977</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7159,37 +7159,37 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>1.977043737016501</v>
+        <v>1.976952970187362</v>
       </c>
       <c r="H37">
-        <v>1.965222678620959</v>
+        <v>1.965222673773879</v>
       </c>
       <c r="I37">
-        <v>-0.01182105839554173</v>
+        <v>-0.01173029641348285</v>
       </c>
       <c r="J37">
-        <v>0.009942222282816902</v>
+        <v>0.009828554440288588</v>
       </c>
       <c r="K37">
         <v>3</v>
       </c>
       <c r="L37">
-        <v>-0.04346164696580174</v>
+        <v>-0.04300914317825905</v>
       </c>
       <c r="M37">
-        <v>0.01981953017471827</v>
+        <v>0.01954855035129335</v>
       </c>
       <c r="N37">
-        <v>-0.5979158768323733</v>
+        <v>-0.5933523250363986</v>
       </c>
       <c r="O37">
-        <v>0.3199840945275008</v>
+        <v>0.3184540776294043</v>
       </c>
       <c r="P37">
-        <v>0.1252499278888124</v>
+        <v>0.116132066454858</v>
       </c>
       <c r="Q37">
-        <v>0.5775376647891546</v>
+        <v>0.5643314792529246</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -7200,22 +7200,22 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>0.0149953669447823</v>
+        <v>0.0150902542936057</v>
       </c>
       <c r="U37">
-        <v>1.115838238703062E-06</v>
+        <v>1.112445033437617E-06</v>
       </c>
       <c r="V37">
-        <v>0.05394245505414247</v>
+        <v>0.05362879421383584</v>
       </c>
       <c r="W37">
-        <v>0.2001463102524095</v>
+        <v>0.1992937962228762</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7242,37 +7242,37 @@
         <v>1</v>
       </c>
       <c r="G38">
-        <v>1.977019663765039</v>
+        <v>1.976952079631702</v>
       </c>
       <c r="H38">
-        <v>1.959981697463381</v>
+        <v>1.959981687279842</v>
       </c>
       <c r="I38">
-        <v>-0.01703796630165793</v>
+        <v>-0.01697039235186026</v>
       </c>
       <c r="J38">
-        <v>0.01022666571774809</v>
+        <v>0.01010992627874066</v>
       </c>
       <c r="K38">
         <v>3</v>
       </c>
       <c r="L38">
-        <v>-0.04958378083047689</v>
+        <v>-0.04914468988432914</v>
       </c>
       <c r="M38">
-        <v>0.01550784822716102</v>
+        <v>0.01520390518060861</v>
       </c>
       <c r="N38">
-        <v>-0.8618005482662123</v>
+        <v>-0.8584119224084468</v>
       </c>
       <c r="O38">
-        <v>0.1942969021797325</v>
+        <v>0.1918250610876104</v>
       </c>
       <c r="P38">
-        <v>0.009728293408042821</v>
+        <v>0.008510582109255926</v>
       </c>
       <c r="Q38">
-        <v>0.9964476621430448</v>
+        <v>0.9962008182189269</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -7283,22 +7283,22 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>0.01484901343583858</v>
+        <v>0.0149266643064968</v>
       </c>
       <c r="U38">
-        <v>5.739714527853905E-07</v>
+        <v>5.441362623185625E-07</v>
       </c>
       <c r="V38">
-        <v>0.05559480354971349</v>
+        <v>0.055272257790528</v>
       </c>
       <c r="W38">
-        <v>0.1596868132628043</v>
+        <v>0.1588960812162411</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7325,37 +7325,37 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>1.95999115844225</v>
+        <v>1.959991086730867</v>
       </c>
       <c r="H39">
-        <v>1.955058475168531</v>
+        <v>1.954967124087597</v>
       </c>
       <c r="I39">
-        <v>-0.00493268327371874</v>
+        <v>-0.00502396264327041</v>
       </c>
       <c r="J39">
-        <v>0.005301339563588784</v>
+        <v>0.00528305562889516</v>
       </c>
       <c r="K39">
         <v>3</v>
       </c>
       <c r="L39">
-        <v>-0.02180391178091621</v>
+        <v>-0.02183700351005611</v>
       </c>
       <c r="M39">
-        <v>0.01193854523347873</v>
+        <v>0.01178907822351529</v>
       </c>
       <c r="N39">
-        <v>-0.2516686492422297</v>
+        <v>-0.256325790320304</v>
       </c>
       <c r="O39">
-        <v>0.4207676176129129</v>
+        <v>0.411782198458145</v>
       </c>
       <c r="P39">
-        <v>9.873009627625606E-07</v>
+        <v>9.875213639043423E-07</v>
       </c>
       <c r="Q39">
-        <v>0.9990343225677822</v>
+        <v>0.999078546750874</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -7366,22 +7366,22 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>0.01402988140497981</v>
+        <v>0.0141069139258711</v>
       </c>
       <c r="U39">
-        <v>6.862976090898095E-07</v>
+        <v>7.200292256803853E-07</v>
       </c>
       <c r="V39">
-        <v>0.02655662820687501</v>
+        <v>0.0265082732134378</v>
       </c>
       <c r="W39">
-        <v>0.5093242875719801</v>
+        <v>0.5064058288802785</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7491,37 +7491,37 @@
         <v>1</v>
       </c>
       <c r="G41">
-        <v>1.959991412684328</v>
+        <v>1.959991218367615</v>
       </c>
       <c r="H41">
-        <v>1.94738561641093</v>
+        <v>1.946571185492213</v>
       </c>
       <c r="I41">
-        <v>-0.01260579627339727</v>
+        <v>-0.01342003287540265</v>
       </c>
       <c r="J41">
-        <v>0.005237593259176438</v>
+        <v>0.005019439841941558</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41">
-        <v>-0.02927415558964218</v>
+        <v>-0.02939413065498341</v>
       </c>
       <c r="M41">
-        <v>0.004062563042847633</v>
+        <v>0.002554064904178097</v>
       </c>
       <c r="N41">
-        <v>-0.6431556889391095</v>
+        <v>-0.6846986226080936</v>
       </c>
       <c r="O41">
-        <v>0.0952911029045802</v>
+        <v>0.0754579352146586</v>
       </c>
       <c r="P41">
-        <v>4.497545797899072E-06</v>
+        <v>3.96235085831087E-06</v>
       </c>
       <c r="Q41">
-        <v>0.9120278248754501</v>
+        <v>0.9097796690258328</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -7532,22 +7532,22 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>0.01391438320699816</v>
+        <v>0.01335450023595839</v>
       </c>
       <c r="U41">
-        <v>7.61447726230038E-07</v>
+        <v>8.092334852749641E-07</v>
       </c>
       <c r="V41">
-        <v>0.02582687929729691</v>
+        <v>0.02508857129025711</v>
       </c>
       <c r="W41">
-        <v>0.5191647402302482</v>
+        <v>0.5131933758374673</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7574,37 +7574,37 @@
         <v>1</v>
       </c>
       <c r="G42">
-        <v>2.328550850518403</v>
+        <v>2.332214657937738</v>
       </c>
       <c r="H42">
-        <v>2.375560612447569</v>
+        <v>2.375561307067098</v>
       </c>
       <c r="I42">
-        <v>0.04700976192916646</v>
+        <v>0.04334664912936008</v>
       </c>
       <c r="J42">
-        <v>0.0596624792537978</v>
+        <v>0.05941354848771144</v>
       </c>
       <c r="K42">
         <v>3</v>
       </c>
       <c r="L42">
-        <v>-0.1428628747361482</v>
+        <v>-0.1457337787391516</v>
       </c>
       <c r="M42">
-        <v>0.2368823985944811</v>
+        <v>0.2324270769978718</v>
       </c>
       <c r="N42">
-        <v>2.018841972839061</v>
+        <v>1.858604609221064</v>
       </c>
       <c r="O42">
-        <v>0.4882586768498665</v>
+        <v>0.5184534277647421</v>
       </c>
       <c r="P42">
-        <v>1.110223024625157E-15</v>
+        <v>4.440892098500626E-16</v>
       </c>
       <c r="Q42">
-        <v>0.5961392227840887</v>
+        <v>0.5949432329953592</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -7615,22 +7615,22 @@
         <v>0</v>
       </c>
       <c r="T42">
-        <v>0.2559390733301036</v>
+        <v>0.2578148746114322</v>
       </c>
       <c r="U42">
-        <v>9.161359325757038E-06</v>
+        <v>8.776472445915248E-06</v>
       </c>
       <c r="V42">
-        <v>0.274682171183108</v>
+        <v>0.2739717262685583</v>
       </c>
       <c r="W42">
-        <v>0.6217993212638278</v>
+        <v>0.6239797284971604</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7657,37 +7657,37 @@
         <v>1</v>
       </c>
       <c r="G43">
-        <v>2.327663122467758</v>
+        <v>2.332160229988872</v>
       </c>
       <c r="H43">
-        <v>2.538140299683232</v>
+        <v>2.538140299683225</v>
       </c>
       <c r="I43">
-        <v>0.2104771772154732</v>
+        <v>0.2059800696943536</v>
       </c>
       <c r="J43">
-        <v>0.04544284397700372</v>
+        <v>0.04512867445944082</v>
       </c>
       <c r="K43">
         <v>3</v>
       </c>
       <c r="L43">
-        <v>0.0658577662992737</v>
+        <v>0.06236048639855499</v>
       </c>
       <c r="M43">
-        <v>0.3550965881316727</v>
+        <v>0.3495996529901523</v>
       </c>
       <c r="N43">
-        <v>9.042424360460204</v>
+        <v>8.832157715653032</v>
       </c>
       <c r="O43">
-        <v>0.01895754807928951</v>
+        <v>0.01972283558073018</v>
       </c>
       <c r="P43">
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>0.4128154230396275</v>
+        <v>0.445115907946472</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -7698,22 +7698,22 @@
         <v>1</v>
       </c>
       <c r="T43">
-        <v>0.2082215536537118</v>
+        <v>0.2110216955223678</v>
       </c>
       <c r="U43">
-        <v>1.061050320862189E-05</v>
+        <v>1.400133178037675E-05</v>
       </c>
       <c r="V43">
-        <v>0.2474846319081728</v>
+        <v>0.2471799239692135</v>
       </c>
       <c r="W43">
-        <v>1.762666022693574E-07</v>
+        <v>1.881196650408328E-08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7740,37 +7740,37 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>2.538140299683223</v>
+        <v>2.538140299683222</v>
       </c>
       <c r="H44">
-        <v>2.586284951871228</v>
+        <v>2.590051534073125</v>
       </c>
       <c r="I44">
-        <v>0.04814465218800511</v>
+        <v>0.05191123438990367</v>
       </c>
       <c r="J44">
-        <v>0.0432679738392537</v>
+        <v>0.04251620123140761</v>
       </c>
       <c r="K44">
         <v>3</v>
       </c>
       <c r="L44">
-        <v>-0.08955335129383994</v>
+        <v>-0.08339429313368812</v>
       </c>
       <c r="M44">
-        <v>0.1858426556698501</v>
+        <v>0.1872167619134955</v>
       </c>
       <c r="N44">
-        <v>1.896847553857203</v>
+        <v>2.045246844564998</v>
       </c>
       <c r="O44">
-        <v>0.3469707721734031</v>
+        <v>0.3093020865654894</v>
       </c>
       <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0.7680312217998135</v>
+        <v>0.7421500050895999</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -7781,22 +7781,22 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>0.1515341484457677</v>
+        <v>0.1537751797164001</v>
       </c>
       <c r="U44">
-        <v>1.078007767749796E-05</v>
+        <v>9.170517146857178E-06</v>
       </c>
       <c r="V44">
-        <v>0.2356415116586208</v>
+        <v>0.2315470919371417</v>
       </c>
       <c r="W44">
-        <v>7.488341161604567E-35</v>
+        <v>9.823872745518807E-22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7879,7 +7879,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7906,37 +7906,37 @@
         <v>1</v>
       </c>
       <c r="G46">
-        <v>2.538140299683226</v>
+        <v>2.538140299683231</v>
       </c>
       <c r="H46">
-        <v>2.697934368694944</v>
+        <v>2.712621292854394</v>
       </c>
       <c r="I46">
-        <v>0.1597940690117191</v>
+        <v>0.1744809931711638</v>
       </c>
       <c r="J46">
-        <v>0.0451580180870263</v>
+        <v>0.04550951491936461</v>
       </c>
       <c r="K46">
         <v>3</v>
       </c>
       <c r="L46">
-        <v>0.0160811011967274</v>
+        <v>0.02964940556077814</v>
       </c>
       <c r="M46">
-        <v>0.3035070368267108</v>
+        <v>0.3193125807815496</v>
       </c>
       <c r="N46">
-        <v>6.295714584085927</v>
+        <v>6.874363611536357</v>
       </c>
       <c r="O46">
-        <v>0.03840340273508602</v>
+        <v>0.03127700490537189</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0.3531781092717563</v>
+        <v>0.3834856310619161</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -7947,22 +7947,22 @@
         <v>1</v>
       </c>
       <c r="T46">
-        <v>0.1537915797164838</v>
+        <v>0.1420397156406817</v>
       </c>
       <c r="U46">
-        <v>8.404980639363739E-06</v>
+        <v>8.109095563724956E-06</v>
       </c>
       <c r="V46">
-        <v>0.2431636978242331</v>
+        <v>0.2478500073508794</v>
       </c>
       <c r="W46">
-        <v>6.962113799093861E-14</v>
+        <v>1.582268966891458E-11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7989,37 +7989,37 @@
         <v>1</v>
       </c>
       <c r="G47">
-        <v>6.848290622803901</v>
+        <v>6.866563139462621</v>
       </c>
       <c r="H47">
-        <v>5.441696710889643</v>
+        <v>5.441696710876834</v>
       </c>
       <c r="I47">
-        <v>-1.406593911914258</v>
+        <v>-1.424866428585787</v>
       </c>
       <c r="J47">
-        <v>0.9388554701954553</v>
+        <v>0.9280858196646317</v>
       </c>
       <c r="K47">
         <v>3</v>
       </c>
       <c r="L47">
-        <v>-4.394451034233184</v>
+        <v>-4.378449716363695</v>
       </c>
       <c r="M47">
-        <v>1.581263210404667</v>
+        <v>1.528716859192122</v>
       </c>
       <c r="N47">
-        <v>-20.53934316441663</v>
+        <v>-20.75079482480805</v>
       </c>
       <c r="O47">
-        <v>0.2310162061382826</v>
+        <v>0.2222853661014497</v>
       </c>
       <c r="P47">
-        <v>0.001147655820493254</v>
+        <v>0.0009892894211060987</v>
       </c>
       <c r="Q47">
-        <v>0.7522300431411013</v>
+        <v>0.747857720600035</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -8030,22 +8030,22 @@
         <v>0</v>
       </c>
       <c r="T47">
-        <v>0.0001696603883548957</v>
+        <v>6.363154069216534E-05</v>
       </c>
       <c r="U47">
-        <v>0.704392667787722</v>
+        <v>0.6949961230018965</v>
       </c>
       <c r="V47">
-        <v>4.334532267002111</v>
+        <v>4.312192512777159</v>
       </c>
       <c r="W47">
-        <v>0.001473445386142282</v>
+        <v>0.002603805146267635</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8072,37 +8072,37 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>6.852960485995165</v>
+        <v>6.866552638690923</v>
       </c>
       <c r="H48">
-        <v>6.591158548346657</v>
+        <v>6.591152817823406</v>
       </c>
       <c r="I48">
-        <v>-0.2618019376485092</v>
+        <v>-0.2753998208675161</v>
       </c>
       <c r="J48">
-        <v>0.8949743110770713</v>
+        <v>0.8877615553383974</v>
       </c>
       <c r="K48">
         <v>3</v>
       </c>
       <c r="L48">
-        <v>-3.110009627259566</v>
+        <v>-3.100653302627117</v>
       </c>
       <c r="M48">
-        <v>2.586405751962548</v>
+        <v>2.549853660892085</v>
       </c>
       <c r="N48">
-        <v>-3.820275021044297</v>
+        <v>-4.010743605397013</v>
       </c>
       <c r="O48">
-        <v>0.7889505672529816</v>
+        <v>0.7766971845925295</v>
       </c>
       <c r="P48">
-        <v>0.0104988466107595</v>
+        <v>0.00933479411172522</v>
       </c>
       <c r="Q48">
-        <v>0.9313837563421024</v>
+        <v>0.9295452980219808</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -8113,22 +8113,22 @@
         <v>0</v>
       </c>
       <c r="T48">
-        <v>0.5555110352850318</v>
+        <v>0.5443629130508342</v>
       </c>
       <c r="U48">
-        <v>0.0002226720112165021</v>
+        <v>0.0002482364095907002</v>
       </c>
       <c r="V48">
-        <v>4.691700290063939</v>
+        <v>4.66741956407447</v>
       </c>
       <c r="W48">
-        <v>0.4044534385610952</v>
+        <v>0.411313118566013</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8155,37 +8155,37 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>6.591660461972968</v>
+        <v>6.591514466481987</v>
       </c>
       <c r="H49">
-        <v>6.053370927566542</v>
+        <v>6.069143955707469</v>
       </c>
       <c r="I49">
-        <v>-0.5382895344064257</v>
+        <v>-0.522370510774518</v>
       </c>
       <c r="J49">
-        <v>0.6045762190477729</v>
+        <v>0.6062843120804442</v>
       </c>
       <c r="K49">
         <v>3</v>
       </c>
       <c r="L49">
-        <v>-2.462320888977404</v>
+        <v>-2.451837779706402</v>
       </c>
       <c r="M49">
-        <v>1.385741820164553</v>
+        <v>1.407096758157366</v>
       </c>
       <c r="N49">
-        <v>-8.166220598160313</v>
+        <v>-7.924893640616051</v>
       </c>
       <c r="O49">
-        <v>0.4388653683072901</v>
+        <v>0.4522742782606974</v>
       </c>
       <c r="P49">
-        <v>0.03234940551171972</v>
+        <v>0.03385734541957741</v>
       </c>
       <c r="Q49">
-        <v>0.9997089461462456</v>
+        <v>0.9996376335563179</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -8196,22 +8196,22 @@
         <v>0</v>
       </c>
       <c r="T49">
-        <v>0.8482979057518689</v>
+        <v>0.8427271311301602</v>
       </c>
       <c r="U49">
-        <v>1.03242320365715E-06</v>
+        <v>5.343548775268861E-12</v>
       </c>
       <c r="V49">
-        <v>3.292743782160414</v>
+        <v>3.291195115241907</v>
       </c>
       <c r="W49">
-        <v>0.01017767387959923</v>
+        <v>0.1911640488229976</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8294,7 +8294,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CO2_Fixation</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8321,37 +8321,37 @@
         <v>1</v>
       </c>
       <c r="G51">
-        <v>6.59158001013266</v>
+        <v>6.591660520323245</v>
       </c>
       <c r="H51">
-        <v>6.242144985203292</v>
+        <v>6.266672674985772</v>
       </c>
       <c r="I51">
-        <v>-0.3494350249293684</v>
+        <v>-0.3249878453374726</v>
       </c>
       <c r="J51">
-        <v>0.6154101806493649</v>
+        <v>0.6013932946668807</v>
       </c>
       <c r="K51">
         <v>3</v>
       </c>
       <c r="L51">
-        <v>-2.307944880570919</v>
+        <v>-2.238889713972483</v>
       </c>
       <c r="M51">
-        <v>1.609074830712182</v>
+        <v>1.588914023297538</v>
       </c>
       <c r="N51">
-        <v>-5.301233154906902</v>
+        <v>-4.930287965156551</v>
       </c>
       <c r="O51">
-        <v>0.6098816502586638</v>
+        <v>0.6264670499699984</v>
       </c>
       <c r="P51">
-        <v>0.04516665057248748</v>
+        <v>0.02957687153507405</v>
       </c>
       <c r="Q51">
-        <v>0.547530993451675</v>
+        <v>0.5200086538958213</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -8362,16 +8362,16 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>0.3244914930714116</v>
+        <v>0.3236407905145064</v>
       </c>
       <c r="U51">
-        <v>0.000896952497384903</v>
+        <v>1.498056809509892E-09</v>
       </c>
       <c r="V51">
-        <v>3.311514875445636</v>
+        <v>3.275680875378317</v>
       </c>
       <c r="W51">
-        <v>0.1393926226377443</v>
+        <v>0.005721042199989076</v>
       </c>
     </row>
     <row r="52">
@@ -8487,37 +8487,37 @@
         <v>1</v>
       </c>
       <c r="G53">
-        <v>0.3153355993272437</v>
+        <v>0.3153352424376289</v>
       </c>
       <c r="H53">
-        <v>0.3157231349461231</v>
+        <v>0.3157304535109755</v>
       </c>
       <c r="I53">
-        <v>0.0003875356188793529</v>
+        <v>0.0003952110733465017</v>
       </c>
       <c r="J53">
-        <v>0.0009442374299881536</v>
+        <v>0.0009586914402361674</v>
       </c>
       <c r="K53">
         <v>3</v>
       </c>
       <c r="L53">
-        <v>-0.00261744930149703</v>
+        <v>-0.002655772958540206</v>
       </c>
       <c r="M53">
-        <v>0.003392520539255736</v>
+        <v>0.003446195105233209</v>
       </c>
       <c r="N53">
-        <v>0.1228962475870612</v>
+        <v>0.125330448411478</v>
       </c>
       <c r="O53">
-        <v>0.7090485357599001</v>
+        <v>0.7078507854183568</v>
       </c>
       <c r="P53">
-        <v>0.004960061082535661</v>
+        <v>0.00314072950458133</v>
       </c>
       <c r="Q53">
-        <v>0.3458447272586079</v>
+        <v>0.3452842744354752</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -8528,16 +8528,16 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>0.0002129659157101916</v>
+        <v>0.0002721451483668004</v>
       </c>
       <c r="U53">
-        <v>1.777067762232534E-06</v>
+        <v>2.269958981893772E-07</v>
       </c>
       <c r="V53">
-        <v>0.003868360764759008</v>
+        <v>0.003865893252774135</v>
       </c>
       <c r="W53">
-        <v>0.7134183998808797</v>
+        <v>0.7269982467127181</v>
       </c>
     </row>
     <row r="54">
@@ -8570,37 +8570,37 @@
         <v>1</v>
       </c>
       <c r="G54">
-        <v>0.3157230535705502</v>
+        <v>0.3157304562415406</v>
       </c>
       <c r="H54">
-        <v>0.3154075004466786</v>
+        <v>0.3154071899154539</v>
       </c>
       <c r="I54">
-        <v>-0.0003155531238716422</v>
+        <v>-0.0003232663260867559</v>
       </c>
       <c r="J54">
-        <v>0.001215385295587757</v>
+        <v>0.001229887052545243</v>
       </c>
       <c r="K54">
         <v>3</v>
       </c>
       <c r="L54">
-        <v>-0.004183451567311045</v>
+        <v>-0.004237315832375632</v>
       </c>
       <c r="M54">
-        <v>0.003552345319567761</v>
+        <v>0.003590783180202121</v>
       </c>
       <c r="N54">
-        <v>-0.09994617760819607</v>
+        <v>-0.1023868048508599</v>
       </c>
       <c r="O54">
-        <v>0.8119454255237746</v>
+        <v>0.8096894602134965</v>
       </c>
       <c r="P54">
-        <v>5.701614414843625E-05</v>
+        <v>3.471564218149314E-05</v>
       </c>
       <c r="Q54">
-        <v>0.04229615597581859</v>
+        <v>0.03646049284901376</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -8611,16 +8611,16 @@
         <v>0</v>
       </c>
       <c r="T54">
-        <v>1.189696786237807E-06</v>
+        <v>9.014764402473941E-06</v>
       </c>
       <c r="U54">
-        <v>1.668466918898754E-08</v>
+        <v>4.57671499828114E-07</v>
       </c>
       <c r="V54">
-        <v>0.00505041489817106</v>
+        <v>0.005036308905457747</v>
       </c>
       <c r="W54">
-        <v>0.7031866239805585</v>
+        <v>0.7167722616246767</v>
       </c>
     </row>
     <row r="55">
@@ -8653,37 +8653,37 @@
         <v>1</v>
       </c>
       <c r="G55">
-        <v>0.3157046821594244</v>
+        <v>0.3157191284367973</v>
       </c>
       <c r="H55">
-        <v>0.3162806761833847</v>
+        <v>0.3162792612330411</v>
       </c>
       <c r="I55">
-        <v>0.0005759940239603648</v>
+        <v>0.00056013279624383</v>
       </c>
       <c r="J55">
-        <v>0.0007732939981426408</v>
+        <v>0.0007604856151211545</v>
       </c>
       <c r="K55">
         <v>3</v>
       </c>
       <c r="L55">
-        <v>-0.001884972603326749</v>
+        <v>-0.001860071839819896</v>
       </c>
       <c r="M55">
-        <v>0.003036960651247478</v>
+        <v>0.002980337432307556</v>
       </c>
       <c r="N55">
-        <v>0.1824470958176983</v>
+        <v>0.1774149064129198</v>
       </c>
       <c r="O55">
-        <v>0.5104010062440915</v>
+        <v>0.5147676674980879</v>
       </c>
       <c r="P55">
-        <v>0.01972209931172753</v>
+        <v>0.01734769364584898</v>
       </c>
       <c r="Q55">
-        <v>0.916583228695367</v>
+        <v>0.9321330704262643</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -8694,16 +8694,16 @@
         <v>0</v>
       </c>
       <c r="T55">
-        <v>0.0008605731654238511</v>
+        <v>0.0008624994120359363</v>
       </c>
       <c r="U55">
-        <v>1.703986438653003E-07</v>
+        <v>1.655493299107841E-07</v>
       </c>
       <c r="V55">
-        <v>0.004143841892799715</v>
+        <v>0.004119826880231321</v>
       </c>
       <c r="W55">
-        <v>7.898994042120962E-64</v>
+        <v>1.38744095679252E-106</v>
       </c>
     </row>
     <row r="56">
@@ -8736,37 +8736,37 @@
         <v>1</v>
       </c>
       <c r="G56">
-        <v>0.3157231357166184</v>
+        <v>0.3157333588089347</v>
       </c>
       <c r="H56">
-        <v>0.3151123796484406</v>
+        <v>0.3152920904522567</v>
       </c>
       <c r="I56">
-        <v>-0.0006107560681777322</v>
+        <v>-0.0004412683566780214</v>
       </c>
       <c r="J56">
-        <v>0.001216761001392869</v>
+        <v>0.001774409480107203</v>
       </c>
       <c r="K56">
         <v>3</v>
       </c>
       <c r="L56">
-        <v>-0.004483032621473771</v>
+        <v>-0.006088231250705574</v>
       </c>
       <c r="M56">
-        <v>0.003261520485118307</v>
+        <v>0.005205694537349531</v>
       </c>
       <c r="N56">
-        <v>-0.1934467256545699</v>
+        <v>-0.1397598145291495</v>
       </c>
       <c r="O56">
-        <v>0.6502258100576246</v>
+        <v>0.8196572960007106</v>
       </c>
       <c r="P56">
-        <v>0.0701339933399493</v>
+        <v>0.03374103650774773</v>
       </c>
       <c r="Q56">
-        <v>0.5368706021295284</v>
+        <v>0.3412674915381697</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -8777,16 +8777,16 @@
         <v>0</v>
       </c>
       <c r="T56">
-        <v>0.001163103107385138</v>
+        <v>0.001833861386739818</v>
       </c>
       <c r="U56">
-        <v>2.882195261948886E-07</v>
+        <v>4.22459765822859E-07</v>
       </c>
       <c r="V56">
-        <v>0.006484610301725857</v>
+        <v>0.00689502251825283</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>0.7495196684892372</v>
       </c>
     </row>
     <row r="57">
@@ -8902,37 +8902,37 @@
         <v>1</v>
       </c>
       <c r="G58">
-        <v>430.2111944878837</v>
+        <v>430.2137702149078</v>
       </c>
       <c r="H58">
-        <v>409.719741372384</v>
+        <v>409.8348775694029</v>
       </c>
       <c r="I58">
-        <v>-20.49145311549982</v>
+        <v>-20.37889264550478</v>
       </c>
       <c r="J58">
-        <v>3.659532457323773</v>
+        <v>3.579652998800908</v>
       </c>
       <c r="K58">
         <v>3</v>
       </c>
       <c r="L58">
-        <v>-32.13771866337567</v>
+        <v>-31.77094610573647</v>
       </c>
       <c r="M58">
-        <v>-8.845187567623974</v>
+        <v>-8.986839185273084</v>
       </c>
       <c r="N58">
-        <v>-4.763114809202607</v>
+        <v>-4.73692244563087</v>
       </c>
       <c r="O58">
-        <v>0.01125339679453341</v>
+        <v>0.01074480726525029</v>
       </c>
       <c r="P58">
-        <v>1.554312234475219E-14</v>
+        <v>5.551115123125783E-15</v>
       </c>
       <c r="Q58">
-        <v>0.6943840068664153</v>
+        <v>0.6675276327245081</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -8943,16 +8943,16 @@
         <v>1</v>
       </c>
       <c r="T58">
-        <v>7.791175451652052</v>
+        <v>7.698783014118577</v>
       </c>
       <c r="U58">
-        <v>0.001901006866306922</v>
+        <v>0.001442329427050546</v>
       </c>
       <c r="V58">
-        <v>19.60900153084086</v>
+        <v>19.39228031228478</v>
       </c>
       <c r="W58">
-        <v>1.51711935354114E-08</v>
+        <v>3.965550902123399E-11</v>
       </c>
     </row>
     <row r="59">
@@ -8985,37 +8985,37 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>409.622170524124</v>
+        <v>409.8034587840996</v>
       </c>
       <c r="H59">
-        <v>400.7567577842185</v>
+        <v>400.7599321827772</v>
       </c>
       <c r="I59">
-        <v>-8.86541273990559</v>
+        <v>-9.043526601322419</v>
       </c>
       <c r="J59">
-        <v>4.429857669730576</v>
+        <v>4.333668126423748</v>
       </c>
       <c r="K59">
         <v>3</v>
       </c>
       <c r="L59">
-        <v>-22.96319691387236</v>
+        <v>-22.83519271858545</v>
       </c>
       <c r="M59">
-        <v>5.232371434061177</v>
+        <v>4.748139515940606</v>
       </c>
       <c r="N59">
-        <v>-2.164290260110195</v>
+        <v>-2.206796064668381</v>
       </c>
       <c r="O59">
-        <v>0.1391524428753107</v>
+        <v>0.128166862355742</v>
       </c>
       <c r="P59">
-        <v>1.998401444325282E-15</v>
+        <v>6.661338147750939E-16</v>
       </c>
       <c r="Q59">
-        <v>0.9813730342446082</v>
+        <v>0.9798984110099337</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -9026,16 +9026,16 @@
         <v>0</v>
       </c>
       <c r="T59">
-        <v>9.928060705068173</v>
+        <v>9.819666485806268</v>
       </c>
       <c r="U59">
-        <v>0.0011663166488086</v>
+        <v>0.001204063601102828</v>
       </c>
       <c r="V59">
-        <v>23.73657677089098</v>
+        <v>23.47705459380846</v>
       </c>
       <c r="W59">
-        <v>4.450583619880312E-06</v>
+        <v>3.135478910989255E-11</v>
       </c>
     </row>
     <row r="60">
@@ -9068,37 +9068,37 @@
         <v>1</v>
       </c>
       <c r="G60">
-        <v>409.627669231335</v>
+        <v>409.7887912303106</v>
       </c>
       <c r="H60">
-        <v>397.4039510398969</v>
+        <v>397.4082034531409</v>
       </c>
       <c r="I60">
-        <v>-12.2237181914381</v>
+        <v>-12.38058777716968</v>
       </c>
       <c r="J60">
-        <v>4.26023312324332</v>
+        <v>4.168287177607073</v>
       </c>
       <c r="K60">
         <v>3</v>
       </c>
       <c r="L60">
-        <v>-25.78168135415108</v>
+        <v>-25.64593790490677</v>
       </c>
       <c r="M60">
-        <v>1.33424497127487</v>
+        <v>0.8847623505674029</v>
       </c>
       <c r="N60">
-        <v>-2.984104617340882</v>
+        <v>-3.021211912604879</v>
       </c>
       <c r="O60">
-        <v>0.06408908599845142</v>
+        <v>0.05905932557481774</v>
       </c>
       <c r="P60">
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0.8915837031056246</v>
+        <v>0.8863287092242488</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -9109,16 +9109,16 @@
         <v>0</v>
       </c>
       <c r="T60">
-        <v>10.31233309826335</v>
+        <v>10.18194361123499</v>
       </c>
       <c r="U60">
-        <v>0.001198096178399145</v>
+        <v>0.001598978632212218</v>
       </c>
       <c r="V60">
-        <v>22.82756009902734</v>
+        <v>22.58112551826893</v>
       </c>
       <c r="W60">
-        <v>1.656251806462896E-06</v>
+        <v>5.041243534816925E-06</v>
       </c>
     </row>
     <row r="61">
@@ -9151,37 +9151,37 @@
         <v>1</v>
       </c>
       <c r="G61">
-        <v>409.6140990578524</v>
+        <v>409.8001771516513</v>
       </c>
       <c r="H61">
-        <v>390.593337227264</v>
+        <v>389.0557932526642</v>
       </c>
       <c r="I61">
-        <v>-19.02076183058843</v>
+        <v>-20.74438389898702</v>
       </c>
       <c r="J61">
-        <v>4.098041476069388</v>
+        <v>4.272136231086739</v>
       </c>
       <c r="K61">
         <v>3</v>
       </c>
       <c r="L61">
-        <v>-32.06255878500485</v>
+        <v>-34.34022806327768</v>
       </c>
       <c r="M61">
-        <v>-5.978964876172014</v>
+        <v>-7.148539734696365</v>
       </c>
       <c r="N61">
-        <v>-4.643580842148212</v>
+        <v>-5.062072945690876</v>
       </c>
       <c r="O61">
-        <v>0.01885020510643454</v>
+        <v>0.0166752522478707</v>
       </c>
       <c r="P61">
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0.2323660201923865</v>
+        <v>0.7409446315743013</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -9192,16 +9192,16 @@
         <v>1</v>
       </c>
       <c r="T61">
-        <v>9.88624768341209</v>
+        <v>9.840425285720679</v>
       </c>
       <c r="U61">
-        <v>0.001334003575691423</v>
+        <v>0.001510152346017734</v>
       </c>
       <c r="V61">
-        <v>21.83446937288144</v>
+        <v>23.14371368646203</v>
       </c>
       <c r="W61">
-        <v>3.2284563039027E-05</v>
+        <v>4.989184458509152E-07</v>
       </c>
     </row>
     <row r="62">
@@ -9317,37 +9317,37 @@
         <v>1</v>
       </c>
       <c r="G63">
-        <v>1.948268149331924</v>
+        <v>1.948271209719626</v>
       </c>
       <c r="H63">
-        <v>1.943024357263128</v>
+        <v>1.943111261665812</v>
       </c>
       <c r="I63">
-        <v>-0.00524379206879628</v>
+        <v>-0.005159948053814313</v>
       </c>
       <c r="J63">
-        <v>0.003953411392643144</v>
+        <v>0.003856300869723809</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63">
-        <v>-0.01782531154857997</v>
+        <v>-0.0174324185087292</v>
       </c>
       <c r="M63">
-        <v>0.007337727410987411</v>
+        <v>0.007112522401100572</v>
       </c>
       <c r="N63">
-        <v>-0.2691514548751626</v>
+        <v>-0.2648475236954754</v>
       </c>
       <c r="O63">
-        <v>0.2766432087978002</v>
+        <v>0.2732597245260793</v>
       </c>
       <c r="P63">
-        <v>1.913775804496254E-10</v>
+        <v>8.506528814677949E-11</v>
       </c>
       <c r="Q63">
-        <v>0.9936804682547112</v>
+        <v>0.9949529799195193</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -9358,16 +9358,16 @@
         <v>0</v>
       </c>
       <c r="T63">
-        <v>0.01423032162681809</v>
+        <v>0.01410781226749054</v>
       </c>
       <c r="U63">
-        <v>5.376115281604507E-07</v>
+        <v>5.717415249641919E-07</v>
       </c>
       <c r="V63">
-        <v>0.0172534776599471</v>
+        <v>0.01706369831855342</v>
       </c>
       <c r="W63">
-        <v>0.6639040958908912</v>
+        <v>0.6568476988517707</v>
       </c>
     </row>
     <row r="64">
@@ -9400,37 +9400,37 @@
         <v>1</v>
       </c>
       <c r="G64">
-        <v>1.943039652383867</v>
+        <v>1.943139339343058</v>
       </c>
       <c r="H64">
-        <v>1.941265305603797</v>
+        <v>1.941265139922319</v>
       </c>
       <c r="I64">
-        <v>-0.00177434678006975</v>
+        <v>-0.00187419942073911</v>
       </c>
       <c r="J64">
-        <v>0.004339328278691033</v>
+        <v>0.004203416901147594</v>
       </c>
       <c r="K64">
         <v>3</v>
       </c>
       <c r="L64">
-        <v>-0.01558402602800314</v>
+        <v>-0.01525134800736336</v>
       </c>
       <c r="M64">
-        <v>0.01203533246786364</v>
+        <v>0.01150294916588514</v>
       </c>
       <c r="N64">
-        <v>-0.09131809419806994</v>
+        <v>-0.09645213715722231</v>
       </c>
       <c r="O64">
-        <v>0.7100525165459641</v>
+        <v>0.6859026771126462</v>
       </c>
       <c r="P64">
-        <v>4.154676602752261E-12</v>
+        <v>2.041256053075813E-12</v>
       </c>
       <c r="Q64">
-        <v>0.99994683652827</v>
+        <v>0.9999650763886551</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -9441,16 +9441,16 @@
         <v>0</v>
       </c>
       <c r="T64">
-        <v>0.01357137757161643</v>
+        <v>0.01344622721816947</v>
       </c>
       <c r="U64">
-        <v>5.93773902386992E-07</v>
+        <v>5.66873855914748E-07</v>
       </c>
       <c r="V64">
-        <v>0.01677286818663838</v>
+        <v>0.01656148965366479</v>
       </c>
       <c r="W64">
-        <v>0.7504836364244967</v>
+        <v>0.7413864261175886</v>
       </c>
     </row>
     <row r="65">
@@ -9483,37 +9483,37 @@
         <v>1</v>
       </c>
       <c r="G65">
-        <v>1.943056409485883</v>
+        <v>1.943137138087516</v>
       </c>
       <c r="H65">
-        <v>1.939257543721702</v>
+        <v>1.939257354679854</v>
       </c>
       <c r="I65">
-        <v>-0.003798865764180969</v>
+        <v>-0.003879783407662445</v>
       </c>
       <c r="J65">
-        <v>0.003881662316996381</v>
+        <v>0.003766740591531881</v>
       </c>
       <c r="K65">
         <v>3</v>
       </c>
       <c r="L65">
-        <v>-0.0161520476632651</v>
+        <v>-0.01586723308614525</v>
       </c>
       <c r="M65">
-        <v>0.008554316134903159</v>
+        <v>0.008107666270820355</v>
       </c>
       <c r="N65">
-        <v>-0.1955098032993349</v>
+        <v>-0.1996659593198359</v>
       </c>
       <c r="O65">
-        <v>0.3999165716671191</v>
+        <v>0.3787781174855744</v>
       </c>
       <c r="P65">
-        <v>2.005284827077958E-09</v>
+        <v>1.124627169168946E-09</v>
       </c>
       <c r="Q65">
-        <v>0.999114871858075</v>
+        <v>0.9990206494416535</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -9524,16 +9524,16 @@
         <v>0</v>
       </c>
       <c r="T65">
-        <v>0.01186007359056078</v>
+        <v>0.01175583122523736</v>
       </c>
       <c r="U65">
-        <v>5.991932744776056E-07</v>
+        <v>4.964117866142347E-07</v>
       </c>
       <c r="V65">
-        <v>0.01632935563465338</v>
+        <v>0.01612826254253137</v>
       </c>
       <c r="W65">
-        <v>0.6939229869839398</v>
+        <v>0.6842391555207569</v>
       </c>
     </row>
     <row r="66">
@@ -9566,37 +9566,37 @@
         <v>1</v>
       </c>
       <c r="G66">
-        <v>1.943043816759888</v>
+        <v>1.943141405492432</v>
       </c>
       <c r="H66">
-        <v>1.936367353770543</v>
+        <v>1.935721994105011</v>
       </c>
       <c r="I66">
-        <v>-0.006676462989344632</v>
+        <v>-0.007419411387421295</v>
       </c>
       <c r="J66">
-        <v>0.004159744104884571</v>
+        <v>0.004050616268352666</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66">
-        <v>-0.01991462524686022</v>
+        <v>-0.02031028016476231</v>
       </c>
       <c r="M66">
-        <v>0.006561699268170957</v>
+        <v>0.005471457389919725</v>
       </c>
       <c r="N66">
-        <v>-0.3436084627508776</v>
+        <v>-0.3818256029360386</v>
       </c>
       <c r="O66">
-        <v>0.2068339965039547</v>
+        <v>0.1643951673923553</v>
       </c>
       <c r="P66">
-        <v>7.282283842613424E-08</v>
+        <v>1.914946370362713E-07</v>
       </c>
       <c r="Q66">
-        <v>0.9861669451029793</v>
+        <v>0.9823710929996634</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -9607,16 +9607,16 @@
         <v>0</v>
       </c>
       <c r="T66">
-        <v>0.01157268013398052</v>
+        <v>0.01063763645186407</v>
       </c>
       <c r="U66">
-        <v>5.763115460050453E-07</v>
+        <v>7.665914896786784E-07</v>
       </c>
       <c r="V66">
-        <v>0.01704898102758481</v>
+        <v>0.01709833141074798</v>
       </c>
       <c r="W66">
-        <v>0.7106239580137147</v>
+        <v>0.6951375704280913</v>
       </c>
     </row>
     <row r="67">
@@ -9732,37 +9732,37 @@
         <v>1</v>
       </c>
       <c r="G68">
-        <v>2.771225627884546</v>
+        <v>2.771240426322375</v>
       </c>
       <c r="H68">
-        <v>2.841602092123555</v>
+        <v>2.841930055237366</v>
       </c>
       <c r="I68">
-        <v>0.07037646423900969</v>
+        <v>0.07068962891499055</v>
       </c>
       <c r="J68">
-        <v>0.04244239874310623</v>
+        <v>0.04148379210775971</v>
       </c>
       <c r="K68">
         <v>3</v>
       </c>
       <c r="L68">
-        <v>-0.06469419082836662</v>
+        <v>-0.06133031200750678</v>
       </c>
       <c r="M68">
-        <v>0.205447119306386</v>
+        <v>0.2027095698374879</v>
       </c>
       <c r="N68">
-        <v>2.53954292031907</v>
+        <v>2.550829882660181</v>
       </c>
       <c r="O68">
-        <v>0.1958647064806621</v>
+        <v>0.1869238745852355</v>
       </c>
       <c r="P68">
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0.9736762231794301</v>
+        <v>0.9641668787557865</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -9773,16 +9773,16 @@
         <v>0</v>
       </c>
       <c r="T68">
-        <v>0.1110889755322012</v>
+        <v>0.1112360024055218</v>
       </c>
       <c r="U68">
-        <v>5.494710475748625E-06</v>
+        <v>5.861337019358823E-06</v>
       </c>
       <c r="V68">
-        <v>0.2274176007041696</v>
+        <v>0.2247327754723665</v>
       </c>
       <c r="W68">
-        <v>6.672654773435305E-56</v>
+        <v>2.548509081382792E-46</v>
       </c>
     </row>
     <row r="69">
@@ -9815,37 +9815,37 @@
         <v>1</v>
       </c>
       <c r="G69">
-        <v>2.839335005286892</v>
+        <v>2.840990555052098</v>
       </c>
       <c r="H69">
-        <v>2.86704576363682</v>
+        <v>2.867083444299015</v>
       </c>
       <c r="I69">
-        <v>0.0277107583499275</v>
+        <v>0.02609288924691698</v>
       </c>
       <c r="J69">
-        <v>0.05272905281620509</v>
+        <v>0.05176661890884371</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69">
-        <v>-0.1400966209661139</v>
+        <v>-0.1386515958365624</v>
       </c>
       <c r="M69">
-        <v>0.1955181376659689</v>
+        <v>0.1908373743303964</v>
       </c>
       <c r="N69">
-        <v>0.9759594517142067</v>
+        <v>0.9184433647805101</v>
       </c>
       <c r="O69">
-        <v>0.6355829920308547</v>
+        <v>0.6489152706289032</v>
       </c>
       <c r="P69">
-        <v>1.509903313490213E-13</v>
+        <v>4.873879078104437E-14</v>
       </c>
       <c r="Q69">
-        <v>0.991968658144788</v>
+        <v>0.9886560494352415</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -9856,16 +9856,16 @@
         <v>0</v>
       </c>
       <c r="T69">
-        <v>0.08479109486025831</v>
+        <v>0.08593287746605856</v>
       </c>
       <c r="U69">
-        <v>7.211908076161837E-06</v>
+        <v>7.232534748068155E-06</v>
       </c>
       <c r="V69">
-        <v>0.2499702431176397</v>
+        <v>0.2471189503046436</v>
       </c>
       <c r="W69">
-        <v>0.5749646268837605</v>
+        <v>0.5757866747347514</v>
       </c>
     </row>
     <row r="70">
@@ -9898,37 +9898,37 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <v>2.840525949986456</v>
+        <v>2.841034999317064</v>
       </c>
       <c r="H70">
-        <v>2.843171654728482</v>
+        <v>2.843240340532977</v>
       </c>
       <c r="I70">
-        <v>0.002645704742025528</v>
+        <v>0.002205341215912867</v>
       </c>
       <c r="J70">
-        <v>0.04929439677464202</v>
+        <v>0.04818339124230137</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70">
-        <v>-0.1542310661446231</v>
+        <v>-0.1511357142191885</v>
       </c>
       <c r="M70">
-        <v>0.1595224756286741</v>
+        <v>0.1555463966510142</v>
       </c>
       <c r="N70">
-        <v>0.09314136848628836</v>
+        <v>0.07762457049782889</v>
       </c>
       <c r="O70">
-        <v>0.9605710281673863</v>
+        <v>0.9663700805915419</v>
       </c>
       <c r="P70">
-        <v>8.72368843829463E-12</v>
+        <v>2.55484522426741E-12</v>
       </c>
       <c r="Q70">
-        <v>0.95810937170445</v>
+        <v>0.9439177805828365</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -9939,16 +9939,16 @@
         <v>0</v>
       </c>
       <c r="T70">
-        <v>0.07169998641067622</v>
+        <v>0.07324899263104312</v>
       </c>
       <c r="U70">
-        <v>7.731144241133527E-06</v>
+        <v>7.587595429335021E-06</v>
       </c>
       <c r="V70">
-        <v>0.2641451022907346</v>
+        <v>0.2610269380465201</v>
       </c>
       <c r="W70">
-        <v>2.57567345497727E-44</v>
+        <v>5.164219023285096E-42</v>
       </c>
     </row>
     <row r="71">
@@ -9981,37 +9981,37 @@
         <v>1</v>
       </c>
       <c r="G71">
-        <v>2.841758573884985</v>
+        <v>2.841529888670257</v>
       </c>
       <c r="H71">
-        <v>2.926898197667955</v>
+        <v>2.932506021723353</v>
       </c>
       <c r="I71">
-        <v>0.08513962378297039</v>
+        <v>0.09097613305309646</v>
       </c>
       <c r="J71">
-        <v>0.0479909251515636</v>
+        <v>0.04679481896271249</v>
       </c>
       <c r="K71">
         <v>3</v>
       </c>
       <c r="L71">
-        <v>-0.06758891865277016</v>
+        <v>-0.05794586566120791</v>
       </c>
       <c r="M71">
-        <v>0.2378681662187109</v>
+        <v>0.2398981317674008</v>
       </c>
       <c r="N71">
-        <v>2.996018893560529</v>
+        <v>3.20166025407075</v>
       </c>
       <c r="O71">
-        <v>0.1741509923555374</v>
+        <v>0.1471130267084311</v>
       </c>
       <c r="P71">
-        <v>1.103117597267556E-12</v>
+        <v>2.473576898864849E-13</v>
       </c>
       <c r="Q71">
-        <v>0.7951163346389026</v>
+        <v>0.8212913909258585</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -10022,16 +10022,16 @@
         <v>0</v>
       </c>
       <c r="T71">
-        <v>0.08472067363348257</v>
+        <v>0.08098199489215732</v>
       </c>
       <c r="U71">
-        <v>6.920258430123838E-06</v>
+        <v>7.320170019031891E-06</v>
       </c>
       <c r="V71">
-        <v>0.2557138602463883</v>
+        <v>0.253504537483755</v>
       </c>
       <c r="W71">
-        <v>3.60384401082165E-12</v>
+        <v>2.235651918946122E-12</v>
       </c>
     </row>
     <row r="72">
@@ -10147,37 +10147,37 @@
         <v>1</v>
       </c>
       <c r="G73">
-        <v>5.583867041105841</v>
+        <v>5.583311313835311</v>
       </c>
       <c r="H73">
-        <v>5.525482094818368</v>
+        <v>5.483461997581386</v>
       </c>
       <c r="I73">
-        <v>-0.05838494628747413</v>
+        <v>-0.09984931625392426</v>
       </c>
       <c r="J73">
-        <v>0.3184944237185825</v>
+        <v>0.3138259393826464</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73">
-        <v>-1.071976348304141</v>
+        <v>-1.098583517544416</v>
       </c>
       <c r="M73">
-        <v>0.9552064557291924</v>
+        <v>0.8988848850365675</v>
       </c>
       <c r="N73">
-        <v>-1.045600582135485</v>
+        <v>-1.788353015646827</v>
       </c>
       <c r="O73">
-        <v>0.8662401433987721</v>
+        <v>0.7712198193670468</v>
       </c>
       <c r="P73">
-        <v>7.057230197116127E-06</v>
+        <v>7.261974614536371E-06</v>
       </c>
       <c r="Q73">
-        <v>0.9984314835722887</v>
+        <v>0.998167240215236</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -10188,16 +10188,16 @@
         <v>0</v>
       </c>
       <c r="T73">
-        <v>0.2606927708304726</v>
+        <v>0.2394398228436408</v>
       </c>
       <c r="U73">
-        <v>0.0001049582654523172</v>
+        <v>8.565847780285781E-05</v>
       </c>
       <c r="V73">
-        <v>1.706776731037123</v>
+        <v>1.700109122774087</v>
       </c>
       <c r="W73">
-        <v>1.782644942593974E-58</v>
+        <v>2.650271870245946E-50</v>
       </c>
     </row>
     <row r="74">
@@ -10230,37 +10230,37 @@
         <v>1</v>
       </c>
       <c r="G74">
-        <v>5.523315766740235</v>
+        <v>5.483450118493105</v>
       </c>
       <c r="H74">
-        <v>5.714420479698197</v>
+        <v>5.714364609931082</v>
       </c>
       <c r="I74">
-        <v>0.1911047129579628</v>
+        <v>0.2309144914379769</v>
       </c>
       <c r="J74">
-        <v>0.4592324826215018</v>
+        <v>0.4508324978083577</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74">
-        <v>-1.2703780046271</v>
+        <v>-1.203835725514056</v>
       </c>
       <c r="M74">
-        <v>1.652587430543026</v>
+        <v>1.66566470839001</v>
       </c>
       <c r="N74">
-        <v>3.459963562263425</v>
+        <v>4.211116841552195</v>
       </c>
       <c r="O74">
-        <v>0.7052861346091143</v>
+        <v>0.6438377991583484</v>
       </c>
       <c r="P74">
-        <v>0.0002991728792167692</v>
+        <v>0.0002689464221578008</v>
       </c>
       <c r="Q74">
-        <v>0.663318413328859</v>
+        <v>0.6712364536979576</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -10271,16 +10271,16 @@
         <v>0</v>
       </c>
       <c r="T74">
-        <v>9.666117474354326E-05</v>
+        <v>9.933198824382698E-05</v>
       </c>
       <c r="U74">
-        <v>2.052302649965805E-05</v>
+        <v>1.914466356389803E-05</v>
       </c>
       <c r="V74">
-        <v>2.28991362452534</v>
+        <v>2.271804039381512</v>
       </c>
       <c r="W74">
-        <v>0.4934940152480488</v>
+        <v>0.4900361321914736</v>
       </c>
     </row>
     <row r="75">
@@ -10313,37 +10313,37 @@
         <v>1</v>
       </c>
       <c r="G75">
-        <v>5.522953577512842</v>
+        <v>5.482791860141587</v>
       </c>
       <c r="H75">
-        <v>5.840061574115506</v>
+        <v>5.840495680439751</v>
       </c>
       <c r="I75">
-        <v>0.3171079966026632</v>
+        <v>0.3577038202981643</v>
       </c>
       <c r="J75">
-        <v>0.391891399234844</v>
+        <v>0.3784796531811237</v>
       </c>
       <c r="K75">
         <v>3</v>
       </c>
       <c r="L75">
-        <v>-0.9300653389647285</v>
+        <v>-0.8467873535931619</v>
       </c>
       <c r="M75">
-        <v>1.564281332170055</v>
+        <v>1.562194994189491</v>
       </c>
       <c r="N75">
-        <v>5.7416379144267</v>
+        <v>6.524118175971155</v>
       </c>
       <c r="O75">
-        <v>0.4776369727421054</v>
+        <v>0.4143286704071242</v>
       </c>
       <c r="P75">
-        <v>7.223239208986598E-07</v>
+        <v>5.967690021035921E-07</v>
       </c>
       <c r="Q75">
-        <v>0.8622167181625052</v>
+        <v>0.8851316495005027</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>0</v>
       </c>
       <c r="T75">
-        <v>7.910360931826291E-05</v>
+        <v>7.517436659572141E-05</v>
       </c>
       <c r="U75">
-        <v>0.2298283543443495</v>
+        <v>0.2005442888836886</v>
       </c>
       <c r="V75">
-        <v>1.910632197267715</v>
+        <v>1.900808129636865</v>
       </c>
       <c r="W75">
-        <v>1.018988721670083E-13</v>
+        <v>2.63035531014967E-14</v>
       </c>
     </row>
     <row r="76">
@@ -10396,37 +10396,37 @@
         <v>1</v>
       </c>
       <c r="G76">
-        <v>5.525669808315548</v>
+        <v>5.483082524840212</v>
       </c>
       <c r="H76">
-        <v>5.644751024459976</v>
+        <v>5.622861454890106</v>
       </c>
       <c r="I76">
-        <v>0.1190812161444288</v>
+        <v>0.1397789300498946</v>
       </c>
       <c r="J76">
-        <v>0.3997687792368437</v>
+        <v>0.3768352249264002</v>
       </c>
       <c r="K76">
         <v>3</v>
       </c>
       <c r="L76">
-        <v>-1.153161458305643</v>
+        <v>-1.059478939217883</v>
       </c>
       <c r="M76">
-        <v>1.3913238905945</v>
+        <v>1.339036799317672</v>
       </c>
       <c r="N76">
-        <v>2.155054867108133</v>
+        <v>2.549276422826921</v>
       </c>
       <c r="O76">
-        <v>0.7852361681925821</v>
+        <v>0.7353357509890049</v>
       </c>
       <c r="P76">
-        <v>4.652565599450043E-08</v>
+        <v>1.441303676408268E-08</v>
       </c>
       <c r="Q76">
-        <v>0.7873021625055505</v>
+        <v>0.7981428562763699</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -10437,16 +10437,16 @@
         <v>0</v>
       </c>
       <c r="T76">
-        <v>0.0001538674803317717</v>
+        <v>0.0001740725385511504</v>
       </c>
       <c r="U76">
-        <v>0.3255448917230016</v>
+        <v>0.2820952044887132</v>
       </c>
       <c r="V76">
-        <v>1.741354265451647</v>
+        <v>1.731633377047392</v>
       </c>
       <c r="W76">
-        <v>1.598717939305513E-50</v>
+        <v>1.93149470475548E-82</v>
       </c>
     </row>
   </sheetData>
